--- a/docs/oc-regiones/articulos-de-escritorio-y-papeleria/tarapaca.xlsx
+++ b/docs/oc-regiones/articulos-de-escritorio-y-papeleria/tarapaca.xlsx
@@ -569,7 +569,7 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>1123.31</v>
+        <v>1112.1</v>
       </c>
     </row>
     <row r="3">
@@ -630,7 +630,7 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>817.26</v>
+        <v>812.79</v>
       </c>
     </row>
     <row r="4">
@@ -691,7 +691,7 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>5186.25</v>
+        <v>5128.46</v>
       </c>
     </row>
     <row r="5">
@@ -752,7 +752,7 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>3347.85</v>
+        <v>3329.52</v>
       </c>
     </row>
     <row r="6">
@@ -813,7 +813,7 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>5182.5</v>
+        <v>5154.12</v>
       </c>
     </row>
     <row r="7">
@@ -874,7 +874,7 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>1152.74</v>
+        <v>1146.43</v>
       </c>
     </row>
     <row r="8">
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>1409.56</v>
+        <v>1407.77</v>
       </c>
     </row>
     <row r="9">
@@ -996,7 +996,7 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>1469.58</v>
+        <v>1474.82</v>
       </c>
     </row>
     <row r="10">
@@ -1057,7 +1057,7 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>21801.53</v>
+        <v>21873.24</v>
       </c>
     </row>
     <row r="11">
@@ -1118,7 +1118,7 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>2908.43</v>
+        <v>2929.4</v>
       </c>
     </row>
     <row r="12">
@@ -1179,7 +1179,7 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>1184.99</v>
+        <v>1180.11</v>
       </c>
     </row>
     <row r="13">
@@ -1240,7 +1240,7 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>1134.85</v>
+        <v>1140.71</v>
       </c>
     </row>
     <row r="14">
@@ -1301,7 +1301,7 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>1452.1</v>
+        <v>1459.6</v>
       </c>
     </row>
     <row r="15">
@@ -1362,7 +1362,7 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>2976.94</v>
+        <v>2964.46</v>
       </c>
     </row>
     <row r="16">
@@ -1423,7 +1423,7 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>945.91</v>
+        <v>934.96</v>
       </c>
     </row>
     <row r="17">
@@ -1484,7 +1484,7 @@
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>764.3099999999999</v>
+        <v>757.83</v>
       </c>
     </row>
     <row r="18">
@@ -1545,7 +1545,7 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>11132.66</v>
+        <v>11162.18</v>
       </c>
     </row>
     <row r="19">
@@ -1606,7 +1606,7 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>2004.16</v>
+        <v>2009.47</v>
       </c>
     </row>
     <row r="20">
@@ -1667,7 +1667,7 @@
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>4408.84</v>
+        <v>4420.53</v>
       </c>
     </row>
     <row r="21">
@@ -1728,7 +1728,7 @@
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>1364.75</v>
+        <v>1368.37</v>
       </c>
     </row>
     <row r="22">
@@ -1789,7 +1789,7 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>2112.84</v>
+        <v>2109.88</v>
       </c>
     </row>
     <row r="23">
@@ -1850,7 +1850,7 @@
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>4446.12</v>
+        <v>4476.72</v>
       </c>
     </row>
     <row r="24">
@@ -1911,7 +1911,7 @@
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>1882.39</v>
+        <v>1898.47</v>
       </c>
     </row>
     <row r="25">
@@ -1972,7 +1972,7 @@
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>968.78</v>
+        <v>981.23</v>
       </c>
     </row>
     <row r="26">
@@ -2033,7 +2033,7 @@
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>2399.25</v>
+        <v>2412.38</v>
       </c>
     </row>
     <row r="27">
@@ -2094,7 +2094,7 @@
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>6592.64</v>
+        <v>6508.96</v>
       </c>
     </row>
     <row r="28">
@@ -2155,7 +2155,7 @@
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>2033.42</v>
+        <v>2007.61</v>
       </c>
     </row>
     <row r="29">
@@ -2216,7 +2216,7 @@
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>4630.53</v>
+        <v>4563.81</v>
       </c>
     </row>
     <row r="30">
@@ -2277,7 +2277,7 @@
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>857.72</v>
+        <v>845.36</v>
       </c>
     </row>
     <row r="31">
@@ -2338,7 +2338,7 @@
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>7808.42</v>
+        <v>7767.17</v>
       </c>
     </row>
     <row r="32">
@@ -2399,7 +2399,7 @@
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>9611.91</v>
+        <v>9561.139999999999</v>
       </c>
     </row>
     <row r="33">
@@ -2460,7 +2460,7 @@
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>1791.8</v>
+        <v>1782.34</v>
       </c>
     </row>
     <row r="34">
@@ -2521,7 +2521,7 @@
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>1175.3</v>
+        <v>1169.1</v>
       </c>
     </row>
     <row r="35">
@@ -2582,7 +2582,7 @@
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>2487.88</v>
+        <v>2563.32</v>
       </c>
     </row>
     <row r="36">
@@ -2643,7 +2643,7 @@
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>2006.12</v>
+        <v>2066.95</v>
       </c>
     </row>
     <row r="37">
@@ -2704,7 +2704,7 @@
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>912.29</v>
+        <v>909.05</v>
       </c>
     </row>
     <row r="38">
@@ -2765,7 +2765,7 @@
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>5573.67</v>
+        <v>5553.82</v>
       </c>
     </row>
     <row r="39">
@@ -2826,7 +2826,7 @@
         </is>
       </c>
       <c r="M39" s="2" t="n">
-        <v>858.03</v>
+        <v>860.51</v>
       </c>
     </row>
     <row r="40">
@@ -2887,7 +2887,7 @@
         </is>
       </c>
       <c r="M40" s="2" t="n">
-        <v>1291.43</v>
+        <v>1298.1</v>
       </c>
     </row>
     <row r="41">
@@ -2948,7 +2948,7 @@
         </is>
       </c>
       <c r="M41" s="2" t="n">
-        <v>1525.01</v>
+        <v>1529.2</v>
       </c>
     </row>
     <row r="42">
@@ -3009,7 +3009,7 @@
         </is>
       </c>
       <c r="M42" s="2" t="n">
-        <v>1492.02</v>
+        <v>1505.59</v>
       </c>
     </row>
     <row r="43">
@@ -3070,7 +3070,7 @@
         </is>
       </c>
       <c r="M43" s="2" t="n">
-        <v>5630.93</v>
+        <v>5670.13</v>
       </c>
     </row>
     <row r="44">
@@ -3131,7 +3131,7 @@
         </is>
       </c>
       <c r="M44" s="2" t="n">
-        <v>1197.13</v>
+        <v>1195.08</v>
       </c>
     </row>
     <row r="45">
@@ -3192,7 +3192,7 @@
         </is>
       </c>
       <c r="M45" s="2" t="n">
-        <v>2642.88</v>
+        <v>2640.16</v>
       </c>
     </row>
     <row r="46">
@@ -3253,7 +3253,7 @@
         </is>
       </c>
       <c r="M46" s="2" t="n">
-        <v>9608.059999999999</v>
+        <v>9555.74</v>
       </c>
     </row>
     <row r="47">
@@ -3314,7 +3314,7 @@
         </is>
       </c>
       <c r="M47" s="2" t="n">
-        <v>5174</v>
+        <v>5200.79</v>
       </c>
     </row>
     <row r="48">
@@ -3375,7 +3375,7 @@
         </is>
       </c>
       <c r="M48" s="2" t="n">
-        <v>1831.94</v>
+        <v>1833.71</v>
       </c>
     </row>
     <row r="49">
@@ -3436,7 +3436,7 @@
         </is>
       </c>
       <c r="M49" s="2" t="n">
-        <v>1682.15</v>
+        <v>1756.44</v>
       </c>
     </row>
     <row r="50">
@@ -3497,7 +3497,7 @@
         </is>
       </c>
       <c r="M50" s="2" t="n">
-        <v>1057.29</v>
+        <v>1074.71</v>
       </c>
     </row>
     <row r="51">
@@ -3558,7 +3558,7 @@
         </is>
       </c>
       <c r="M51" s="2" t="n">
-        <v>874.1</v>
+        <v>876.25</v>
       </c>
     </row>
     <row r="52">
@@ -3619,7 +3619,7 @@
         </is>
       </c>
       <c r="M52" s="2" t="n">
-        <v>2080.9</v>
+        <v>2066.21</v>
       </c>
     </row>
     <row r="53">
@@ -3680,7 +3680,7 @@
         </is>
       </c>
       <c r="M53" s="2" t="n">
-        <v>1119.59</v>
+        <v>1139.89</v>
       </c>
     </row>
     <row r="54">
@@ -3741,7 +3741,7 @@
         </is>
       </c>
       <c r="M54" s="2" t="n">
-        <v>1560.67</v>
+        <v>1588.97</v>
       </c>
     </row>
     <row r="55">
@@ -3802,7 +3802,7 @@
         </is>
       </c>
       <c r="M55" s="2" t="n">
-        <v>2311.89</v>
+        <v>2277.41</v>
       </c>
     </row>
     <row r="56">
@@ -3863,7 +3863,7 @@
         </is>
       </c>
       <c r="M56" s="2" t="n">
-        <v>7619.76</v>
+        <v>7570.95</v>
       </c>
     </row>
     <row r="57">
@@ -3924,7 +3924,7 @@
         </is>
       </c>
       <c r="M57" s="2" t="n">
-        <v>2221.18</v>
+        <v>2206.95</v>
       </c>
     </row>
     <row r="58">
@@ -3985,7 +3985,7 @@
         </is>
       </c>
       <c r="M58" s="2" t="n">
-        <v>880.34</v>
+        <v>859.85</v>
       </c>
     </row>
     <row r="59">
@@ -4046,7 +4046,7 @@
         </is>
       </c>
       <c r="M59" s="2" t="n">
-        <v>1510.16</v>
+        <v>1475.02</v>
       </c>
     </row>
     <row r="60">
@@ -4107,7 +4107,7 @@
         </is>
       </c>
       <c r="M60" s="2" t="n">
-        <v>771.47</v>
+        <v>753.52</v>
       </c>
     </row>
     <row r="61">
@@ -4168,7 +4168,7 @@
         </is>
       </c>
       <c r="M61" s="2" t="n">
-        <v>32505.25</v>
+        <v>31748.88</v>
       </c>
     </row>
     <row r="62">
@@ -4229,7 +4229,7 @@
         </is>
       </c>
       <c r="M62" s="2" t="n">
-        <v>2902.97</v>
+        <v>2810.41</v>
       </c>
     </row>
     <row r="63">
@@ -4290,7 +4290,7 @@
         </is>
       </c>
       <c r="M63" s="2" t="n">
-        <v>1003.54</v>
+        <v>983.75</v>
       </c>
     </row>
     <row r="64">
@@ -4351,7 +4351,7 @@
         </is>
       </c>
       <c r="M64" s="2" t="n">
-        <v>791.08</v>
+        <v>775.48</v>
       </c>
     </row>
     <row r="65">
@@ -4412,7 +4412,7 @@
         </is>
       </c>
       <c r="M65" s="2" t="n">
-        <v>2014.31</v>
+        <v>1961.27</v>
       </c>
     </row>
     <row r="66">
@@ -4473,7 +4473,7 @@
         </is>
       </c>
       <c r="M66" s="2" t="n">
-        <v>2787.97</v>
+        <v>2737.42</v>
       </c>
     </row>
     <row r="67">
@@ -4534,7 +4534,7 @@
         </is>
       </c>
       <c r="M67" s="2" t="n">
-        <v>900.21</v>
+        <v>883.89</v>
       </c>
     </row>
     <row r="68">
@@ -4595,7 +4595,7 @@
         </is>
       </c>
       <c r="M68" s="2" t="n">
-        <v>1097.83</v>
+        <v>1068.43</v>
       </c>
     </row>
     <row r="69">
@@ -4656,7 +4656,7 @@
         </is>
       </c>
       <c r="M69" s="2" t="n">
-        <v>1038.77</v>
+        <v>1043.09</v>
       </c>
     </row>
     <row r="70">
@@ -4717,7 +4717,7 @@
         </is>
       </c>
       <c r="M70" s="2" t="n">
-        <v>2144.06</v>
+        <v>2170.45</v>
       </c>
     </row>
     <row r="71">
@@ -4778,7 +4778,7 @@
         </is>
       </c>
       <c r="M71" s="2" t="n">
-        <v>1816.75</v>
+        <v>1851.11</v>
       </c>
     </row>
     <row r="72">
@@ -4839,7 +4839,7 @@
         </is>
       </c>
       <c r="M72" s="2" t="n">
-        <v>830.35</v>
+        <v>839.79</v>
       </c>
     </row>
     <row r="73">
@@ -4900,7 +4900,7 @@
         </is>
       </c>
       <c r="M73" s="2" t="n">
-        <v>2981.65</v>
+        <v>3008.51</v>
       </c>
     </row>
     <row r="74">
@@ -4961,7 +4961,7 @@
         </is>
       </c>
       <c r="M74" s="2" t="n">
-        <v>5693.64</v>
+        <v>5730.05</v>
       </c>
     </row>
     <row r="75">
@@ -5022,7 +5022,7 @@
         </is>
       </c>
       <c r="M75" s="2" t="n">
-        <v>2648.99</v>
+        <v>2654.48</v>
       </c>
     </row>
     <row r="76">
@@ -5083,7 +5083,7 @@
         </is>
       </c>
       <c r="M76" s="2" t="n">
-        <v>2965.83</v>
+        <v>2971.98</v>
       </c>
     </row>
     <row r="77">
@@ -5144,7 +5144,7 @@
         </is>
       </c>
       <c r="M77" s="2" t="n">
-        <v>803.89</v>
+        <v>797.04</v>
       </c>
     </row>
     <row r="78">
@@ -5205,7 +5205,7 @@
         </is>
       </c>
       <c r="M78" s="2" t="n">
-        <v>1434.01</v>
+        <v>1421.78</v>
       </c>
     </row>
     <row r="79">
@@ -5266,7 +5266,7 @@
         </is>
       </c>
       <c r="M79" s="2" t="n">
-        <v>4018.6</v>
+        <v>4063.54</v>
       </c>
     </row>
     <row r="80">
@@ -5327,7 +5327,7 @@
         </is>
       </c>
       <c r="M80" s="2" t="n">
-        <v>9022.43</v>
+        <v>9123.34</v>
       </c>
     </row>
     <row r="81">
@@ -5388,7 +5388,7 @@
         </is>
       </c>
       <c r="M81" s="2" t="n">
-        <v>3415.67</v>
+        <v>3448.12</v>
       </c>
     </row>
     <row r="82">
@@ -5449,7 +5449,7 @@
         </is>
       </c>
       <c r="M82" s="2" t="n">
-        <v>27604.79</v>
+        <v>27867.05</v>
       </c>
     </row>
     <row r="83">
@@ -5510,7 +5510,7 @@
         </is>
       </c>
       <c r="M83" s="2" t="n">
-        <v>1734.68</v>
+        <v>1717.38</v>
       </c>
     </row>
     <row r="84">
@@ -5571,7 +5571,7 @@
         </is>
       </c>
       <c r="M84" s="2" t="n">
-        <v>2932.22</v>
+        <v>2900.32</v>
       </c>
     </row>
     <row r="85">
@@ -5632,7 +5632,7 @@
         </is>
       </c>
       <c r="M85" s="2" t="n">
-        <v>1331.31</v>
+        <v>1338.38</v>
       </c>
     </row>
     <row r="86">
@@ -5693,7 +5693,7 @@
         </is>
       </c>
       <c r="M86" s="2" t="n">
-        <v>4332.3</v>
+        <v>4394.29</v>
       </c>
     </row>
     <row r="87">
@@ -5754,7 +5754,7 @@
         </is>
       </c>
       <c r="M87" s="2" t="n">
-        <v>797.08</v>
+        <v>806.4299999999999</v>
       </c>
     </row>
     <row r="88">
@@ -5815,7 +5815,7 @@
         </is>
       </c>
       <c r="M88" s="2" t="n">
-        <v>1311.09</v>
+        <v>1288.94</v>
       </c>
     </row>
     <row r="89">
@@ -5876,7 +5876,7 @@
         </is>
       </c>
       <c r="M89" s="2" t="n">
-        <v>794.98</v>
+        <v>783.7</v>
       </c>
     </row>
     <row r="90">
@@ -5937,7 +5937,7 @@
         </is>
       </c>
       <c r="M90" s="2" t="n">
-        <v>1112.8</v>
+        <v>1097.01</v>
       </c>
     </row>
     <row r="91">
@@ -5998,7 +5998,7 @@
         </is>
       </c>
       <c r="M91" s="2" t="n">
-        <v>1140.79</v>
+        <v>1133.72</v>
       </c>
     </row>
     <row r="92">
@@ -6059,7 +6059,7 @@
         </is>
       </c>
       <c r="M92" s="2" t="n">
-        <v>814.88</v>
+        <v>833.25</v>
       </c>
     </row>
     <row r="93">
@@ -6120,7 +6120,7 @@
         </is>
       </c>
       <c r="M93" s="2" t="n">
-        <v>816.01</v>
+        <v>818.53</v>
       </c>
     </row>
     <row r="94">
@@ -6181,7 +6181,7 @@
         </is>
       </c>
       <c r="M94" s="2" t="n">
-        <v>3213.92</v>
+        <v>3171.11</v>
       </c>
     </row>
     <row r="95">
@@ -6242,7 +6242,7 @@
         </is>
       </c>
       <c r="M95" s="2" t="n">
-        <v>8342.790000000001</v>
+        <v>8179.49</v>
       </c>
     </row>
     <row r="96">
@@ -6303,7 +6303,7 @@
         </is>
       </c>
       <c r="M96" s="2" t="n">
-        <v>4498.93</v>
+        <v>4432.28</v>
       </c>
     </row>
     <row r="97">
@@ -6364,7 +6364,7 @@
         </is>
       </c>
       <c r="M97" s="2" t="n">
-        <v>1097.48</v>
+        <v>1081.22</v>
       </c>
     </row>
     <row r="98">
@@ -6425,7 +6425,7 @@
         </is>
       </c>
       <c r="M98" s="2" t="n">
-        <v>1246.03</v>
+        <v>1227.57</v>
       </c>
     </row>
     <row r="99">
@@ -6486,7 +6486,7 @@
         </is>
       </c>
       <c r="M99" s="2" t="n">
-        <v>10019.67</v>
+        <v>9813.75</v>
       </c>
     </row>
     <row r="100">
@@ -6547,7 +6547,7 @@
         </is>
       </c>
       <c r="M100" s="2" t="n">
-        <v>3385.15</v>
+        <v>3398.37</v>
       </c>
     </row>
     <row r="101">
@@ -6608,7 +6608,7 @@
         </is>
       </c>
       <c r="M101" s="2" t="n">
-        <v>796.98</v>
+        <v>805</v>
       </c>
     </row>
     <row r="102">
@@ -6669,7 +6669,7 @@
         </is>
       </c>
       <c r="M102" s="2" t="n">
-        <v>1197.47</v>
+        <v>1202.13</v>
       </c>
     </row>
     <row r="103">
@@ -6730,7 +6730,7 @@
         </is>
       </c>
       <c r="M103" s="2" t="n">
-        <v>962.16</v>
+        <v>968.89</v>
       </c>
     </row>
     <row r="104">
@@ -6791,7 +6791,7 @@
         </is>
       </c>
       <c r="M104" s="2" t="n">
-        <v>1404.82</v>
+        <v>1401.76</v>
       </c>
     </row>
     <row r="105">
@@ -6852,7 +6852,7 @@
         </is>
       </c>
       <c r="M105" s="2" t="n">
-        <v>6441.56</v>
+        <v>6337.61</v>
       </c>
     </row>
     <row r="106">
@@ -6913,7 +6913,7 @@
         </is>
       </c>
       <c r="M106" s="2" t="n">
-        <v>3344.05</v>
+        <v>3290.43</v>
       </c>
     </row>
     <row r="107">
@@ -6974,7 +6974,7 @@
         </is>
       </c>
       <c r="M107" s="2" t="n">
-        <v>2720.55</v>
+        <v>2705.47</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/articulos-de-escritorio-y-papeleria/tarapaca.xlsx
+++ b/docs/oc-regiones/articulos-de-escritorio-y-papeleria/tarapaca.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M107"/>
+  <dimension ref="A1:M110"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -514,7 +514,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>1346281-174-CM25</t>
+          <t>1070620-15782-CM25</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -524,27 +524,27 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>ago-2025</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-08-18</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>62.000.970-9</t>
+          <t>62.000.530-4</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
+          <t>HOSPITAL DOCTOR ERNESTO TORRES GALDAMES</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -569,13 +569,13 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>1112.1</v>
+        <v>7260.53</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>696217-138-CM25</t>
+          <t>2549-36-CM25</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -585,27 +585,27 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>sep-2025</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-09-29</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>61.935.400-1</t>
+          <t>61.606.100-3</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>MINISTERIO PUBLICO</t>
+          <t>SERVICIO DE SALUD IQUIQUE</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -615,12 +615,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA NENE SPA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>76.067.436-2</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
@@ -630,13 +630,13 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>812.79</v>
+        <v>1062.19</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>1079967-642-CM25</t>
+          <t>707412-92-CM25</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -646,12 +646,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>oct-2025</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-10-16</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -661,12 +661,12 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>60.505.102-2</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS I ZONA</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -676,12 +676,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>MUÑOZ Y VILCHES LIMITADA</t>
+          <t>DISTRIBUIDORA NENE SPA</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>77.008.207-2</t>
+          <t>76.067.436-2</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
@@ -691,13 +691,13 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>5128.46</v>
+        <v>4633.33</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>1070620-18352-CM25</t>
+          <t>1346281-174-CM25</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -712,22 +712,22 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>62.000.530-4</t>
+          <t>62.000.970-9</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>HOSPITAL DOCTOR ERNESTO TORRES GALDAMES</t>
+          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>3329.52</v>
+        <v>1112.1</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>1260688-275-CM25</t>
+          <t>696217-138-CM25</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -773,7 +773,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>71.497.400-9</t>
+          <t>61.935.400-1</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>CORPORACION MUNICIPAL DE DESARROLLO SOCIAL POZO AL</t>
+          <t>MINISTERIO PUBLICO</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -798,12 +798,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>SOCIEDAD DE INVERSIONES DASSEN SPA</t>
+          <t>DISTRIBUIDORA NENE SPA</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>77.537.871-9</t>
+          <t>76.067.436-2</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
@@ -813,13 +813,13 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>5154.12</v>
+        <v>812.79</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>1213005-338-CM25</t>
+          <t>1079967-642-CM25</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -834,22 +834,22 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>71.497.400-9</t>
+          <t>60.505.102-2</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>CORP MUNICIPAL DE DESARROLLO SOCIAL DE POZO ALMONTE</t>
+          <t>SECCIÓN COMPRAS I ZONA</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -859,12 +859,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>SOCIEDAD DE INVERSIONES DASSEN SPA</t>
+          <t>MUÑOZ Y VILCHES LIMITADA</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>77.537.871-9</t>
+          <t>77.008.207-2</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
@@ -874,13 +874,13 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>1146.43</v>
+        <v>5128.46</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>768-642-CM25</t>
+          <t>1213005-338-CM25</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -895,22 +895,22 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>72.223.100-7</t>
+          <t>71.497.400-9</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL DE TARAPACA</t>
+          <t>CORP MUNICIPAL DE DESARROLLO SOCIAL DE POZO ALMONTE</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -920,12 +920,12 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA NENE SPA</t>
+          <t>SOCIEDAD DE INVERSIONES DASSEN SPA</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>76.067.436-2</t>
+          <t>77.537.871-9</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
@@ -935,13 +935,13 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>1407.77</v>
+        <v>1146.43</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>696217-149-CM25</t>
+          <t>1070620-18352-CM25</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -956,22 +956,22 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>61.935.400-1</t>
+          <t>62.000.530-4</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>MINISTERIO PUBLICO</t>
+          <t>HOSPITAL DOCTOR ERNESTO TORRES GALDAMES</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -996,13 +996,13 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>1474.82</v>
+        <v>3329.52</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>1079967-659-CM25</t>
+          <t>1260688-275-CM25</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1017,22 +1017,22 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>60.505.102-2</t>
+          <t>71.497.400-9</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS I ZONA</t>
+          <t>CORPORACION MUNICIPAL DE DESARROLLO SOCIAL POZO AL</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1042,12 +1042,12 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>MUÑOZ Y VILCHES LIMITADA</t>
+          <t>SOCIEDAD DE INVERSIONES DASSEN SPA</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>77.008.207-2</t>
+          <t>77.537.871-9</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
@@ -1057,13 +1057,13 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>21873.24</v>
+        <v>5154.12</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>908366-104-CM25</t>
+          <t>768-642-CM25</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1078,7 +1078,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1088,12 +1088,12 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>69.010.400-8</t>
+          <t>72.223.100-7</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PICA</t>
+          <t>GOBIERNO REGIONAL DE TARAPACA</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1118,13 +1118,13 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>2929.4</v>
+        <v>1407.77</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>1070620-29585-CM25</t>
+          <t>696217-149-CM25</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1139,22 +1139,22 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>62.000.530-4</t>
+          <t>61.935.400-1</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>HOSPITAL DOCTOR ERNESTO TORRES GALDAMES</t>
+          <t>MINISTERIO PUBLICO</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1179,13 +1179,13 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>1180.11</v>
+        <v>1474.82</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>845-201-CM25</t>
+          <t>1079967-659-CM25</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1200,7 +1200,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1210,12 +1210,12 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>70.072.600-2</t>
+          <t>60.505.102-2</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
+          <t>SECCIÓN COMPRAS I ZONA</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1225,12 +1225,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>BARDANE SPA</t>
+          <t>MUÑOZ Y VILCHES LIMITADA</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>77.205.722-9</t>
+          <t>77.008.207-2</t>
         </is>
       </c>
       <c r="K13" t="inlineStr"/>
@@ -1240,13 +1240,13 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>1140.71</v>
+        <v>21873.24</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>845-200-CM25</t>
+          <t>908366-104-CM25</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1261,7 +1261,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1271,12 +1271,12 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>70.072.600-2</t>
+          <t>69.010.400-8</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
+          <t>I MUNICIPALIDAD DE PICA</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1286,12 +1286,12 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>BARDANE SPA</t>
+          <t>DISTRIBUIDORA NENE SPA</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>77.205.722-9</t>
+          <t>76.067.436-2</t>
         </is>
       </c>
       <c r="K14" t="inlineStr"/>
@@ -1301,13 +1301,13 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>1459.6</v>
+        <v>2929.4</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>1350296-2536-CM25</t>
+          <t>1070620-29585-CM25</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1317,12 +1317,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1332,12 +1332,12 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>65.228.694-1</t>
+          <t>62.000.530-4</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>HOSPITAL DE ALTO HOSPICIO</t>
+          <t>HOSPITAL DOCTOR ERNESTO TORRES GALDAMES</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1362,13 +1362,13 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>2964.46</v>
+        <v>1180.11</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>5651-2194-CM25</t>
+          <t>845-200-CM25</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1378,12 +1378,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1393,12 +1393,12 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>61.313.000-4</t>
+          <t>70.072.600-2</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>CORP NACIONAL FORESTAL</t>
+          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1408,12 +1408,12 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA NENE SPA</t>
+          <t>BARDANE SPA</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>76.067.436-2</t>
+          <t>77.205.722-9</t>
         </is>
       </c>
       <c r="K16" t="inlineStr"/>
@@ -1423,13 +1423,13 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>934.96</v>
+        <v>1459.6</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>5663-52-CM25</t>
+          <t>845-201-CM25</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1439,12 +1439,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025-12-11</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>70.072.600-2</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA NENE SPA</t>
+          <t>BARDANE SPA</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>76.067.436-2</t>
+          <t>77.205.722-9</t>
         </is>
       </c>
       <c r="K17" t="inlineStr"/>
@@ -1484,13 +1484,13 @@
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>757.83</v>
+        <v>1140.71</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>845-220-CM25</t>
+          <t>1350296-2536-CM25</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1505,7 +1505,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025-12-17</t>
+          <t>2025-12-09</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1515,12 +1515,12 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>70.072.600-2</t>
+          <t>65.228.694-1</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
+          <t>HOSPITAL DE ALTO HOSPICIO</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1545,13 +1545,13 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>11162.18</v>
+        <v>2964.46</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>845-222-CM25</t>
+          <t>5651-2194-CM25</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1566,7 +1566,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025-12-17</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1576,12 +1576,12 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>70.072.600-2</t>
+          <t>61.313.000-4</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
+          <t>CORP NACIONAL FORESTAL</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1606,13 +1606,13 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>2009.47</v>
+        <v>934.96</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>3145-686-CM25</t>
+          <t>5663-52-CM25</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1627,22 +1627,22 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025-12-17</t>
+          <t>2025-12-11</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>61.103.023-1</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Iª Brigada Aérea</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1667,13 +1667,13 @@
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>4420.53</v>
+        <v>757.83</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>548847-88-CM25</t>
+          <t>845-222-CM25</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1693,17 +1693,17 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>61.979.440-0</t>
+          <t>70.072.600-2</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Instituto de Prevision Social</t>
+          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1713,12 +1713,12 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE LIMITADA</t>
+          <t>DISTRIBUIDORA NENE SPA</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>77.012.870-6</t>
+          <t>76.067.436-2</t>
         </is>
       </c>
       <c r="K21" t="inlineStr"/>
@@ -1728,13 +1728,13 @@
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>1368.37</v>
+        <v>2009.47</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>802-80-CM25</t>
+          <t>3145-686-CM25</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1749,22 +1749,22 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025-12-18</t>
+          <t>2025-12-17</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>72.396.000-2</t>
+          <t>61.103.023-1</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>CORP NACIONAL DE DESARROLLO INDIGENA</t>
+          <t>Iª Brigada Aérea</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1789,13 +1789,13 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>2109.88</v>
+        <v>4420.53</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>1355-60-CM25</t>
+          <t>548847-88-CM25</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1810,22 +1810,22 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-12-17</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>61.002.007-0</t>
+          <t>61.979.440-0</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Servicio de Registro Civil e Identificación</t>
+          <t>Instituto de Prevision Social</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1835,12 +1835,12 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>SOCIEDAD SOLUCIONES INTEGRALES SPA</t>
+          <t>COMERCIAL RED OFFICE LIMITADA</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>76.540.457-6</t>
+          <t>77.012.870-6</t>
         </is>
       </c>
       <c r="K23" t="inlineStr"/>
@@ -1850,13 +1850,13 @@
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>4476.72</v>
+        <v>1368.37</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>951-1855-CM25</t>
+          <t>845-220-CM25</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1871,7 +1871,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2025-12-23</t>
+          <t>2025-12-17</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1881,12 +1881,12 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>60.511.010-K</t>
+          <t>70.072.600-2</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>DELEGACIÓN PRESIDENCIAL REGIONAL DE TARAPACÁ</t>
+          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -1911,13 +1911,13 @@
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>1898.47</v>
+        <v>11162.18</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>1486-88-CM25</t>
+          <t>802-80-CM25</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2025-12-18</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>60.902.013-K</t>
+          <t>72.396.000-2</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Departamento Provincial de Educación Iquique</t>
+          <t>CORP NACIONAL DE DESARROLLO INDIGENA</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -1972,13 +1972,13 @@
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>981.23</v>
+        <v>2109.88</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>951-1858-CM25</t>
+          <t>1355-60-CM25</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1993,7 +1993,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2025-12-30</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -2003,12 +2003,12 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>60.511.010-K</t>
+          <t>61.002.007-0</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>DELEGACIÓN PRESIDENCIAL REGIONAL DE TARAPACÁ</t>
+          <t>Servicio de Registro Civil e Identificación</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -2018,12 +2018,12 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA NENE SPA</t>
+          <t>SOCIEDAD SOLUCIONES INTEGRALES SPA</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>76.067.436-2</t>
+          <t>76.540.457-6</t>
         </is>
       </c>
       <c r="K26" t="inlineStr"/>
@@ -2033,13 +2033,13 @@
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>2412.38</v>
+        <v>4476.72</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>1350296-22-CM26</t>
+          <t>951-1855-CM25</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2049,12 +2049,12 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026-01-08</t>
+          <t>2025-12-23</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -2064,12 +2064,12 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>65.228.694-1</t>
+          <t>60.511.010-K</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>HOSPITAL DE ALTO HOSPICIO</t>
+          <t>DELEGACIÓN PRESIDENCIAL REGIONAL DE TARAPACÁ</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -2079,12 +2079,12 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>DISTRIBUIDORA NENE SPA</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>76.067.436-2</t>
         </is>
       </c>
       <c r="K27" t="inlineStr"/>
@@ -2094,13 +2094,13 @@
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>6508.96</v>
+        <v>1898.47</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>1350296-21-CM26</t>
+          <t>1486-88-CM25</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2110,12 +2110,12 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026-01-08</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -2125,12 +2125,12 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>65.228.694-1</t>
+          <t>60.902.013-K</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>HOSPITAL DE ALTO HOSPICIO</t>
+          <t>Departamento Provincial de Educación Iquique</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>DISTRIBUIDORA NENE SPA</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>76.067.436-2</t>
         </is>
       </c>
       <c r="K28" t="inlineStr"/>
@@ -2155,13 +2155,13 @@
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>2007.61</v>
+        <v>981.23</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>1070620-157-CM26</t>
+          <t>951-1858-CM25</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026-01-09</t>
+          <t>2025-12-30</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -2186,12 +2186,12 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>62.000.530-4</t>
+          <t>60.511.010-K</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>HOSPITAL DOCTOR ERNESTO TORRES GALDAMES</t>
+          <t>DELEGACIÓN PRESIDENCIAL REGIONAL DE TARAPACÁ</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -2216,13 +2216,13 @@
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>4563.81</v>
+        <v>2412.38</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>1070620-209-CM26</t>
+          <t>1350296-22-CM26</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2237,7 +2237,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026-01-09</t>
+          <t>2026-01-08</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -2247,12 +2247,12 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>62.000.530-4</t>
+          <t>65.228.694-1</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>HOSPITAL DOCTOR ERNESTO TORRES GALDAMES</t>
+          <t>HOSPITAL DE ALTO HOSPICIO</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -2262,12 +2262,12 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA NENE SPA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>76.067.436-2</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K30" t="inlineStr"/>
@@ -2277,13 +2277,13 @@
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>845.36</v>
+        <v>6508.96</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>1070620-732-CM26</t>
+          <t>1350296-21-CM26</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2298,7 +2298,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026-01-20</t>
+          <t>2026-01-08</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -2308,12 +2308,12 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>62.000.530-4</t>
+          <t>65.228.694-1</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>HOSPITAL DOCTOR ERNESTO TORRES GALDAMES</t>
+          <t>HOSPITAL DE ALTO HOSPICIO</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -2323,12 +2323,12 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA NENE SPA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>76.067.436-2</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K31" t="inlineStr"/>
@@ -2338,13 +2338,13 @@
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>7767.17</v>
+        <v>2007.61</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2174-2-CM26</t>
+          <t>1070620-157-CM26</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2359,7 +2359,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026-01-20</t>
+          <t>2026-01-09</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -2369,12 +2369,12 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>60.301.001-9</t>
+          <t>62.000.530-4</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
+          <t>HOSPITAL DOCTOR ERNESTO TORRES GALDAMES</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -2384,12 +2384,12 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>DISTRIBUIDORA NENE SPA</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>76.067.436-2</t>
         </is>
       </c>
       <c r="K32" t="inlineStr"/>
@@ -2399,13 +2399,13 @@
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>9561.139999999999</v>
+        <v>4563.81</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>1227-10-CM26</t>
+          <t>1070620-209-CM26</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2420,7 +2420,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026-01-20</t>
+          <t>2026-01-09</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -2430,12 +2430,12 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>60.804.002-1</t>
+          <t>62.000.530-4</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>DIRECCIÓN REGIONAL ADUANA DE IQUIQUE</t>
+          <t>HOSPITAL DOCTOR ERNESTO TORRES GALDAMES</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -2460,13 +2460,13 @@
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>1782.34</v>
+        <v>845.36</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>1091793-13-CM26</t>
+          <t>1070620-732-CM26</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2491,12 +2491,12 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>62.000.710-2</t>
+          <t>62.000.530-4</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>INSTITUTO NACIONAL DE DESARROLLO SUSTENTABLE DE LA</t>
+          <t>HOSPITAL DOCTOR ERNESTO TORRES GALDAMES</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -2506,12 +2506,12 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>DISTRIBUIDORA NENE SPA</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>76.067.436-2</t>
         </is>
       </c>
       <c r="K34" t="inlineStr"/>
@@ -2521,13 +2521,13 @@
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>1169.1</v>
+        <v>7767.17</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>1426397-13-CM26</t>
+          <t>2174-2-CM26</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2542,7 +2542,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026-01-29</t>
+          <t>2026-01-20</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -2552,12 +2552,12 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>61.980.910-6</t>
+          <t>60.301.001-9</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Servicio Local de Educación Pública Iquique</t>
+          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -2567,12 +2567,12 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE LIMITADA</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>77.012.870-6</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K35" t="inlineStr"/>
@@ -2582,13 +2582,13 @@
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>2563.32</v>
+        <v>9561.139999999999</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>1426397-14-CM26</t>
+          <t>1227-10-CM26</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2603,7 +2603,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026-01-29</t>
+          <t>2026-01-20</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -2613,12 +2613,12 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>61.980.910-6</t>
+          <t>60.804.002-1</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Servicio Local de Educación Pública Iquique</t>
+          <t>DIRECCIÓN REGIONAL ADUANA DE IQUIQUE</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -2628,12 +2628,12 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>BARDANE SPA</t>
+          <t>DISTRIBUIDORA NENE SPA</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>77.205.722-9</t>
+          <t>76.067.436-2</t>
         </is>
       </c>
       <c r="K36" t="inlineStr"/>
@@ -2643,13 +2643,13 @@
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>2066.95</v>
+        <v>1782.34</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>838102-17-CM26</t>
+          <t>1091793-13-CM26</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2659,12 +2659,12 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-01-20</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -2674,12 +2674,12 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>73.923.800-5</t>
+          <t>62.000.710-2</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Zona Bienestar "Iquique" Bienestar Social</t>
+          <t>INSTITUTO NACIONAL DE DESARROLLO SUSTENTABLE DE LA</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -2689,12 +2689,12 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA NENE SPA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>76.067.436-2</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K37" t="inlineStr"/>
@@ -2704,13 +2704,13 @@
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>909.05</v>
+        <v>1169.1</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>1057448-20-CM26</t>
+          <t>1426397-13-CM26</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2720,12 +2720,12 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-01-29</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -2735,12 +2735,12 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>61.606.100-3</t>
+          <t>61.980.910-6</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD IQUIQUE</t>
+          <t>Servicio Local de Educación Pública Iquique</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA NENE SPA</t>
+          <t>COMERCIAL RED OFFICE LIMITADA</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>76.067.436-2</t>
+          <t>77.012.870-6</t>
         </is>
       </c>
       <c r="K38" t="inlineStr"/>
@@ -2765,13 +2765,13 @@
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>5553.82</v>
+        <v>2563.32</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>838102-20-CM26</t>
+          <t>1426397-14-CM26</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2781,12 +2781,12 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-01-29</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -2796,12 +2796,12 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>73.923.800-5</t>
+          <t>61.980.910-6</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Zona Bienestar "Iquique" Bienestar Social</t>
+          <t>Servicio Local de Educación Pública Iquique</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -2811,12 +2811,12 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>BARDANE SPA</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>77.205.722-9</t>
         </is>
       </c>
       <c r="K39" t="inlineStr"/>
@@ -2826,13 +2826,13 @@
         </is>
       </c>
       <c r="M39" s="2" t="n">
-        <v>860.51</v>
+        <v>2066.95</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>1346281-35-CM26</t>
+          <t>838102-17-CM26</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2847,22 +2847,22 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>62.000.970-9</t>
+          <t>73.923.800-5</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
+          <t>Zona Bienestar "Iquique" Bienestar Social</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -2887,13 +2887,13 @@
         </is>
       </c>
       <c r="M40" s="2" t="n">
-        <v>1298.1</v>
+        <v>909.05</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>3170-16-CM26</t>
+          <t>1057448-20-CM26</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2908,7 +2908,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -2918,12 +2918,12 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>61.941.300-8</t>
+          <t>61.606.100-3</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>CENTRO DE ABASTECIMIENTO (I)</t>
+          <t>SERVICIO DE SALUD IQUIQUE</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -2933,12 +2933,12 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA IGESCOM SPA</t>
+          <t>DISTRIBUIDORA NENE SPA</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>77.152.668-3</t>
+          <t>76.067.436-2</t>
         </is>
       </c>
       <c r="K41" t="inlineStr"/>
@@ -2948,13 +2948,13 @@
         </is>
       </c>
       <c r="M41" s="2" t="n">
-        <v>1529.2</v>
+        <v>5553.82</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>1227-32-CM26</t>
+          <t>838102-20-CM26</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2969,7 +2969,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026-02-10</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -2979,12 +2979,12 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>60.804.002-1</t>
+          <t>73.923.800-5</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>DIRECCIÓN REGIONAL ADUANA DE IQUIQUE</t>
+          <t>Zona Bienestar "Iquique" Bienestar Social</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -2994,12 +2994,12 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA NENE SPA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>76.067.436-2</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K42" t="inlineStr"/>
@@ -3009,13 +3009,13 @@
         </is>
       </c>
       <c r="M42" s="2" t="n">
-        <v>1505.59</v>
+        <v>860.51</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>1070620-1585-CM26</t>
+          <t>1346281-35-CM26</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3030,22 +3030,22 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>62.000.530-4</t>
+          <t>62.000.970-9</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>HOSPITAL DOCTOR ERNESTO TORRES GALDAMES</t>
+          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -3070,13 +3070,13 @@
         </is>
       </c>
       <c r="M43" s="2" t="n">
-        <v>5670.13</v>
+        <v>1298.1</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>707412-14-CM26</t>
+          <t>3170-16-CM26</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3091,7 +3091,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026-02-16</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -3101,12 +3101,12 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>61.941.300-8</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>CENTRO DE ABASTECIMIENTO (I)</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -3116,12 +3116,12 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>MALMO S.A.</t>
+          <t>COMERCIALIZADORA IGESCOM SPA</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>76.195.558-6</t>
+          <t>77.152.668-3</t>
         </is>
       </c>
       <c r="K44" t="inlineStr"/>
@@ -3131,13 +3131,13 @@
         </is>
       </c>
       <c r="M44" s="2" t="n">
-        <v>1195.08</v>
+        <v>1529.2</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>907562-10-CM26</t>
+          <t>1227-32-CM26</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3152,7 +3152,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2026-02-17</t>
+          <t>2026-02-10</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -3162,12 +3162,12 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>69.010.400-8</t>
+          <t>60.804.002-1</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PICA</t>
+          <t>DIRECCIÓN REGIONAL ADUANA DE IQUIQUE</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -3192,13 +3192,13 @@
         </is>
       </c>
       <c r="M45" s="2" t="n">
-        <v>2640.16</v>
+        <v>1505.59</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2013-209-CM26</t>
+          <t>1070620-1585-CM26</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3213,22 +3213,22 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>70.777.500-9</t>
+          <t>62.000.530-4</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD ARTURO PRAT</t>
+          <t>HOSPITAL DOCTOR ERNESTO TORRES GALDAMES</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -3238,12 +3238,12 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE LIMITADA</t>
+          <t>DISTRIBUIDORA NENE SPA</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>77.012.870-6</t>
+          <t>76.067.436-2</t>
         </is>
       </c>
       <c r="K46" t="inlineStr"/>
@@ -3253,13 +3253,13 @@
         </is>
       </c>
       <c r="M46" s="2" t="n">
-        <v>9555.74</v>
+        <v>5670.13</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>1350296-324-CM26</t>
+          <t>707412-14-CM26</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3274,7 +3274,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-16</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -3284,12 +3284,12 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>65.228.694-1</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>HOSPITAL DE ALTO HOSPICIO</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -3299,12 +3299,12 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>MALMO S.A.</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>76.195.558-6</t>
         </is>
       </c>
       <c r="K47" t="inlineStr"/>
@@ -3314,13 +3314,13 @@
         </is>
       </c>
       <c r="M47" s="2" t="n">
-        <v>5200.79</v>
+        <v>1195.08</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>618472-2-CM26</t>
+          <t>907562-10-CM26</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -3335,7 +3335,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-17</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -3345,12 +3345,12 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>61.979.990-9</t>
+          <t>69.010.400-8</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>I MUNICIPALIDAD DE PICA</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -3375,13 +3375,13 @@
         </is>
       </c>
       <c r="M48" s="2" t="n">
-        <v>1833.71</v>
+        <v>2640.16</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>1347772-17-CM26</t>
+          <t>2013-209-CM26</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -3391,27 +3391,27 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>62.000.890-7</t>
+          <t>70.777.500-9</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PROTECCIÓN ESPECIALIZADA A LA</t>
+          <t>UNIVERSIDAD ARTURO PRAT</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -3421,12 +3421,12 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA NENE SPA</t>
+          <t>COMERCIAL RED OFFICE LIMITADA</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>76.067.436-2</t>
+          <t>77.012.870-6</t>
         </is>
       </c>
       <c r="K49" t="inlineStr"/>
@@ -3436,13 +3436,13 @@
         </is>
       </c>
       <c r="M49" s="2" t="n">
-        <v>1756.44</v>
+        <v>9555.74</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>1070620-2309-CM26</t>
+          <t>1350296-324-CM26</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -3452,12 +3452,12 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -3467,12 +3467,12 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>62.000.530-4</t>
+          <t>65.228.694-1</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>HOSPITAL DOCTOR ERNESTO TORRES GALDAMES</t>
+          <t>HOSPITAL DE ALTO HOSPICIO</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -3482,12 +3482,12 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA NENE SPA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>76.067.436-2</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K50" t="inlineStr"/>
@@ -3497,13 +3497,13 @@
         </is>
       </c>
       <c r="M50" s="2" t="n">
-        <v>1074.71</v>
+        <v>5200.79</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>707412-18-CM26</t>
+          <t>618472-2-CM26</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -3513,12 +3513,12 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>61.979.990-9</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>Ejercito de Chile</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -3543,12 +3543,12 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>DISTRIBUIDORA NENE SPA</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>76.067.436-2</t>
         </is>
       </c>
       <c r="K51" t="inlineStr"/>
@@ -3558,13 +3558,13 @@
         </is>
       </c>
       <c r="M51" s="2" t="n">
-        <v>876.25</v>
+        <v>1833.71</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2013-259-CM26</t>
+          <t>1347772-17-CM26</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -3579,22 +3579,22 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>70.777.500-9</t>
+          <t>62.000.890-7</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD ARTURO PRAT</t>
+          <t>SERVICIO NACIONAL DE PROTECCIÓN ESPECIALIZADA A LA</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -3604,12 +3604,12 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE LIMITADA</t>
+          <t>DISTRIBUIDORA NENE SPA</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>77.012.870-6</t>
+          <t>76.067.436-2</t>
         </is>
       </c>
       <c r="K52" t="inlineStr"/>
@@ -3619,13 +3619,13 @@
         </is>
       </c>
       <c r="M52" s="2" t="n">
-        <v>2066.21</v>
+        <v>1756.44</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>1407-118-CM26</t>
+          <t>1070620-2309-CM26</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -3640,7 +3640,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -3650,12 +3650,12 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>61.004.002-0</t>
+          <t>62.000.530-4</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Iquique</t>
+          <t>HOSPITAL DOCTOR ERNESTO TORRES GALDAMES</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -3665,12 +3665,12 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>DISTRIBUIDORA NENE SPA</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>76.067.436-2</t>
         </is>
       </c>
       <c r="K53" t="inlineStr"/>
@@ -3680,13 +3680,13 @@
         </is>
       </c>
       <c r="M53" s="2" t="n">
-        <v>1139.89</v>
+        <v>1074.71</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>1070620-2522-CM26</t>
+          <t>707412-18-CM26</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -3701,7 +3701,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -3711,12 +3711,12 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>62.000.530-4</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>HOSPITAL DOCTOR ERNESTO TORRES GALDAMES</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -3726,12 +3726,12 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA NENE SPA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>76.067.436-2</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K54" t="inlineStr"/>
@@ -3741,13 +3741,13 @@
         </is>
       </c>
       <c r="M54" s="2" t="n">
-        <v>1588.97</v>
+        <v>876.25</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>3352-37-CM26</t>
+          <t>2013-259-CM26</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -3762,22 +3762,22 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>61.101.024-9</t>
+          <t>70.777.500-9</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>EJERCITO DE CHILE ESCUELA CABALLERIA QUI</t>
+          <t>UNIVERSIDAD ARTURO PRAT</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -3787,12 +3787,12 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>COMERCIAL RED OFFICE LIMITADA</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>77.012.870-6</t>
         </is>
       </c>
       <c r="K55" t="inlineStr"/>
@@ -3802,13 +3802,13 @@
         </is>
       </c>
       <c r="M55" s="2" t="n">
-        <v>2277.41</v>
+        <v>2066.21</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>3349-62-CM26</t>
+          <t>1407-118-CM26</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -3823,7 +3823,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -3833,12 +3833,12 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>65.283.230-K</t>
+          <t>61.004.002-0</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>Dirección Regional de Gendarmeria - Iquique</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -3848,12 +3848,12 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA NENE SPA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>76.067.436-2</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K56" t="inlineStr"/>
@@ -3863,13 +3863,13 @@
         </is>
       </c>
       <c r="M56" s="2" t="n">
-        <v>7570.95</v>
+        <v>1139.89</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>1070620-2949-CM26</t>
+          <t>1070620-2522-CM26</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -3884,7 +3884,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -3924,13 +3924,13 @@
         </is>
       </c>
       <c r="M57" s="2" t="n">
-        <v>2206.95</v>
+        <v>1588.97</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>1346281-48-CM26</t>
+          <t>3352-37-CM26</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -3945,7 +3945,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -3955,12 +3955,12 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>62.000.970-9</t>
+          <t>61.101.024-9</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
+          <t>EJERCITO DE CHILE ESCUELA CABALLERIA QUI</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -3985,13 +3985,13 @@
         </is>
       </c>
       <c r="M58" s="2" t="n">
-        <v>859.85</v>
+        <v>2277.41</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>3352-49-CM26</t>
+          <t>3349-62-CM26</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4006,7 +4006,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -4016,12 +4016,12 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>61.101.024-9</t>
+          <t>65.283.230-K</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>EJERCITO DE CHILE ESCUELA CABALLERIA QUI</t>
+          <t>Ejercito de Chile</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -4031,12 +4031,12 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>MALMO S.A.</t>
+          <t>DISTRIBUIDORA NENE SPA</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>76.195.558-6</t>
+          <t>76.067.436-2</t>
         </is>
       </c>
       <c r="K59" t="inlineStr"/>
@@ -4046,13 +4046,13 @@
         </is>
       </c>
       <c r="M59" s="2" t="n">
-        <v>1475.02</v>
+        <v>7570.95</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>1346281-50-CM26</t>
+          <t>1070620-2949-CM26</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -4067,7 +4067,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -4077,12 +4077,12 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>62.000.970-9</t>
+          <t>62.000.530-4</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
+          <t>HOSPITAL DOCTOR ERNESTO TORRES GALDAMES</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -4107,13 +4107,13 @@
         </is>
       </c>
       <c r="M60" s="2" t="n">
-        <v>753.52</v>
+        <v>2206.95</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>1079967-130-CM26</t>
+          <t>1346281-48-CM26</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -4138,12 +4138,12 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>60.505.102-2</t>
+          <t>62.000.970-9</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS I ZONA</t>
+          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -4153,12 +4153,12 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>MALMO S.A.</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>76.195.558-6</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K61" t="inlineStr"/>
@@ -4168,13 +4168,13 @@
         </is>
       </c>
       <c r="M61" s="2" t="n">
-        <v>31748.88</v>
+        <v>859.85</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>5126-29-CM26</t>
+          <t>3352-49-CM26</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -4184,12 +4184,12 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -4199,12 +4199,12 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>61.979.650-0</t>
+          <t>61.101.024-9</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Estado Mayor Conjunto</t>
+          <t>EJERCITO DE CHILE ESCUELA CABALLERIA QUI</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -4214,12 +4214,12 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>MALMO S.A.</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>76.195.558-6</t>
         </is>
       </c>
       <c r="K62" t="inlineStr"/>
@@ -4229,13 +4229,13 @@
         </is>
       </c>
       <c r="M62" s="2" t="n">
-        <v>2810.41</v>
+        <v>1475.02</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>1070620-3123-CM26</t>
+          <t>1346281-50-CM26</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -4245,12 +4245,12 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -4260,12 +4260,12 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>62.000.530-4</t>
+          <t>62.000.970-9</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>HOSPITAL DOCTOR ERNESTO TORRES GALDAMES</t>
+          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -4275,12 +4275,12 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>IMPORTADORA HEVIA SPA</t>
+          <t>DISTRIBUIDORA NENE SPA</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>76.872.717-1</t>
+          <t>76.067.436-2</t>
         </is>
       </c>
       <c r="K63" t="inlineStr"/>
@@ -4290,13 +4290,13 @@
         </is>
       </c>
       <c r="M63" s="2" t="n">
-        <v>983.75</v>
+        <v>753.52</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>1070620-3155-CM26</t>
+          <t>1079967-130-CM26</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -4306,12 +4306,12 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -4321,12 +4321,12 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>62.000.530-4</t>
+          <t>60.505.102-2</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>HOSPITAL DOCTOR ERNESTO TORRES GALDAMES</t>
+          <t>SECCIÓN COMPRAS I ZONA</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -4336,12 +4336,12 @@
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA NENE SPA</t>
+          <t>MALMO S.A.</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>76.067.436-2</t>
+          <t>76.195.558-6</t>
         </is>
       </c>
       <c r="K64" t="inlineStr"/>
@@ -4351,13 +4351,13 @@
         </is>
       </c>
       <c r="M64" s="2" t="n">
-        <v>775.48</v>
+        <v>31748.88</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>548847-11-CM26</t>
+          <t>5126-29-CM26</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -4372,7 +4372,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -4382,12 +4382,12 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>61.979.440-0</t>
+          <t>61.979.650-0</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Instituto de Prevision Social</t>
+          <t>Estado Mayor Conjunto</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -4397,12 +4397,12 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA NENE SPA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>76.067.436-2</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K65" t="inlineStr"/>
@@ -4412,13 +4412,13 @@
         </is>
       </c>
       <c r="M65" s="2" t="n">
-        <v>1961.27</v>
+        <v>2810.41</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>1312459-14-CM26</t>
+          <t>1070620-3123-CM26</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -4433,7 +4433,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -4443,12 +4443,12 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>65.039.239-6</t>
+          <t>62.000.530-4</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>CORPORACION MUNICIPAL DE DEPORTES DE IQUIQUE</t>
+          <t>HOSPITAL DOCTOR ERNESTO TORRES GALDAMES</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -4458,12 +4458,12 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA NENE SPA</t>
+          <t>IMPORTADORA HEVIA SPA</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>76.067.436-2</t>
+          <t>76.872.717-1</t>
         </is>
       </c>
       <c r="K66" t="inlineStr"/>
@@ -4473,13 +4473,13 @@
         </is>
       </c>
       <c r="M66" s="2" t="n">
-        <v>2737.42</v>
+        <v>983.75</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>1312459-13-CM26</t>
+          <t>1070620-3155-CM26</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -4494,7 +4494,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -4504,12 +4504,12 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>65.039.239-6</t>
+          <t>62.000.530-4</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>CORPORACION MUNICIPAL DE DEPORTES DE IQUIQUE</t>
+          <t>HOSPITAL DOCTOR ERNESTO TORRES GALDAMES</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -4534,13 +4534,13 @@
         </is>
       </c>
       <c r="M67" s="2" t="n">
-        <v>883.89</v>
+        <v>775.48</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>3352-48-CM26</t>
+          <t>548847-11-CM26</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -4555,7 +4555,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -4565,12 +4565,12 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>61.101.024-9</t>
+          <t>61.979.440-0</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>EJERCITO DE CHILE ESCUELA CABALLERIA QUI</t>
+          <t>Instituto de Prevision Social</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -4580,12 +4580,12 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>OTTO HAN SPA</t>
+          <t>DISTRIBUIDORA NENE SPA</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>77.809.872-5</t>
+          <t>76.067.436-2</t>
         </is>
       </c>
       <c r="K68" t="inlineStr"/>
@@ -4595,13 +4595,13 @@
         </is>
       </c>
       <c r="M68" s="2" t="n">
-        <v>1068.43</v>
+        <v>1961.27</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>696217-29-CM26</t>
+          <t>1312459-13-CM26</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -4616,22 +4616,22 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>61.935.400-1</t>
+          <t>65.039.239-6</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>MINISTERIO PUBLICO</t>
+          <t>CORPORACION MUNICIPAL DE DEPORTES DE IQUIQUE</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -4656,13 +4656,13 @@
         </is>
       </c>
       <c r="M69" s="2" t="n">
-        <v>1043.09</v>
+        <v>883.89</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>1070620-3444-CM26</t>
+          <t>1312459-14-CM26</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -4677,7 +4677,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -4687,12 +4687,12 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>62.000.530-4</t>
+          <t>65.039.239-6</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>HOSPITAL DOCTOR ERNESTO TORRES GALDAMES</t>
+          <t>CORPORACION MUNICIPAL DE DEPORTES DE IQUIQUE</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -4717,13 +4717,13 @@
         </is>
       </c>
       <c r="M70" s="2" t="n">
-        <v>2170.45</v>
+        <v>2737.42</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>5690-47-CM26</t>
+          <t>3352-48-CM26</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -4738,7 +4738,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -4748,12 +4748,12 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>61.308.000-7</t>
+          <t>61.101.024-9</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>SERVICIO AGRICOLA Y GANADERO</t>
+          <t>EJERCITO DE CHILE ESCUELA CABALLERIA QUI</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -4763,12 +4763,12 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>OTTO HAN SPA</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>77.809.872-5</t>
         </is>
       </c>
       <c r="K71" t="inlineStr"/>
@@ -4778,13 +4778,13 @@
         </is>
       </c>
       <c r="M71" s="2" t="n">
-        <v>1851.11</v>
+        <v>1068.43</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>935934-87-CM26</t>
+          <t>696217-29-CM26</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -4799,22 +4799,22 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>61.980.770-7</t>
+          <t>61.935.400-1</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Zona de Bienestar Iquique</t>
+          <t>MINISTERIO PUBLICO</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -4824,12 +4824,12 @@
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>DISTRIBUIDORA NENE SPA</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>76.067.436-2</t>
         </is>
       </c>
       <c r="K72" t="inlineStr"/>
@@ -4839,13 +4839,13 @@
         </is>
       </c>
       <c r="M72" s="2" t="n">
-        <v>839.79</v>
+        <v>1043.09</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>1070620-3772-CM26</t>
+          <t>1070620-3444-CM26</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -4860,7 +4860,7 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -4900,13 +4900,13 @@
         </is>
       </c>
       <c r="M73" s="2" t="n">
-        <v>3008.51</v>
+        <v>2170.45</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>1026727-110-CM26</t>
+          <t>5690-47-CM26</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -4921,7 +4921,7 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -4931,12 +4931,12 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>65.154.398-3</t>
+          <t>61.308.000-7</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>CENTRO DE FORMACION TECNICA DE LA REGION DE TARAPACA</t>
+          <t>SERVICIO AGRICOLA Y GANADERO</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -4946,12 +4946,12 @@
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA NENE SPA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>76.067.436-2</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K74" t="inlineStr"/>
@@ -4961,13 +4961,13 @@
         </is>
       </c>
       <c r="M74" s="2" t="n">
-        <v>5730.05</v>
+        <v>1851.11</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>1070620-3965-CM26</t>
+          <t>935934-87-CM26</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -4982,7 +4982,7 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -4992,12 +4992,12 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>62.000.530-4</t>
+          <t>61.980.770-7</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>HOSPITAL DOCTOR ERNESTO TORRES GALDAMES</t>
+          <t>Zona de Bienestar Iquique</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -5007,12 +5007,12 @@
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA NENE SPA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>76.067.436-2</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K75" t="inlineStr"/>
@@ -5022,13 +5022,13 @@
         </is>
       </c>
       <c r="M75" s="2" t="n">
-        <v>2654.48</v>
+        <v>839.79</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>1070620-3970-CM26</t>
+          <t>1070620-3772-CM26</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -5043,7 +5043,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -5083,13 +5083,13 @@
         </is>
       </c>
       <c r="M76" s="2" t="n">
-        <v>2971.98</v>
+        <v>3008.51</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>696217-36-CM26</t>
+          <t>1026727-110-CM26</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -5099,27 +5099,27 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>61.935.400-1</t>
+          <t>65.154.398-3</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>MINISTERIO PUBLICO</t>
+          <t>CENTRO DE FORMACION TECNICA DE LA REGION DE TARAPACA</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -5144,13 +5144,13 @@
         </is>
       </c>
       <c r="M77" s="2" t="n">
-        <v>797.04</v>
+        <v>5730.05</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>1077499-48-CM26</t>
+          <t>1070620-3965-CM26</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -5160,12 +5160,12 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -5175,12 +5175,12 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>61.606.100-3</t>
+          <t>62.000.530-4</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD IQUIQUE</t>
+          <t>HOSPITAL DOCTOR ERNESTO TORRES GALDAMES</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -5190,12 +5190,12 @@
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE LIMITADA</t>
+          <t>DISTRIBUIDORA NENE SPA</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>77.012.870-6</t>
+          <t>76.067.436-2</t>
         </is>
       </c>
       <c r="K78" t="inlineStr"/>
@@ -5205,13 +5205,13 @@
         </is>
       </c>
       <c r="M78" s="2" t="n">
-        <v>1421.78</v>
+        <v>2654.48</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>1070620-4300-CM26</t>
+          <t>1070620-3970-CM26</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -5221,12 +5221,12 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -5266,13 +5266,13 @@
         </is>
       </c>
       <c r="M79" s="2" t="n">
-        <v>4063.54</v>
+        <v>2971.98</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>1355-15-CM26</t>
+          <t>696217-36-CM26</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -5287,22 +5287,22 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>61.002.007-0</t>
+          <t>61.935.400-1</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Servicio de Registro Civil e Identificación</t>
+          <t>MINISTERIO PUBLICO</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -5312,12 +5312,12 @@
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA SAN JERONIMO SPA</t>
+          <t>DISTRIBUIDORA NENE SPA</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>77.610.393-4</t>
+          <t>76.067.436-2</t>
         </is>
       </c>
       <c r="K80" t="inlineStr"/>
@@ -5327,13 +5327,13 @@
         </is>
       </c>
       <c r="M80" s="2" t="n">
-        <v>9123.34</v>
+        <v>797.04</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>2013-788-CM26</t>
+          <t>1077499-48-CM26</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -5348,22 +5348,22 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>70.777.500-9</t>
+          <t>61.606.100-3</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD ARTURO PRAT</t>
+          <t>SERVICIO DE SALUD IQUIQUE</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -5373,12 +5373,12 @@
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>INVERSIONES CORP PREMIER LTDA</t>
+          <t>COMERCIAL RED OFFICE LIMITADA</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>76.473.108-5</t>
+          <t>77.012.870-6</t>
         </is>
       </c>
       <c r="K81" t="inlineStr"/>
@@ -5388,13 +5388,13 @@
         </is>
       </c>
       <c r="M81" s="2" t="n">
-        <v>3448.12</v>
+        <v>1421.78</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>1426397-149-CM26</t>
+          <t>1355-15-CM26</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -5409,7 +5409,7 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -5419,12 +5419,12 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>61.980.910-6</t>
+          <t>61.002.007-0</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Servicio Local de Educación Pública Iquique</t>
+          <t>Servicio de Registro Civil e Identificación</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -5434,12 +5434,12 @@
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA NENE SPA</t>
+          <t>COMERCIALIZADORA SAN JERONIMO SPA</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>76.067.436-2</t>
+          <t>77.610.393-4</t>
         </is>
       </c>
       <c r="K82" t="inlineStr"/>
@@ -5449,13 +5449,13 @@
         </is>
       </c>
       <c r="M82" s="2" t="n">
-        <v>27867.05</v>
+        <v>9123.34</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>1070620-4588-CM26</t>
+          <t>1070620-4300-CM26</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -5470,7 +5470,7 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -5510,13 +5510,13 @@
         </is>
       </c>
       <c r="M83" s="2" t="n">
-        <v>1717.38</v>
+        <v>4063.54</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>1350296-953-CM26</t>
+          <t>1426397-149-CM26</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -5531,7 +5531,7 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -5541,12 +5541,12 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>65.228.694-1</t>
+          <t>61.980.910-6</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>HOSPITAL DE ALTO HOSPICIO</t>
+          <t>Servicio Local de Educación Pública Iquique</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -5571,13 +5571,13 @@
         </is>
       </c>
       <c r="M84" s="2" t="n">
-        <v>2900.32</v>
+        <v>27867.05</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>3349-159-CM26</t>
+          <t>2013-788-CM26</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -5592,22 +5592,22 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>65.283.230-K</t>
+          <t>70.777.500-9</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>UNIVERSIDAD ARTURO PRAT</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -5617,12 +5617,12 @@
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA NENE SPA</t>
+          <t>INVERSIONES CORP PREMIER LTDA</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>76.067.436-2</t>
+          <t>76.473.108-5</t>
         </is>
       </c>
       <c r="K85" t="inlineStr"/>
@@ -5632,13 +5632,13 @@
         </is>
       </c>
       <c r="M85" s="2" t="n">
-        <v>1338.38</v>
+        <v>3448.12</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>1070620-5112-CM26</t>
+          <t>1070620-4588-CM26</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -5648,12 +5648,12 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -5693,13 +5693,13 @@
         </is>
       </c>
       <c r="M86" s="2" t="n">
-        <v>4394.29</v>
+        <v>1717.38</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>1070620-5145-CM26</t>
+          <t>1350296-953-CM26</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -5709,12 +5709,12 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -5724,12 +5724,12 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>62.000.530-4</t>
+          <t>65.228.694-1</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>HOSPITAL DOCTOR ERNESTO TORRES GALDAMES</t>
+          <t>HOSPITAL DE ALTO HOSPICIO</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -5754,13 +5754,13 @@
         </is>
       </c>
       <c r="M87" s="2" t="n">
-        <v>806.4299999999999</v>
+        <v>2900.32</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>1350296-923-CM26</t>
+          <t>3349-159-CM26</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -5770,12 +5770,12 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -5785,12 +5785,12 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>65.228.694-1</t>
+          <t>65.283.230-K</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>HOSPITAL DE ALTO HOSPICIO</t>
+          <t>Ejercito de Chile</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
@@ -5800,12 +5800,12 @@
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA IGESCOM SPA</t>
+          <t>DISTRIBUIDORA NENE SPA</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>77.152.668-3</t>
+          <t>76.067.436-2</t>
         </is>
       </c>
       <c r="K88" t="inlineStr"/>
@@ -5815,13 +5815,13 @@
         </is>
       </c>
       <c r="M88" s="2" t="n">
-        <v>1288.94</v>
+        <v>1338.38</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>948-72-CM26</t>
+          <t>1070620-5112-CM26</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -5836,7 +5836,7 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -5846,12 +5846,12 @@
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>60.901.003-7</t>
+          <t>62.000.530-4</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Secretaría Regional Ministerial de Educación de la Primera Región</t>
+          <t>HOSPITAL DOCTOR ERNESTO TORRES GALDAMES</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -5876,13 +5876,13 @@
         </is>
       </c>
       <c r="M89" s="2" t="n">
-        <v>783.7</v>
+        <v>4394.29</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>1407-331-CM26</t>
+          <t>1070620-5145-CM26</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -5897,7 +5897,7 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
@@ -5907,12 +5907,12 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>61.004.002-0</t>
+          <t>62.000.530-4</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Iquique</t>
+          <t>HOSPITAL DOCTOR ERNESTO TORRES GALDAMES</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
@@ -5937,13 +5937,13 @@
         </is>
       </c>
       <c r="M90" s="2" t="n">
-        <v>1097.01</v>
+        <v>806.4299999999999</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>1057448-209-CM26</t>
+          <t>1350296-923-CM26</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -5958,7 +5958,7 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -5968,12 +5968,12 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>61.606.100-3</t>
+          <t>65.228.694-1</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD IQUIQUE</t>
+          <t>HOSPITAL DE ALTO HOSPICIO</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
@@ -5983,12 +5983,12 @@
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA NENE SPA</t>
+          <t>COMERCIALIZADORA IGESCOM SPA</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>76.067.436-2</t>
+          <t>77.152.668-3</t>
         </is>
       </c>
       <c r="K91" t="inlineStr"/>
@@ -5998,13 +5998,13 @@
         </is>
       </c>
       <c r="M91" s="2" t="n">
-        <v>1133.72</v>
+        <v>1288.94</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>1227-161-CM26</t>
+          <t>948-72-CM26</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -6019,7 +6019,7 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
@@ -6029,12 +6029,12 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>60.804.002-1</t>
+          <t>60.901.003-7</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>DIRECCIÓN REGIONAL ADUANA DE IQUIQUE</t>
+          <t>Secretaría Regional Ministerial de Educación de la Primera Región</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -6059,13 +6059,13 @@
         </is>
       </c>
       <c r="M92" s="2" t="n">
-        <v>833.25</v>
+        <v>783.7</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>1346281-93-CM26</t>
+          <t>1407-331-CM26</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -6080,7 +6080,7 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
@@ -6090,12 +6090,12 @@
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>62.000.970-9</t>
+          <t>61.004.002-0</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
+          <t>Dirección Regional de Gendarmeria - Iquique</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -6120,13 +6120,13 @@
         </is>
       </c>
       <c r="M93" s="2" t="n">
-        <v>818.53</v>
+        <v>1097.01</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>548847-33-CM26</t>
+          <t>1057448-209-CM26</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -6141,7 +6141,7 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
@@ -6151,12 +6151,12 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>61.979.440-0</t>
+          <t>61.606.100-3</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Instituto de Prevision Social</t>
+          <t>SERVICIO DE SALUD IQUIQUE</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
@@ -6166,12 +6166,12 @@
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>DISTRIBUIDORA NENE SPA</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>76.067.436-2</t>
         </is>
       </c>
       <c r="K94" t="inlineStr"/>
@@ -6181,13 +6181,13 @@
         </is>
       </c>
       <c r="M94" s="2" t="n">
-        <v>3171.11</v>
+        <v>1133.72</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>707412-47-CM26</t>
+          <t>1227-161-CM26</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -6202,22 +6202,22 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>60.804.002-1</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>DIRECCIÓN REGIONAL ADUANA DE IQUIQUE</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
@@ -6242,13 +6242,13 @@
         </is>
       </c>
       <c r="M95" s="2" t="n">
-        <v>8179.49</v>
+        <v>833.25</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>1070620-5843-CM26</t>
+          <t>1346281-93-CM26</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -6263,7 +6263,7 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
@@ -6273,12 +6273,12 @@
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>62.000.530-4</t>
+          <t>62.000.970-9</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>HOSPITAL DOCTOR ERNESTO TORRES GALDAMES</t>
+          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -6303,13 +6303,13 @@
         </is>
       </c>
       <c r="M96" s="2" t="n">
-        <v>4432.28</v>
+        <v>818.53</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>1350296-1137-CM26</t>
+          <t>548847-33-CM26</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -6324,7 +6324,7 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
@@ -6334,12 +6334,12 @@
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>65.228.694-1</t>
+          <t>61.979.440-0</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>HOSPITAL DE ALTO HOSPICIO</t>
+          <t>Instituto de Prevision Social</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -6349,12 +6349,12 @@
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA NENE SPA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>76.067.436-2</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K97" t="inlineStr"/>
@@ -6364,13 +6364,13 @@
         </is>
       </c>
       <c r="M97" s="2" t="n">
-        <v>1081.22</v>
+        <v>3171.11</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>1350296-1138-CM26</t>
+          <t>707412-47-CM26</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -6385,22 +6385,22 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>65.228.694-1</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>HOSPITAL DE ALTO HOSPICIO</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
@@ -6410,12 +6410,12 @@
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>DISTRIBUIDORA NENE SPA</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>76.067.436-2</t>
         </is>
       </c>
       <c r="K98" t="inlineStr"/>
@@ -6425,13 +6425,13 @@
         </is>
       </c>
       <c r="M98" s="2" t="n">
-        <v>1227.57</v>
+        <v>8179.49</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>2013-1102-CM26</t>
+          <t>1070620-5843-CM26</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -6446,22 +6446,22 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>70.777.500-9</t>
+          <t>62.000.530-4</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD ARTURO PRAT</t>
+          <t>HOSPITAL DOCTOR ERNESTO TORRES GALDAMES</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
@@ -6471,12 +6471,12 @@
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE LIMITADA</t>
+          <t>DISTRIBUIDORA NENE SPA</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>77.012.870-6</t>
+          <t>76.067.436-2</t>
         </is>
       </c>
       <c r="K99" t="inlineStr"/>
@@ -6486,13 +6486,13 @@
         </is>
       </c>
       <c r="M99" s="2" t="n">
-        <v>9813.75</v>
+        <v>4432.28</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>802-17-CM26</t>
+          <t>1350296-1137-CM26</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -6502,27 +6502,27 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>72.396.000-2</t>
+          <t>65.228.694-1</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>CORP NACIONAL DE DESARROLLO INDIGENA</t>
+          <t>HOSPITAL DE ALTO HOSPICIO</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
@@ -6547,13 +6547,13 @@
         </is>
       </c>
       <c r="M100" s="2" t="n">
-        <v>3398.37</v>
+        <v>1081.22</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>1070620-6258-CM26</t>
+          <t>1350296-1138-CM26</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -6563,12 +6563,12 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
@@ -6578,12 +6578,12 @@
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>62.000.530-4</t>
+          <t>65.228.694-1</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>HOSPITAL DOCTOR ERNESTO TORRES GALDAMES</t>
+          <t>HOSPITAL DE ALTO HOSPICIO</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
@@ -6593,12 +6593,12 @@
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE LIMITADA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>77.012.870-6</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K101" t="inlineStr"/>
@@ -6608,13 +6608,13 @@
         </is>
       </c>
       <c r="M101" s="2" t="n">
-        <v>805</v>
+        <v>1227.57</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>1346281-109-CM26</t>
+          <t>2013-1102-CM26</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -6624,27 +6624,27 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>62.000.970-9</t>
+          <t>70.777.500-9</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
+          <t>UNIVERSIDAD ARTURO PRAT</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
@@ -6654,12 +6654,12 @@
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>COMERCIAL RED OFFICE LIMITADA</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>77.012.870-6</t>
         </is>
       </c>
       <c r="K102" t="inlineStr"/>
@@ -6669,13 +6669,13 @@
         </is>
       </c>
       <c r="M102" s="2" t="n">
-        <v>1202.13</v>
+        <v>9813.75</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>5690-95-CM26</t>
+          <t>802-17-CM26</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -6690,7 +6690,7 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
@@ -6700,12 +6700,12 @@
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>61.308.000-7</t>
+          <t>72.396.000-2</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>SERVICIO AGRICOLA Y GANADERO</t>
+          <t>CORP NACIONAL DE DESARROLLO INDIGENA</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
@@ -6715,12 +6715,12 @@
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>DISTRIBUIDORA NENE SPA</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>76.067.436-2</t>
         </is>
       </c>
       <c r="K103" t="inlineStr"/>
@@ -6730,13 +6730,13 @@
         </is>
       </c>
       <c r="M103" s="2" t="n">
-        <v>968.89</v>
+        <v>3398.37</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>1350296-1197-CM26</t>
+          <t>1070620-6258-CM26</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -6751,7 +6751,7 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
@@ -6761,12 +6761,12 @@
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>65.228.694-1</t>
+          <t>62.000.530-4</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>HOSPITAL DE ALTO HOSPICIO</t>
+          <t>HOSPITAL DOCTOR ERNESTO TORRES GALDAMES</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
@@ -6776,12 +6776,12 @@
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>COMERCIAL RED OFFICE LIMITADA</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>77.012.870-6</t>
         </is>
       </c>
       <c r="K104" t="inlineStr"/>
@@ -6791,13 +6791,13 @@
         </is>
       </c>
       <c r="M104" s="2" t="n">
-        <v>1401.76</v>
+        <v>805</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>1070620-6926-CM26</t>
+          <t>1346281-109-CM26</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -6812,7 +6812,7 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
@@ -6822,12 +6822,12 @@
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>62.000.530-4</t>
+          <t>62.000.970-9</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>HOSPITAL DOCTOR ERNESTO TORRES GALDAMES</t>
+          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
@@ -6837,12 +6837,12 @@
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA NENE SPA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
         <is>
-          <t>76.067.436-2</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K105" t="inlineStr"/>
@@ -6852,13 +6852,13 @@
         </is>
       </c>
       <c r="M105" s="2" t="n">
-        <v>6337.61</v>
+        <v>1202.13</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>1350296-1342-CM26</t>
+          <t>5690-95-CM26</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -6873,22 +6873,22 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>65.228.694-1</t>
+          <t>61.308.000-7</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>HOSPITAL DE ALTO HOSPICIO</t>
+          <t>SERVICIO AGRICOLA Y GANADERO</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
@@ -6898,12 +6898,12 @@
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA NENE SPA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
         <is>
-          <t>76.067.436-2</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K106" t="inlineStr"/>
@@ -6913,13 +6913,13 @@
         </is>
       </c>
       <c r="M106" s="2" t="n">
-        <v>3290.43</v>
+        <v>968.89</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>1350296-1387-CM26</t>
+          <t>1350296-1197-CM26</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -6934,7 +6934,7 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
@@ -6959,12 +6959,12 @@
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA NENE SPA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t>76.067.436-2</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K107" t="inlineStr"/>
@@ -6974,6 +6974,189 @@
         </is>
       </c>
       <c r="M107" s="2" t="n">
+        <v>1401.76</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>1070620-6926-CM26</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>2239-16-LR24</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>62.000.530-4</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>HOSPITAL DOCTOR ERNESTO TORRES GALDAMES</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA NENE SPA</t>
+        </is>
+      </c>
+      <c r="J108" t="inlineStr">
+        <is>
+          <t>76.067.436-2</t>
+        </is>
+      </c>
+      <c r="K108" t="inlineStr"/>
+      <c r="L108" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M108" s="2" t="n">
+        <v>6337.61</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>1350296-1342-CM26</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>2239-16-LR24</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>65.228.694-1</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>HOSPITAL DE ALTO HOSPICIO</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA NENE SPA</t>
+        </is>
+      </c>
+      <c r="J109" t="inlineStr">
+        <is>
+          <t>76.067.436-2</t>
+        </is>
+      </c>
+      <c r="K109" t="inlineStr"/>
+      <c r="L109" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M109" s="2" t="n">
+        <v>3290.43</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>1350296-1387-CM26</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>2239-16-LR24</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>65.228.694-1</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>HOSPITAL DE ALTO HOSPICIO</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA NENE SPA</t>
+        </is>
+      </c>
+      <c r="J110" t="inlineStr">
+        <is>
+          <t>76.067.436-2</t>
+        </is>
+      </c>
+      <c r="K110" t="inlineStr"/>
+      <c r="L110" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M110" s="2" t="n">
         <v>2705.47</v>
       </c>
     </row>

--- a/docs/oc-regiones/articulos-de-escritorio-y-papeleria/tarapaca.xlsx
+++ b/docs/oc-regiones/articulos-de-escritorio-y-papeleria/tarapaca.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tarapacá" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Tarapacá" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M110"/>
+  <dimension ref="A1:M158"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -514,7 +514,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>1070620-15782-CM25</t>
+          <t>1350296-1414-CM25</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -524,12 +524,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>ago-2025</t>
+          <t>jul-2025</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2025-08-18</t>
+          <t>2025-07-03</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -539,12 +539,12 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>62.000.530-4</t>
+          <t>65.228.694-1</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>HOSPITAL DOCTOR ERNESTO TORRES GALDAMES</t>
+          <t>HOSPITAL DE ALTO HOSPICIO</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -554,12 +554,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA NENE SPA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>76.067.436-2</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
@@ -569,13 +569,13 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>7260.53</v>
+        <v>7088.48</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2549-36-CM25</t>
+          <t>3352-194-CM25</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -585,12 +585,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>sep-2025</t>
+          <t>jul-2025</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025-09-29</t>
+          <t>2025-07-07</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -600,12 +600,12 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>61.606.100-3</t>
+          <t>61.101.024-9</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD IQUIQUE</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -630,13 +630,13 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>1062.19</v>
+        <v>800.49</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>707412-92-CM25</t>
+          <t>3352-195-CM25</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -646,12 +646,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>oct-2025</t>
+          <t>jul-2025</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025-10-16</t>
+          <t>2025-07-08</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -661,12 +661,12 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>61.101.024-9</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -676,12 +676,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA NENE SPA</t>
+          <t>EVENTAIL SPA</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>76.067.436-2</t>
+          <t>76.710.414-6</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
@@ -691,13 +691,13 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>4633.33</v>
+        <v>2103.4</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>1346281-174-CM25</t>
+          <t>845-121-CM25</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -707,27 +707,27 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>jul-2025</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-07-10</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>62.000.970-9</t>
+          <t>70.072.600-2</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
+          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -737,12 +737,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA NENE SPA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>76.067.436-2</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>1112.1</v>
+        <v>10608.84</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>696217-138-CM25</t>
+          <t>845-122-CM25</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -768,27 +768,27 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>jul-2025</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-07-10</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>61.935.400-1</t>
+          <t>70.072.600-2</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>MINISTERIO PUBLICO</t>
+          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -798,12 +798,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA NENE SPA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>76.067.436-2</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
@@ -813,13 +813,13 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>812.79</v>
+        <v>3064</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>1079967-642-CM25</t>
+          <t>3352-212-CM25</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -829,12 +829,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>jul-2025</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-07-17</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -844,12 +844,12 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>60.505.102-2</t>
+          <t>61.101.024-9</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS I ZONA</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -859,12 +859,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>MUÑOZ Y VILCHES LIMITADA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>77.008.207-2</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
@@ -874,13 +874,13 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>5128.46</v>
+        <v>1171.08</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>1213005-338-CM25</t>
+          <t>1057448-349-CM25</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -890,27 +890,27 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>jul-2025</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-07-18</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>71.497.400-9</t>
+          <t>61.606.100-3</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>CORP MUNICIPAL DE DESARROLLO SOCIAL DE POZO ALMONTE</t>
+          <t>SERVICIO DE SALUD IQUIQUE</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -920,12 +920,12 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>SOCIEDAD DE INVERSIONES DASSEN SPA</t>
+          <t>DISTRIBUIDORA NENE SPA</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>77.537.871-9</t>
+          <t>76.067.436-2</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
@@ -935,13 +935,13 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>1146.43</v>
+        <v>10008.61</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>1070620-18352-CM25</t>
+          <t>548847-47-CM25</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -951,12 +951,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>jul-2025</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-07-23</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -966,12 +966,12 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>62.000.530-4</t>
+          <t>61.979.440-0</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>HOSPITAL DOCTOR ERNESTO TORRES GALDAMES</t>
+          <t>INSTITUTO DE PREVISION SOCIAL</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -981,12 +981,12 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA NENE SPA</t>
+          <t>MALMO S.A.</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>76.067.436-2</t>
+          <t>76.195.558-6</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
@@ -996,13 +996,13 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>3329.52</v>
+        <v>1847.4</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>1260688-275-CM25</t>
+          <t>978146-18-CM25</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1012,27 +1012,27 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>jul-2025</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-07-25</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>71.497.400-9</t>
+          <t>61.999.160-5</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>CORPORACION MUNICIPAL DE DESARROLLO SOCIAL POZO AL</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1042,12 +1042,12 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>SOCIEDAD DE INVERSIONES DASSEN SPA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>77.537.871-9</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
@@ -1057,13 +1057,13 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>5154.12</v>
+        <v>1387.47</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>768-642-CM25</t>
+          <t>2013-1142-CM25</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1073,27 +1073,27 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>ago-2025</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-08-05</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>72.223.100-7</t>
+          <t>70.777.500-9</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL DE TARAPACA</t>
+          <t>UNIVERSIDAD ARTURO PRAT</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1103,12 +1103,12 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA NENE SPA</t>
+          <t>COMERCIAL RED OFFICE LIMITADA</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>76.067.436-2</t>
+          <t>77.012.870-6</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
@@ -1118,13 +1118,13 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>1407.77</v>
+        <v>7696.6</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>696217-149-CM25</t>
+          <t>1417913-212-CM25</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1134,12 +1134,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>ago-2025</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-08-05</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1149,12 +1149,12 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>61.935.400-1</t>
+          <t>70.938.800-2</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>MINISTERIO PUBLICO</t>
+          <t>CORP MUNICIPAL DE DESARROLLO SOCIAL DE IQUIQUE</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1164,12 +1164,12 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA NENE SPA</t>
+          <t>COMERCIALIZADORA IGESCOM SPA</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>76.067.436-2</t>
+          <t>77.152.668-3</t>
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
@@ -1179,13 +1179,13 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>1474.82</v>
+        <v>1102.98</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>1079967-659-CM25</t>
+          <t>707412-69-CM25</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1195,27 +1195,27 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>ago-2025</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-08-07</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>60.505.102-2</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS I ZONA</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1225,12 +1225,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>MUÑOZ Y VILCHES LIMITADA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>77.008.207-2</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K13" t="inlineStr"/>
@@ -1240,13 +1240,13 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>21873.24</v>
+        <v>2658.58</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>908366-104-CM25</t>
+          <t>3352-227-CM25</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1256,12 +1256,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>ago-2025</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-08-11</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1271,12 +1271,12 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>69.010.400-8</t>
+          <t>61.101.024-9</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PICA</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1286,12 +1286,12 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA NENE SPA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>76.067.436-2</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K14" t="inlineStr"/>
@@ -1301,13 +1301,13 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>2929.4</v>
+        <v>902.36</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>1070620-29585-CM25</t>
+          <t>1355-27-CM25</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1317,12 +1317,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>ago-2025</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-08-14</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1332,12 +1332,12 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>62.000.530-4</t>
+          <t>61.002.007-0</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>HOSPITAL DOCTOR ERNESTO TORRES GALDAMES</t>
+          <t>SERVICIO DE REGISTRO CIVIL E IDENTIFICACION</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA NENE SPA</t>
+          <t>SOCIEDAD SOLUCIONES INTEGRALES SPA</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>76.067.436-2</t>
+          <t>76.540.457-6</t>
         </is>
       </c>
       <c r="K15" t="inlineStr"/>
@@ -1362,13 +1362,13 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>1180.11</v>
+        <v>4447.02</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>845-200-CM25</t>
+          <t>1070620-15782-CM25</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1378,12 +1378,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>ago-2025</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-08-18</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1393,12 +1393,12 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>70.072.600-2</t>
+          <t>62.000.530-4</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
+          <t>HOSPITAL DOCTOR ERNESTO TORRES GALDAMES</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1408,12 +1408,12 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>BARDANE SPA</t>
+          <t>DISTRIBUIDORA NENE SPA</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>77.205.722-9</t>
+          <t>76.067.436-2</t>
         </is>
       </c>
       <c r="K16" t="inlineStr"/>
@@ -1423,13 +1423,13 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>1459.6</v>
+        <v>7260.53</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>845-201-CM25</t>
+          <t>908366-69-CM25</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1439,12 +1439,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>ago-2025</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>70.072.600-2</t>
+          <t>69.010.400-8</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
+          <t>I MUNICIPALIDAD DE PICA</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>BARDANE SPA</t>
+          <t>SOCIEDAD SOLUCIONES INTEGRALES SPA</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>77.205.722-9</t>
+          <t>76.540.457-6</t>
         </is>
       </c>
       <c r="K17" t="inlineStr"/>
@@ -1484,13 +1484,13 @@
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>1140.71</v>
+        <v>2964.29</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>1350296-2536-CM25</t>
+          <t>3447-2566-CM25</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>ago-2025</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2025-08-25</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1515,12 +1515,12 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>65.228.694-1</t>
+          <t>69.265.100-6</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>HOSPITAL DE ALTO HOSPICIO</t>
+          <t>MUNICIPALIDAD DE ALTO HOSPICIO</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1530,12 +1530,12 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA NENE SPA</t>
+          <t>SOCIEDAD SOLUCIONES INTEGRALES SPA</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>76.067.436-2</t>
+          <t>76.540.457-6</t>
         </is>
       </c>
       <c r="K18" t="inlineStr"/>
@@ -1545,13 +1545,13 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>2964.46</v>
+        <v>803.1900000000001</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>5651-2194-CM25</t>
+          <t>802-52-CM25</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1561,12 +1561,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>ago-2025</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>2025-08-26</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1576,12 +1576,12 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>61.313.000-4</t>
+          <t>72.396.000-2</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>CORP NACIONAL FORESTAL</t>
+          <t>CORP NACIONAL DE DESARROLLO INDIGENA</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1591,12 +1591,12 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA NENE SPA</t>
+          <t>COMERCIAL RED OFFICE LIMITADA</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>76.067.436-2</t>
+          <t>77.012.870-6</t>
         </is>
       </c>
       <c r="K19" t="inlineStr"/>
@@ -1606,13 +1606,13 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>934.96</v>
+        <v>719.41</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>5663-52-CM25</t>
+          <t>1417913-264-CM25</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1622,27 +1622,27 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>sep-2025</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025-12-11</t>
+          <t>2025-09-02</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>70.938.800-2</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>CORP MUNICIPAL DE DESARROLLO SOCIAL DE IQUIQUE</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1667,13 +1667,13 @@
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>757.83</v>
+        <v>2016.7</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>845-222-CM25</t>
+          <t>1350296-1989-CM25</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1683,12 +1683,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>sep-2025</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025-12-17</t>
+          <t>2025-09-05</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1698,12 +1698,12 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>70.072.600-2</t>
+          <t>65.228.694-1</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
+          <t>HOSPITAL DE ALTO HOSPICIO</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1713,12 +1713,12 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA NENE SPA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>76.067.436-2</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K21" t="inlineStr"/>
@@ -1728,13 +1728,13 @@
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>2009.47</v>
+        <v>1698.77</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>3145-686-CM25</t>
+          <t>1227-163-CM25</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1744,27 +1744,27 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>sep-2025</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025-12-17</t>
+          <t>2025-09-08</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>61.103.023-1</t>
+          <t>60.804.002-1</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Iª Brigada Aérea</t>
+          <t>SERVICIO NACIONAL DE ADUANAS</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1789,13 +1789,13 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>4420.53</v>
+        <v>1140.92</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>548847-88-CM25</t>
+          <t>1079967-515-CM25</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1805,27 +1805,27 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>sep-2025</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2025-12-17</t>
+          <t>2025-09-17</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>61.979.440-0</t>
+          <t>60.505.102-2</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Instituto de Prevision Social</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1835,12 +1835,12 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE LIMITADA</t>
+          <t>DISTRIBUIDORA NENE SPA</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>77.012.870-6</t>
+          <t>76.067.436-2</t>
         </is>
       </c>
       <c r="K23" t="inlineStr"/>
@@ -1850,13 +1850,13 @@
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>1368.37</v>
+        <v>6375.47</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>845-220-CM25</t>
+          <t>2549-36-CM25</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1866,12 +1866,12 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>sep-2025</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2025-12-17</t>
+          <t>2025-09-29</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1881,12 +1881,12 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>70.072.600-2</t>
+          <t>61.606.100-3</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
+          <t>SERVICIO DE SALUD IQUIQUE</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -1896,12 +1896,12 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA NENE SPA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>76.067.436-2</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K24" t="inlineStr"/>
@@ -1911,13 +1911,13 @@
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>11162.18</v>
+        <v>1062.19</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>802-80-CM25</t>
+          <t>1350296-2121-CM25</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1927,12 +1927,12 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>oct-2025</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2025-12-18</t>
+          <t>2025-10-02</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>72.396.000-2</t>
+          <t>65.228.694-1</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>CORP NACIONAL DE DESARROLLO INDIGENA</t>
+          <t>HOSPITAL DE ALTO HOSPICIO</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -1972,13 +1972,13 @@
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>2109.88</v>
+        <v>761.1900000000001</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>1355-60-CM25</t>
+          <t>1417913-388-CM25</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1988,27 +1988,27 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>oct-2025</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>61.002.007-0</t>
+          <t>70.938.800-2</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Servicio de Registro Civil e Identificación</t>
+          <t>CORP MUNICIPAL DE DESARROLLO SOCIAL DE IQUIQUE</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -2018,12 +2018,12 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>SOCIEDAD SOLUCIONES INTEGRALES SPA</t>
+          <t>DISTRIBUIDORA NENE SPA</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>76.540.457-6</t>
+          <t>76.067.436-2</t>
         </is>
       </c>
       <c r="K26" t="inlineStr"/>
@@ -2033,13 +2033,13 @@
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>4476.72</v>
+        <v>21540.45</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>951-1855-CM25</t>
+          <t>696217-105-CM25</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2049,27 +2049,27 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>oct-2025</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2025-12-23</t>
+          <t>2025-10-09</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>60.511.010-K</t>
+          <t>61.935.400-1</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>DELEGACIÓN PRESIDENCIAL REGIONAL DE TARAPACÁ</t>
+          <t>MINISTERIO PUBLICO</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -2094,13 +2094,13 @@
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>1898.47</v>
+        <v>970.3099999999999</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>1486-88-CM25</t>
+          <t>699-51-CM25</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2110,12 +2110,12 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>oct-2025</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2025-10-10</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -2125,12 +2125,12 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>60.902.013-K</t>
+          <t>60.703.000-6</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Departamento Provincial de Educación Iquique</t>
+          <t>INSTITUTO NACIONAL DE ESTADISTICAS</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA NENE SPA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>76.067.436-2</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K28" t="inlineStr"/>
@@ -2155,13 +2155,13 @@
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>981.23</v>
+        <v>808.75</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>951-1858-CM25</t>
+          <t>1350296-2122-CM25</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>oct-2025</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2025-12-30</t>
+          <t>2025-10-13</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -2186,12 +2186,12 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>60.511.010-K</t>
+          <t>65.228.694-1</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>DELEGACIÓN PRESIDENCIAL REGIONAL DE TARAPACÁ</t>
+          <t>HOSPITAL DE ALTO HOSPICIO</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -2216,13 +2216,13 @@
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>2412.38</v>
+        <v>765.03</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>1350296-22-CM26</t>
+          <t>1346281-166-CM25</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2232,27 +2232,27 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>oct-2025</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026-01-08</t>
+          <t>2025-10-16</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>65.228.694-1</t>
+          <t>62.000.970-9</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>HOSPITAL DE ALTO HOSPICIO</t>
+          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -2262,12 +2262,12 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>DISTRIBUIDORA NENE SPA</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>76.067.436-2</t>
         </is>
       </c>
       <c r="K30" t="inlineStr"/>
@@ -2277,13 +2277,13 @@
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>6508.96</v>
+        <v>1414.5</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>1350296-21-CM26</t>
+          <t>1346281-167-CM25</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2293,27 +2293,27 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>oct-2025</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026-01-08</t>
+          <t>2025-10-16</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>65.228.694-1</t>
+          <t>62.000.970-9</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>HOSPITAL DE ALTO HOSPICIO</t>
+          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -2338,13 +2338,13 @@
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>2007.61</v>
+        <v>1018.57</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>1070620-157-CM26</t>
+          <t>707412-92-CM25</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2354,12 +2354,12 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>oct-2025</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026-01-09</t>
+          <t>2025-10-16</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -2369,12 +2369,12 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>62.000.530-4</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>HOSPITAL DOCTOR ERNESTO TORRES GALDAMES</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -2399,13 +2399,13 @@
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>4563.81</v>
+        <v>4633.33</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>1070620-209-CM26</t>
+          <t>1346281-169-CM25</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2415,27 +2415,27 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>oct-2025</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026-01-09</t>
+          <t>2025-10-24</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>62.000.530-4</t>
+          <t>62.000.970-9</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>HOSPITAL DOCTOR ERNESTO TORRES GALDAMES</t>
+          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -2460,13 +2460,13 @@
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>845.36</v>
+        <v>1810.85</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>1070620-732-CM26</t>
+          <t>1346281-170-CM25</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2476,27 +2476,27 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>oct-2025</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026-01-20</t>
+          <t>2025-10-24</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>62.000.530-4</t>
+          <t>62.000.970-9</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>HOSPITAL DOCTOR ERNESTO TORRES GALDAMES</t>
+          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -2506,12 +2506,12 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA NENE SPA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>76.067.436-2</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K34" t="inlineStr"/>
@@ -2521,13 +2521,13 @@
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>7767.17</v>
+        <v>849.09</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2174-2-CM26</t>
+          <t>5690-171-CM25</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>oct-2025</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026-01-20</t>
+          <t>2025-10-27</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -2552,12 +2552,12 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>60.301.001-9</t>
+          <t>61.308.000-7</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
+          <t>SERVICIO AGRICOLA Y GANADERO</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -2567,12 +2567,12 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>DISTRIBUIDORA NENE SPA</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>76.067.436-2</t>
         </is>
       </c>
       <c r="K35" t="inlineStr"/>
@@ -2582,13 +2582,13 @@
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>9561.139999999999</v>
+        <v>1428.17</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>1227-10-CM26</t>
+          <t>696217-121-CM25</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2598,27 +2598,27 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>oct-2025</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026-01-20</t>
+          <t>2025-10-28</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>60.804.002-1</t>
+          <t>61.935.400-1</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>DIRECCIÓN REGIONAL ADUANA DE IQUIQUE</t>
+          <t>MINISTERIO PUBLICO</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -2643,13 +2643,13 @@
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>1782.34</v>
+        <v>966.9</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>1091793-13-CM26</t>
+          <t>1350296-2287-CM25</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2659,12 +2659,12 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>oct-2025</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026-01-20</t>
+          <t>2025-10-28</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -2674,12 +2674,12 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>62.000.710-2</t>
+          <t>65.228.694-1</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>INSTITUTO NACIONAL DE DESARROLLO SUSTENTABLE DE LA</t>
+          <t>HOSPITAL DE ALTO HOSPICIO</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -2689,12 +2689,12 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>DISTRIBUIDORA NENE SPA</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>76.067.436-2</t>
         </is>
       </c>
       <c r="K37" t="inlineStr"/>
@@ -2704,13 +2704,13 @@
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>1169.1</v>
+        <v>1744.49</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>1426397-13-CM26</t>
+          <t>1346281-174-CM25</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2720,27 +2720,27 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026-01-29</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>61.980.910-6</t>
+          <t>62.000.970-9</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Servicio Local de Educación Pública Iquique</t>
+          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE LIMITADA</t>
+          <t>DISTRIBUIDORA NENE SPA</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>77.012.870-6</t>
+          <t>76.067.436-2</t>
         </is>
       </c>
       <c r="K38" t="inlineStr"/>
@@ -2765,13 +2765,13 @@
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>2563.32</v>
+        <v>1112.1</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>1426397-14-CM26</t>
+          <t>696217-138-CM25</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2781,27 +2781,27 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026-01-29</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>61.980.910-6</t>
+          <t>61.935.400-1</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Servicio Local de Educación Pública Iquique</t>
+          <t>MINISTERIO PUBLICO</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -2811,12 +2811,12 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>BARDANE SPA</t>
+          <t>DISTRIBUIDORA NENE SPA</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>77.205.722-9</t>
+          <t>76.067.436-2</t>
         </is>
       </c>
       <c r="K39" t="inlineStr"/>
@@ -2826,13 +2826,13 @@
         </is>
       </c>
       <c r="M39" s="2" t="n">
-        <v>2066.95</v>
+        <v>812.79</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>838102-17-CM26</t>
+          <t>1079967-642-CM25</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2842,12 +2842,12 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -2857,12 +2857,12 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>73.923.800-5</t>
+          <t>60.505.102-2</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Zona Bienestar "Iquique" Bienestar Social</t>
+          <t>SECCIÓN COMPRAS I ZONA</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -2872,12 +2872,12 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA NENE SPA</t>
+          <t>MUÑOZ Y VILCHES LIMITADA</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>76.067.436-2</t>
+          <t>77.008.207-2</t>
         </is>
       </c>
       <c r="K40" t="inlineStr"/>
@@ -2887,13 +2887,13 @@
         </is>
       </c>
       <c r="M40" s="2" t="n">
-        <v>909.05</v>
+        <v>5128.46</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>1057448-20-CM26</t>
+          <t>1213005-338-CM25</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2903,27 +2903,27 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>61.606.100-3</t>
+          <t>71.497.400-9</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD IQUIQUE</t>
+          <t>CORP MUNICIPAL DE DESARROLLO SOCIAL DE POZO ALMONTE</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -2933,12 +2933,12 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA NENE SPA</t>
+          <t>SOCIEDAD DE INVERSIONES DASSEN SPA</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>76.067.436-2</t>
+          <t>77.537.871-9</t>
         </is>
       </c>
       <c r="K41" t="inlineStr"/>
@@ -2948,13 +2948,13 @@
         </is>
       </c>
       <c r="M41" s="2" t="n">
-        <v>5553.82</v>
+        <v>1146.43</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>838102-20-CM26</t>
+          <t>1260688-275-CM25</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2964,27 +2964,27 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>73.923.800-5</t>
+          <t>71.497.400-9</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Zona Bienestar "Iquique" Bienestar Social</t>
+          <t>CORPORACION MUNICIPAL DE DESARROLLO SOCIAL POZO AL</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -2994,12 +2994,12 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>SOCIEDAD DE INVERSIONES DASSEN SPA</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>77.537.871-9</t>
         </is>
       </c>
       <c r="K42" t="inlineStr"/>
@@ -3009,13 +3009,13 @@
         </is>
       </c>
       <c r="M42" s="2" t="n">
-        <v>860.51</v>
+        <v>5154.12</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>1346281-35-CM26</t>
+          <t>1070620-18352-CM25</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3025,27 +3025,27 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>62.000.970-9</t>
+          <t>62.000.530-4</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
+          <t>HOSPITAL DOCTOR ERNESTO TORRES GALDAMES</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -3070,13 +3070,13 @@
         </is>
       </c>
       <c r="M43" s="2" t="n">
-        <v>1298.1</v>
+        <v>3329.52</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>3170-16-CM26</t>
+          <t>768-642-CM25</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3086,12 +3086,12 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -3101,12 +3101,12 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>61.941.300-8</t>
+          <t>72.223.100-7</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>CENTRO DE ABASTECIMIENTO (I)</t>
+          <t>GOBIERNO REGIONAL DE TARAPACA</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -3116,12 +3116,12 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA IGESCOM SPA</t>
+          <t>DISTRIBUIDORA NENE SPA</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>77.152.668-3</t>
+          <t>76.067.436-2</t>
         </is>
       </c>
       <c r="K44" t="inlineStr"/>
@@ -3131,13 +3131,13 @@
         </is>
       </c>
       <c r="M44" s="2" t="n">
-        <v>1529.2</v>
+        <v>1407.77</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>1227-32-CM26</t>
+          <t>696217-149-CM25</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3147,27 +3147,27 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2026-02-10</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>60.804.002-1</t>
+          <t>61.935.400-1</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>DIRECCIÓN REGIONAL ADUANA DE IQUIQUE</t>
+          <t>MINISTERIO PUBLICO</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -3192,13 +3192,13 @@
         </is>
       </c>
       <c r="M45" s="2" t="n">
-        <v>1505.59</v>
+        <v>1474.82</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>1070620-1585-CM26</t>
+          <t>1079967-659-CM25</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3208,12 +3208,12 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -3223,12 +3223,12 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>62.000.530-4</t>
+          <t>60.505.102-2</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>HOSPITAL DOCTOR ERNESTO TORRES GALDAMES</t>
+          <t>SECCIÓN COMPRAS I ZONA</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -3238,12 +3238,12 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA NENE SPA</t>
+          <t>MUÑOZ Y VILCHES LIMITADA</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>76.067.436-2</t>
+          <t>77.008.207-2</t>
         </is>
       </c>
       <c r="K46" t="inlineStr"/>
@@ -3253,13 +3253,13 @@
         </is>
       </c>
       <c r="M46" s="2" t="n">
-        <v>5670.13</v>
+        <v>21873.24</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>707412-14-CM26</t>
+          <t>908366-104-CM25</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3269,12 +3269,12 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2026-02-16</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -3284,12 +3284,12 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>69.010.400-8</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>I MUNICIPALIDAD DE PICA</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -3299,12 +3299,12 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>MALMO S.A.</t>
+          <t>DISTRIBUIDORA NENE SPA</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>76.195.558-6</t>
+          <t>76.067.436-2</t>
         </is>
       </c>
       <c r="K47" t="inlineStr"/>
@@ -3314,13 +3314,13 @@
         </is>
       </c>
       <c r="M47" s="2" t="n">
-        <v>1195.08</v>
+        <v>2929.4</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>907562-10-CM26</t>
+          <t>1070620-29585-CM25</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -3330,12 +3330,12 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2026-02-17</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -3345,12 +3345,12 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>69.010.400-8</t>
+          <t>62.000.530-4</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PICA</t>
+          <t>HOSPITAL DOCTOR ERNESTO TORRES GALDAMES</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -3375,13 +3375,13 @@
         </is>
       </c>
       <c r="M48" s="2" t="n">
-        <v>2640.16</v>
+        <v>1180.11</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2013-209-CM26</t>
+          <t>845-200-CM25</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -3391,27 +3391,27 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>70.777.500-9</t>
+          <t>70.072.600-2</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD ARTURO PRAT</t>
+          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -3421,12 +3421,12 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE LIMITADA</t>
+          <t>BARDANE SPA</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>77.012.870-6</t>
+          <t>77.205.722-9</t>
         </is>
       </c>
       <c r="K49" t="inlineStr"/>
@@ -3436,13 +3436,13 @@
         </is>
       </c>
       <c r="M49" s="2" t="n">
-        <v>9555.74</v>
+        <v>1459.6</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>1350296-324-CM26</t>
+          <t>845-201-CM25</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -3452,12 +3452,12 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -3467,12 +3467,12 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>65.228.694-1</t>
+          <t>70.072.600-2</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>HOSPITAL DE ALTO HOSPICIO</t>
+          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -3482,12 +3482,12 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>BARDANE SPA</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>77.205.722-9</t>
         </is>
       </c>
       <c r="K50" t="inlineStr"/>
@@ -3497,13 +3497,13 @@
         </is>
       </c>
       <c r="M50" s="2" t="n">
-        <v>5200.79</v>
+        <v>1140.71</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>618472-2-CM26</t>
+          <t>1350296-2536-CM25</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -3513,12 +3513,12 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2025-12-09</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>61.979.990-9</t>
+          <t>65.228.694-1</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>HOSPITAL DE ALTO HOSPICIO</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -3558,13 +3558,13 @@
         </is>
       </c>
       <c r="M51" s="2" t="n">
-        <v>1833.71</v>
+        <v>2964.46</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>1347772-17-CM26</t>
+          <t>5651-2194-CM25</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -3574,12 +3574,12 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -3589,12 +3589,12 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>62.000.890-7</t>
+          <t>61.313.000-4</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PROTECCIÓN ESPECIALIZADA A LA</t>
+          <t>CORP NACIONAL FORESTAL</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -3619,13 +3619,13 @@
         </is>
       </c>
       <c r="M52" s="2" t="n">
-        <v>1756.44</v>
+        <v>934.96</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>1070620-2309-CM26</t>
+          <t>5663-52-CM25</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -3635,12 +3635,12 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2025-12-11</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -3650,12 +3650,12 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>62.000.530-4</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>HOSPITAL DOCTOR ERNESTO TORRES GALDAMES</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -3680,13 +3680,13 @@
         </is>
       </c>
       <c r="M53" s="2" t="n">
-        <v>1074.71</v>
+        <v>757.83</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>707412-18-CM26</t>
+          <t>548847-88-CM25</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -3696,27 +3696,27 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2025-12-17</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>61.979.440-0</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>Instituto de Prevision Social</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -3726,12 +3726,12 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>COMERCIAL RED OFFICE LIMITADA</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>77.012.870-6</t>
         </is>
       </c>
       <c r="K54" t="inlineStr"/>
@@ -3741,13 +3741,13 @@
         </is>
       </c>
       <c r="M54" s="2" t="n">
-        <v>876.25</v>
+        <v>1368.37</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2013-259-CM26</t>
+          <t>3145-686-CM25</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -3757,12 +3757,12 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2025-12-17</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -3772,12 +3772,12 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>70.777.500-9</t>
+          <t>61.103.023-1</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD ARTURO PRAT</t>
+          <t>Iª Brigada Aérea</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -3787,12 +3787,12 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE LIMITADA</t>
+          <t>DISTRIBUIDORA NENE SPA</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>77.012.870-6</t>
+          <t>76.067.436-2</t>
         </is>
       </c>
       <c r="K55" t="inlineStr"/>
@@ -3802,13 +3802,13 @@
         </is>
       </c>
       <c r="M55" s="2" t="n">
-        <v>2066.21</v>
+        <v>4420.53</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>1407-118-CM26</t>
+          <t>845-222-CM25</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -3818,12 +3818,12 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2025-12-17</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -3833,12 +3833,12 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>61.004.002-0</t>
+          <t>70.072.600-2</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Iquique</t>
+          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -3848,12 +3848,12 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>DISTRIBUIDORA NENE SPA</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>76.067.436-2</t>
         </is>
       </c>
       <c r="K56" t="inlineStr"/>
@@ -3863,13 +3863,13 @@
         </is>
       </c>
       <c r="M56" s="2" t="n">
-        <v>1139.89</v>
+        <v>2009.47</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>1070620-2522-CM26</t>
+          <t>845-220-CM25</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -3879,12 +3879,12 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2025-12-17</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -3894,12 +3894,12 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>62.000.530-4</t>
+          <t>70.072.600-2</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>HOSPITAL DOCTOR ERNESTO TORRES GALDAMES</t>
+          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -3924,13 +3924,13 @@
         </is>
       </c>
       <c r="M57" s="2" t="n">
-        <v>1588.97</v>
+        <v>11162.18</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>3352-37-CM26</t>
+          <t>802-80-CM25</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -3940,12 +3940,12 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2025-12-18</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -3955,12 +3955,12 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>61.101.024-9</t>
+          <t>72.396.000-2</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>EJERCITO DE CHILE ESCUELA CABALLERIA QUI</t>
+          <t>CORP NACIONAL DE DESARROLLO INDIGENA</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -3970,12 +3970,12 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>DISTRIBUIDORA NENE SPA</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>76.067.436-2</t>
         </is>
       </c>
       <c r="K58" t="inlineStr"/>
@@ -3985,13 +3985,13 @@
         </is>
       </c>
       <c r="M58" s="2" t="n">
-        <v>2277.41</v>
+        <v>2109.88</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>3349-62-CM26</t>
+          <t>1355-60-CM25</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4001,12 +4001,12 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -4016,12 +4016,12 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>65.283.230-K</t>
+          <t>61.002.007-0</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>Servicio de Registro Civil e Identificación</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -4031,12 +4031,12 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA NENE SPA</t>
+          <t>SOCIEDAD SOLUCIONES INTEGRALES SPA</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>76.067.436-2</t>
+          <t>76.540.457-6</t>
         </is>
       </c>
       <c r="K59" t="inlineStr"/>
@@ -4046,13 +4046,13 @@
         </is>
       </c>
       <c r="M59" s="2" t="n">
-        <v>7570.95</v>
+        <v>4476.72</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>1070620-2949-CM26</t>
+          <t>951-1855-CM25</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -4062,12 +4062,12 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2025-12-23</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -4077,12 +4077,12 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>62.000.530-4</t>
+          <t>60.511.010-K</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>HOSPITAL DOCTOR ERNESTO TORRES GALDAMES</t>
+          <t>DELEGACIÓN PRESIDENCIAL REGIONAL DE TARAPACÁ</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -4107,13 +4107,13 @@
         </is>
       </c>
       <c r="M60" s="2" t="n">
-        <v>2206.95</v>
+        <v>1898.47</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>1346281-48-CM26</t>
+          <t>1486-88-CM25</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -4123,12 +4123,12 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -4138,12 +4138,12 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>62.000.970-9</t>
+          <t>60.902.013-K</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
+          <t>Departamento Provincial de Educación Iquique</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -4153,12 +4153,12 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>DISTRIBUIDORA NENE SPA</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>76.067.436-2</t>
         </is>
       </c>
       <c r="K61" t="inlineStr"/>
@@ -4168,13 +4168,13 @@
         </is>
       </c>
       <c r="M61" s="2" t="n">
-        <v>859.85</v>
+        <v>981.23</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>3352-49-CM26</t>
+          <t>951-1858-CM25</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -4184,12 +4184,12 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2025-12-30</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -4199,12 +4199,12 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>61.101.024-9</t>
+          <t>60.511.010-K</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>EJERCITO DE CHILE ESCUELA CABALLERIA QUI</t>
+          <t>DELEGACIÓN PRESIDENCIAL REGIONAL DE TARAPACÁ</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -4214,12 +4214,12 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>MALMO S.A.</t>
+          <t>DISTRIBUIDORA NENE SPA</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>76.195.558-6</t>
+          <t>76.067.436-2</t>
         </is>
       </c>
       <c r="K62" t="inlineStr"/>
@@ -4229,13 +4229,13 @@
         </is>
       </c>
       <c r="M62" s="2" t="n">
-        <v>1475.02</v>
+        <v>2412.38</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>1346281-50-CM26</t>
+          <t>1350296-22-CM26</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -4245,12 +4245,12 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-01-08</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -4260,12 +4260,12 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>62.000.970-9</t>
+          <t>65.228.694-1</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
+          <t>HOSPITAL DE ALTO HOSPICIO</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -4275,12 +4275,12 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA NENE SPA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>76.067.436-2</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K63" t="inlineStr"/>
@@ -4290,13 +4290,13 @@
         </is>
       </c>
       <c r="M63" s="2" t="n">
-        <v>753.52</v>
+        <v>6508.96</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>1079967-130-CM26</t>
+          <t>1350296-21-CM26</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -4306,12 +4306,12 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-01-08</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -4321,12 +4321,12 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>60.505.102-2</t>
+          <t>65.228.694-1</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS I ZONA</t>
+          <t>HOSPITAL DE ALTO HOSPICIO</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -4336,12 +4336,12 @@
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>MALMO S.A.</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>76.195.558-6</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K64" t="inlineStr"/>
@@ -4351,13 +4351,13 @@
         </is>
       </c>
       <c r="M64" s="2" t="n">
-        <v>31748.88</v>
+        <v>2007.61</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>5126-29-CM26</t>
+          <t>1070620-157-CM26</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -4367,12 +4367,12 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-01-09</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -4382,12 +4382,12 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>61.979.650-0</t>
+          <t>62.000.530-4</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Estado Mayor Conjunto</t>
+          <t>HOSPITAL DOCTOR ERNESTO TORRES GALDAMES</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -4397,12 +4397,12 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>DISTRIBUIDORA NENE SPA</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>76.067.436-2</t>
         </is>
       </c>
       <c r="K65" t="inlineStr"/>
@@ -4412,13 +4412,13 @@
         </is>
       </c>
       <c r="M65" s="2" t="n">
-        <v>2810.41</v>
+        <v>4563.81</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>1070620-3123-CM26</t>
+          <t>1070620-209-CM26</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -4428,12 +4428,12 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-01-09</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -4458,12 +4458,12 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>IMPORTADORA HEVIA SPA</t>
+          <t>DISTRIBUIDORA NENE SPA</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>76.872.717-1</t>
+          <t>76.067.436-2</t>
         </is>
       </c>
       <c r="K66" t="inlineStr"/>
@@ -4473,13 +4473,13 @@
         </is>
       </c>
       <c r="M66" s="2" t="n">
-        <v>983.75</v>
+        <v>845.36</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>1070620-3155-CM26</t>
+          <t>1070620-732-CM26</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -4489,12 +4489,12 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-01-20</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -4534,13 +4534,13 @@
         </is>
       </c>
       <c r="M67" s="2" t="n">
-        <v>775.48</v>
+        <v>7767.17</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>548847-11-CM26</t>
+          <t>2174-2-CM26</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -4550,12 +4550,12 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-01-20</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -4565,12 +4565,12 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>61.979.440-0</t>
+          <t>60.301.001-9</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Instituto de Prevision Social</t>
+          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -4580,12 +4580,12 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA NENE SPA</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>76.067.436-2</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K68" t="inlineStr"/>
@@ -4595,13 +4595,13 @@
         </is>
       </c>
       <c r="M68" s="2" t="n">
-        <v>1961.27</v>
+        <v>9561.139999999999</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>1312459-13-CM26</t>
+          <t>1227-10-CM26</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -4611,12 +4611,12 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-01-20</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -4626,12 +4626,12 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>65.039.239-6</t>
+          <t>60.804.002-1</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>CORPORACION MUNICIPAL DE DEPORTES DE IQUIQUE</t>
+          <t>DIRECCIÓN REGIONAL ADUANA DE IQUIQUE</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -4656,13 +4656,13 @@
         </is>
       </c>
       <c r="M69" s="2" t="n">
-        <v>883.89</v>
+        <v>1782.34</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>1312459-14-CM26</t>
+          <t>1091793-13-CM26</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -4672,12 +4672,12 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-01-20</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -4687,12 +4687,12 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>65.039.239-6</t>
+          <t>62.000.710-2</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>CORPORACION MUNICIPAL DE DEPORTES DE IQUIQUE</t>
+          <t>INSTITUTO NACIONAL DE DESARROLLO SUSTENTABLE DE LA</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -4702,12 +4702,12 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA NENE SPA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>76.067.436-2</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K70" t="inlineStr"/>
@@ -4717,13 +4717,13 @@
         </is>
       </c>
       <c r="M70" s="2" t="n">
-        <v>2737.42</v>
+        <v>1169.1</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>3352-48-CM26</t>
+          <t>1426397-13-CM26</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -4733,12 +4733,12 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-01-29</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -4748,12 +4748,12 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>61.101.024-9</t>
+          <t>61.980.910-6</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>EJERCITO DE CHILE ESCUELA CABALLERIA QUI</t>
+          <t>Servicio Local de Educación Pública Iquique</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -4763,12 +4763,12 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>OTTO HAN SPA</t>
+          <t>COMERCIAL RED OFFICE LIMITADA</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>77.809.872-5</t>
+          <t>77.012.870-6</t>
         </is>
       </c>
       <c r="K71" t="inlineStr"/>
@@ -4778,13 +4778,13 @@
         </is>
       </c>
       <c r="M71" s="2" t="n">
-        <v>1068.43</v>
+        <v>2563.32</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>696217-29-CM26</t>
+          <t>1426397-14-CM26</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -4794,27 +4794,27 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-01-29</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>61.935.400-1</t>
+          <t>61.980.910-6</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>MINISTERIO PUBLICO</t>
+          <t>Servicio Local de Educación Pública Iquique</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -4824,12 +4824,12 @@
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA NENE SPA</t>
+          <t>BARDANE SPA</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>76.067.436-2</t>
+          <t>77.205.722-9</t>
         </is>
       </c>
       <c r="K72" t="inlineStr"/>
@@ -4839,13 +4839,13 @@
         </is>
       </c>
       <c r="M72" s="2" t="n">
-        <v>1043.09</v>
+        <v>2066.95</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>1070620-3444-CM26</t>
+          <t>838102-17-CM26</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -4855,12 +4855,12 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -4870,12 +4870,12 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>62.000.530-4</t>
+          <t>73.923.800-5</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>HOSPITAL DOCTOR ERNESTO TORRES GALDAMES</t>
+          <t>Zona Bienestar "Iquique" Bienestar Social</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -4900,13 +4900,13 @@
         </is>
       </c>
       <c r="M73" s="2" t="n">
-        <v>2170.45</v>
+        <v>909.05</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>5690-47-CM26</t>
+          <t>1057448-20-CM26</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -4916,12 +4916,12 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -4931,12 +4931,12 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>61.308.000-7</t>
+          <t>61.606.100-3</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>SERVICIO AGRICOLA Y GANADERO</t>
+          <t>SERVICIO DE SALUD IQUIQUE</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -4946,12 +4946,12 @@
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>DISTRIBUIDORA NENE SPA</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>76.067.436-2</t>
         </is>
       </c>
       <c r="K74" t="inlineStr"/>
@@ -4961,13 +4961,13 @@
         </is>
       </c>
       <c r="M74" s="2" t="n">
-        <v>1851.11</v>
+        <v>5553.82</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>935934-87-CM26</t>
+          <t>838102-20-CM26</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -4977,12 +4977,12 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -4992,12 +4992,12 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>61.980.770-7</t>
+          <t>73.923.800-5</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Zona de Bienestar Iquique</t>
+          <t>Zona Bienestar "Iquique" Bienestar Social</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -5022,13 +5022,13 @@
         </is>
       </c>
       <c r="M75" s="2" t="n">
-        <v>839.79</v>
+        <v>860.51</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>1070620-3772-CM26</t>
+          <t>1346281-35-CM26</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -5038,27 +5038,27 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>62.000.530-4</t>
+          <t>62.000.970-9</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>HOSPITAL DOCTOR ERNESTO TORRES GALDAMES</t>
+          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -5083,13 +5083,13 @@
         </is>
       </c>
       <c r="M76" s="2" t="n">
-        <v>3008.51</v>
+        <v>1298.1</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>1026727-110-CM26</t>
+          <t>3170-16-CM26</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -5099,12 +5099,12 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -5114,12 +5114,12 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>65.154.398-3</t>
+          <t>61.941.300-8</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>CENTRO DE FORMACION TECNICA DE LA REGION DE TARAPACA</t>
+          <t>CENTRO DE ABASTECIMIENTO (I)</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -5129,12 +5129,12 @@
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA NENE SPA</t>
+          <t>COMERCIALIZADORA IGESCOM SPA</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>76.067.436-2</t>
+          <t>77.152.668-3</t>
         </is>
       </c>
       <c r="K77" t="inlineStr"/>
@@ -5144,13 +5144,13 @@
         </is>
       </c>
       <c r="M77" s="2" t="n">
-        <v>5730.05</v>
+        <v>1529.2</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>1070620-3965-CM26</t>
+          <t>1227-32-CM26</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -5160,12 +5160,12 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-02-10</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -5175,12 +5175,12 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>62.000.530-4</t>
+          <t>60.804.002-1</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>HOSPITAL DOCTOR ERNESTO TORRES GALDAMES</t>
+          <t>DIRECCIÓN REGIONAL ADUANA DE IQUIQUE</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -5205,13 +5205,13 @@
         </is>
       </c>
       <c r="M78" s="2" t="n">
-        <v>2654.48</v>
+        <v>1505.59</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>1070620-3970-CM26</t>
+          <t>1070620-1585-CM26</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -5221,12 +5221,12 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -5266,13 +5266,13 @@
         </is>
       </c>
       <c r="M79" s="2" t="n">
-        <v>2971.98</v>
+        <v>5670.13</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>696217-36-CM26</t>
+          <t>707412-14-CM26</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -5282,27 +5282,27 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-02-16</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>61.935.400-1</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>MINISTERIO PUBLICO</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -5312,12 +5312,12 @@
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA NENE SPA</t>
+          <t>MALMO S.A.</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>76.067.436-2</t>
+          <t>76.195.558-6</t>
         </is>
       </c>
       <c r="K80" t="inlineStr"/>
@@ -5327,13 +5327,13 @@
         </is>
       </c>
       <c r="M80" s="2" t="n">
-        <v>797.04</v>
+        <v>1195.08</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>1077499-48-CM26</t>
+          <t>907562-10-CM26</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -5343,12 +5343,12 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-02-17</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -5358,12 +5358,12 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>61.606.100-3</t>
+          <t>69.010.400-8</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD IQUIQUE</t>
+          <t>I MUNICIPALIDAD DE PICA</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -5373,12 +5373,12 @@
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE LIMITADA</t>
+          <t>DISTRIBUIDORA NENE SPA</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>77.012.870-6</t>
+          <t>76.067.436-2</t>
         </is>
       </c>
       <c r="K81" t="inlineStr"/>
@@ -5388,13 +5388,13 @@
         </is>
       </c>
       <c r="M81" s="2" t="n">
-        <v>1421.78</v>
+        <v>2640.16</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>1355-15-CM26</t>
+          <t>2013-209-CM26</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -5404,27 +5404,27 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>61.002.007-0</t>
+          <t>70.777.500-9</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Servicio de Registro Civil e Identificación</t>
+          <t>UNIVERSIDAD ARTURO PRAT</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -5434,12 +5434,12 @@
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA SAN JERONIMO SPA</t>
+          <t>COMERCIAL RED OFFICE LIMITADA</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>77.610.393-4</t>
+          <t>77.012.870-6</t>
         </is>
       </c>
       <c r="K82" t="inlineStr"/>
@@ -5449,13 +5449,13 @@
         </is>
       </c>
       <c r="M82" s="2" t="n">
-        <v>9123.34</v>
+        <v>9555.74</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>1070620-4300-CM26</t>
+          <t>1350296-324-CM26</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -5465,12 +5465,12 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -5480,12 +5480,12 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>62.000.530-4</t>
+          <t>65.228.694-1</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>HOSPITAL DOCTOR ERNESTO TORRES GALDAMES</t>
+          <t>HOSPITAL DE ALTO HOSPICIO</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -5495,12 +5495,12 @@
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA NENE SPA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>76.067.436-2</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K83" t="inlineStr"/>
@@ -5510,13 +5510,13 @@
         </is>
       </c>
       <c r="M83" s="2" t="n">
-        <v>4063.54</v>
+        <v>5200.79</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>1426397-149-CM26</t>
+          <t>618472-2-CM26</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -5526,12 +5526,12 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -5541,12 +5541,12 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>61.980.910-6</t>
+          <t>61.979.990-9</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Servicio Local de Educación Pública Iquique</t>
+          <t>Ejercito de Chile</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -5571,13 +5571,13 @@
         </is>
       </c>
       <c r="M84" s="2" t="n">
-        <v>27867.05</v>
+        <v>1833.71</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>2013-788-CM26</t>
+          <t>1347772-17-CM26</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -5587,27 +5587,27 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>70.777.500-9</t>
+          <t>62.000.890-7</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD ARTURO PRAT</t>
+          <t>SERVICIO NACIONAL DE PROTECCIÓN ESPECIALIZADA A LA</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -5617,12 +5617,12 @@
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>INVERSIONES CORP PREMIER LTDA</t>
+          <t>DISTRIBUIDORA NENE SPA</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>76.473.108-5</t>
+          <t>76.067.436-2</t>
         </is>
       </c>
       <c r="K85" t="inlineStr"/>
@@ -5632,13 +5632,13 @@
         </is>
       </c>
       <c r="M85" s="2" t="n">
-        <v>3448.12</v>
+        <v>1756.44</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>1070620-4588-CM26</t>
+          <t>1070620-2309-CM26</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -5648,12 +5648,12 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -5693,13 +5693,13 @@
         </is>
       </c>
       <c r="M86" s="2" t="n">
-        <v>1717.38</v>
+        <v>1074.71</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>1350296-953-CM26</t>
+          <t>707412-18-CM26</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -5709,12 +5709,12 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -5724,12 +5724,12 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>65.228.694-1</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>HOSPITAL DE ALTO HOSPICIO</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -5739,12 +5739,12 @@
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA NENE SPA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>76.067.436-2</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K87" t="inlineStr"/>
@@ -5754,13 +5754,13 @@
         </is>
       </c>
       <c r="M87" s="2" t="n">
-        <v>2900.32</v>
+        <v>876.25</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>3349-159-CM26</t>
+          <t>2013-259-CM26</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -5770,27 +5770,27 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>65.283.230-K</t>
+          <t>70.777.500-9</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>UNIVERSIDAD ARTURO PRAT</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
@@ -5800,12 +5800,12 @@
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA NENE SPA</t>
+          <t>COMERCIAL RED OFFICE LIMITADA</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>76.067.436-2</t>
+          <t>77.012.870-6</t>
         </is>
       </c>
       <c r="K88" t="inlineStr"/>
@@ -5815,13 +5815,13 @@
         </is>
       </c>
       <c r="M88" s="2" t="n">
-        <v>1338.38</v>
+        <v>2066.21</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>1070620-5112-CM26</t>
+          <t>1407-118-CM26</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -5831,12 +5831,12 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -5846,12 +5846,12 @@
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>62.000.530-4</t>
+          <t>61.004.002-0</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>HOSPITAL DOCTOR ERNESTO TORRES GALDAMES</t>
+          <t>Dirección Regional de Gendarmeria - Iquique</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -5861,12 +5861,12 @@
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA NENE SPA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>76.067.436-2</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K89" t="inlineStr"/>
@@ -5876,13 +5876,13 @@
         </is>
       </c>
       <c r="M89" s="2" t="n">
-        <v>4394.29</v>
+        <v>1139.89</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>1070620-5145-CM26</t>
+          <t>1070620-2522-CM26</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -5892,12 +5892,12 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
@@ -5937,13 +5937,13 @@
         </is>
       </c>
       <c r="M90" s="2" t="n">
-        <v>806.4299999999999</v>
+        <v>1588.97</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>1350296-923-CM26</t>
+          <t>3352-37-CM26</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -5953,12 +5953,12 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -5968,12 +5968,12 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>65.228.694-1</t>
+          <t>61.101.024-9</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>HOSPITAL DE ALTO HOSPICIO</t>
+          <t>EJERCITO DE CHILE ESCUELA CABALLERIA QUI</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
@@ -5983,12 +5983,12 @@
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA IGESCOM SPA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>77.152.668-3</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K91" t="inlineStr"/>
@@ -5998,13 +5998,13 @@
         </is>
       </c>
       <c r="M91" s="2" t="n">
-        <v>1288.94</v>
+        <v>2277.41</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>948-72-CM26</t>
+          <t>3349-62-CM26</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
@@ -6029,12 +6029,12 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>60.901.003-7</t>
+          <t>65.283.230-K</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Secretaría Regional Ministerial de Educación de la Primera Región</t>
+          <t>Ejercito de Chile</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -6059,13 +6059,13 @@
         </is>
       </c>
       <c r="M92" s="2" t="n">
-        <v>783.7</v>
+        <v>7570.95</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>1407-331-CM26</t>
+          <t>1070620-2949-CM26</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -6075,12 +6075,12 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
@@ -6090,12 +6090,12 @@
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>61.004.002-0</t>
+          <t>62.000.530-4</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Iquique</t>
+          <t>HOSPITAL DOCTOR ERNESTO TORRES GALDAMES</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -6120,13 +6120,13 @@
         </is>
       </c>
       <c r="M93" s="2" t="n">
-        <v>1097.01</v>
+        <v>2206.95</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>1057448-209-CM26</t>
+          <t>1346281-48-CM26</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -6136,12 +6136,12 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
@@ -6151,12 +6151,12 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>61.606.100-3</t>
+          <t>62.000.970-9</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD IQUIQUE</t>
+          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
@@ -6166,12 +6166,12 @@
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA NENE SPA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>76.067.436-2</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K94" t="inlineStr"/>
@@ -6181,13 +6181,13 @@
         </is>
       </c>
       <c r="M94" s="2" t="n">
-        <v>1133.72</v>
+        <v>859.85</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>1227-161-CM26</t>
+          <t>3352-49-CM26</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
@@ -6212,12 +6212,12 @@
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>60.804.002-1</t>
+          <t>61.101.024-9</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>DIRECCIÓN REGIONAL ADUANA DE IQUIQUE</t>
+          <t>EJERCITO DE CHILE ESCUELA CABALLERIA QUI</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
@@ -6227,12 +6227,12 @@
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA NENE SPA</t>
+          <t>MALMO S.A.</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>76.067.436-2</t>
+          <t>76.195.558-6</t>
         </is>
       </c>
       <c r="K95" t="inlineStr"/>
@@ -6242,13 +6242,13 @@
         </is>
       </c>
       <c r="M95" s="2" t="n">
-        <v>833.25</v>
+        <v>1475.02</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>1346281-93-CM26</t>
+          <t>1346281-50-CM26</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -6258,12 +6258,12 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
@@ -6303,13 +6303,13 @@
         </is>
       </c>
       <c r="M96" s="2" t="n">
-        <v>818.53</v>
+        <v>753.52</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>548847-33-CM26</t>
+          <t>1079967-130-CM26</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -6319,12 +6319,12 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
@@ -6334,12 +6334,12 @@
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>61.979.440-0</t>
+          <t>60.505.102-2</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Instituto de Prevision Social</t>
+          <t>SECCIÓN COMPRAS I ZONA</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -6349,12 +6349,12 @@
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>MALMO S.A.</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>76.195.558-6</t>
         </is>
       </c>
       <c r="K97" t="inlineStr"/>
@@ -6364,13 +6364,13 @@
         </is>
       </c>
       <c r="M97" s="2" t="n">
-        <v>3171.11</v>
+        <v>31748.88</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>707412-47-CM26</t>
+          <t>5126-29-CM26</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -6380,27 +6380,27 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>61.979.650-0</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>Estado Mayor Conjunto</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
@@ -6410,12 +6410,12 @@
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA NENE SPA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>76.067.436-2</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K98" t="inlineStr"/>
@@ -6425,13 +6425,13 @@
         </is>
       </c>
       <c r="M98" s="2" t="n">
-        <v>8179.49</v>
+        <v>2810.41</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>1070620-5843-CM26</t>
+          <t>1070620-3155-CM26</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -6441,12 +6441,12 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
@@ -6486,13 +6486,13 @@
         </is>
       </c>
       <c r="M99" s="2" t="n">
-        <v>4432.28</v>
+        <v>775.48</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>1350296-1137-CM26</t>
+          <t>1070620-3123-CM26</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -6502,12 +6502,12 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
@@ -6517,12 +6517,12 @@
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>65.228.694-1</t>
+          <t>62.000.530-4</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>HOSPITAL DE ALTO HOSPICIO</t>
+          <t>HOSPITAL DOCTOR ERNESTO TORRES GALDAMES</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
@@ -6532,12 +6532,12 @@
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA NENE SPA</t>
+          <t>IMPORTADORA HEVIA SPA</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>76.067.436-2</t>
+          <t>76.872.717-1</t>
         </is>
       </c>
       <c r="K100" t="inlineStr"/>
@@ -6547,13 +6547,13 @@
         </is>
       </c>
       <c r="M100" s="2" t="n">
-        <v>1081.22</v>
+        <v>983.75</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>1350296-1138-CM26</t>
+          <t>548847-11-CM26</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -6563,12 +6563,12 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
@@ -6578,12 +6578,12 @@
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>65.228.694-1</t>
+          <t>61.979.440-0</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>HOSPITAL DE ALTO HOSPICIO</t>
+          <t>Instituto de Prevision Social</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
@@ -6593,12 +6593,12 @@
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>DISTRIBUIDORA NENE SPA</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>76.067.436-2</t>
         </is>
       </c>
       <c r="K101" t="inlineStr"/>
@@ -6608,13 +6608,13 @@
         </is>
       </c>
       <c r="M101" s="2" t="n">
-        <v>1227.57</v>
+        <v>1961.27</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>2013-1102-CM26</t>
+          <t>1312459-13-CM26</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -6624,27 +6624,27 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>70.777.500-9</t>
+          <t>65.039.239-6</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD ARTURO PRAT</t>
+          <t>CORPORACION MUNICIPAL DE DEPORTES DE IQUIQUE</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
@@ -6654,12 +6654,12 @@
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE LIMITADA</t>
+          <t>DISTRIBUIDORA NENE SPA</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>77.012.870-6</t>
+          <t>76.067.436-2</t>
         </is>
       </c>
       <c r="K102" t="inlineStr"/>
@@ -6669,13 +6669,13 @@
         </is>
       </c>
       <c r="M102" s="2" t="n">
-        <v>9813.75</v>
+        <v>883.89</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>802-17-CM26</t>
+          <t>1312459-14-CM26</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -6685,27 +6685,27 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>72.396.000-2</t>
+          <t>65.039.239-6</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>CORP NACIONAL DE DESARROLLO INDIGENA</t>
+          <t>CORPORACION MUNICIPAL DE DEPORTES DE IQUIQUE</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
@@ -6730,13 +6730,13 @@
         </is>
       </c>
       <c r="M103" s="2" t="n">
-        <v>3398.37</v>
+        <v>2737.42</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>1070620-6258-CM26</t>
+          <t>3352-48-CM26</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -6746,12 +6746,12 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
@@ -6761,12 +6761,12 @@
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>62.000.530-4</t>
+          <t>61.101.024-9</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>HOSPITAL DOCTOR ERNESTO TORRES GALDAMES</t>
+          <t>EJERCITO DE CHILE ESCUELA CABALLERIA QUI</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
@@ -6776,12 +6776,12 @@
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE LIMITADA</t>
+          <t>OTTO HAN SPA</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t>77.012.870-6</t>
+          <t>77.809.872-5</t>
         </is>
       </c>
       <c r="K104" t="inlineStr"/>
@@ -6791,13 +6791,13 @@
         </is>
       </c>
       <c r="M104" s="2" t="n">
-        <v>805</v>
+        <v>1068.43</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>1346281-109-CM26</t>
+          <t>696217-29-CM26</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -6807,27 +6807,27 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>62.000.970-9</t>
+          <t>61.935.400-1</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
+          <t>MINISTERIO PUBLICO</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
@@ -6837,12 +6837,12 @@
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>DISTRIBUIDORA NENE SPA</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>76.067.436-2</t>
         </is>
       </c>
       <c r="K105" t="inlineStr"/>
@@ -6852,13 +6852,13 @@
         </is>
       </c>
       <c r="M105" s="2" t="n">
-        <v>1202.13</v>
+        <v>1043.09</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>5690-95-CM26</t>
+          <t>1070620-3444-CM26</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -6868,27 +6868,27 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>61.308.000-7</t>
+          <t>62.000.530-4</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>SERVICIO AGRICOLA Y GANADERO</t>
+          <t>HOSPITAL DOCTOR ERNESTO TORRES GALDAMES</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
@@ -6898,12 +6898,12 @@
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>DISTRIBUIDORA NENE SPA</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>76.067.436-2</t>
         </is>
       </c>
       <c r="K106" t="inlineStr"/>
@@ -6913,13 +6913,13 @@
         </is>
       </c>
       <c r="M106" s="2" t="n">
-        <v>968.89</v>
+        <v>2170.45</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>1350296-1197-CM26</t>
+          <t>5690-47-CM26</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -6929,12 +6929,12 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
@@ -6944,12 +6944,12 @@
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>65.228.694-1</t>
+          <t>61.308.000-7</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>HOSPITAL DE ALTO HOSPICIO</t>
+          <t>SERVICIO AGRICOLA Y GANADERO</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
@@ -6974,13 +6974,13 @@
         </is>
       </c>
       <c r="M107" s="2" t="n">
-        <v>1401.76</v>
+        <v>1851.11</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>1070620-6926-CM26</t>
+          <t>935934-87-CM26</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -6990,12 +6990,12 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
@@ -7005,12 +7005,12 @@
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>62.000.530-4</t>
+          <t>61.980.770-7</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>HOSPITAL DOCTOR ERNESTO TORRES GALDAMES</t>
+          <t>Zona de Bienestar Iquique</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
@@ -7020,12 +7020,12 @@
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA NENE SPA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
         <is>
-          <t>76.067.436-2</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K108" t="inlineStr"/>
@@ -7035,13 +7035,13 @@
         </is>
       </c>
       <c r="M108" s="2" t="n">
-        <v>6337.61</v>
+        <v>839.79</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>1350296-1342-CM26</t>
+          <t>1070620-3772-CM26</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -7051,12 +7051,12 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
@@ -7066,12 +7066,12 @@
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>65.228.694-1</t>
+          <t>62.000.530-4</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>HOSPITAL DE ALTO HOSPICIO</t>
+          <t>HOSPITAL DOCTOR ERNESTO TORRES GALDAMES</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
@@ -7096,13 +7096,13 @@
         </is>
       </c>
       <c r="M109" s="2" t="n">
-        <v>3290.43</v>
+        <v>3008.51</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>1350296-1387-CM26</t>
+          <t>1026727-110-CM26</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -7112,12 +7112,12 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
@@ -7127,12 +7127,12 @@
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>65.228.694-1</t>
+          <t>65.154.398-3</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>HOSPITAL DE ALTO HOSPICIO</t>
+          <t>CENTRO DE FORMACION TECNICA DE LA REGION DE TARAPACA</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
@@ -7157,7 +7157,2935 @@
         </is>
       </c>
       <c r="M110" s="2" t="n">
+        <v>5730.05</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>1070620-3965-CM26</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>2239-16-LR24</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>abr-2026</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>62.000.530-4</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>HOSPITAL DOCTOR ERNESTO TORRES GALDAMES</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA NENE SPA</t>
+        </is>
+      </c>
+      <c r="J111" t="inlineStr">
+        <is>
+          <t>76.067.436-2</t>
+        </is>
+      </c>
+      <c r="K111" t="inlineStr"/>
+      <c r="L111" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M111" s="2" t="n">
+        <v>2654.48</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>1070620-3970-CM26</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>2239-16-LR24</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>abr-2026</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>62.000.530-4</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>HOSPITAL DOCTOR ERNESTO TORRES GALDAMES</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA NENE SPA</t>
+        </is>
+      </c>
+      <c r="J112" t="inlineStr">
+        <is>
+          <t>76.067.436-2</t>
+        </is>
+      </c>
+      <c r="K112" t="inlineStr"/>
+      <c r="L112" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M112" s="2" t="n">
+        <v>2971.98</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>696217-36-CM26</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>2239-16-LR24</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>may-2026</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>61.935.400-1</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>MINISTERIO PUBLICO</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA NENE SPA</t>
+        </is>
+      </c>
+      <c r="J113" t="inlineStr">
+        <is>
+          <t>76.067.436-2</t>
+        </is>
+      </c>
+      <c r="K113" t="inlineStr"/>
+      <c r="L113" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M113" s="2" t="n">
+        <v>797.04</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>1077499-48-CM26</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>2239-16-LR24</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>may-2026</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>61.606.100-3</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD IQUIQUE</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>COMERCIAL RED OFFICE LIMITADA</t>
+        </is>
+      </c>
+      <c r="J114" t="inlineStr">
+        <is>
+          <t>77.012.870-6</t>
+        </is>
+      </c>
+      <c r="K114" t="inlineStr"/>
+      <c r="L114" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M114" s="2" t="n">
+        <v>1421.78</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>1355-15-CM26</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>2239-16-LR24</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>may-2026</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>61.002.007-0</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>Servicio de Registro Civil e Identificación</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>COMERCIALIZADORA SAN JERONIMO SPA</t>
+        </is>
+      </c>
+      <c r="J115" t="inlineStr">
+        <is>
+          <t>77.610.393-4</t>
+        </is>
+      </c>
+      <c r="K115" t="inlineStr"/>
+      <c r="L115" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M115" s="2" t="n">
+        <v>9123.34</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>1070620-4300-CM26</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>2239-16-LR24</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>may-2026</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>62.000.530-4</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>HOSPITAL DOCTOR ERNESTO TORRES GALDAMES</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA NENE SPA</t>
+        </is>
+      </c>
+      <c r="J116" t="inlineStr">
+        <is>
+          <t>76.067.436-2</t>
+        </is>
+      </c>
+      <c r="K116" t="inlineStr"/>
+      <c r="L116" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M116" s="2" t="n">
+        <v>4063.54</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>2013-788-CM26</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>2239-16-LR24</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>may-2026</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>70.777.500-9</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD ARTURO PRAT</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>INVERSIONES CORP PREMIER LTDA</t>
+        </is>
+      </c>
+      <c r="J117" t="inlineStr">
+        <is>
+          <t>76.473.108-5</t>
+        </is>
+      </c>
+      <c r="K117" t="inlineStr"/>
+      <c r="L117" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M117" s="2" t="n">
+        <v>3448.12</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>1426397-149-CM26</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>2239-16-LR24</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>may-2026</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>61.980.910-6</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>Servicio Local de Educación Pública Iquique</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA NENE SPA</t>
+        </is>
+      </c>
+      <c r="J118" t="inlineStr">
+        <is>
+          <t>76.067.436-2</t>
+        </is>
+      </c>
+      <c r="K118" t="inlineStr"/>
+      <c r="L118" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M118" s="2" t="n">
+        <v>27867.05</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>1070620-4588-CM26</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>2239-16-LR24</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>may-2026</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>62.000.530-4</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>HOSPITAL DOCTOR ERNESTO TORRES GALDAMES</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA NENE SPA</t>
+        </is>
+      </c>
+      <c r="J119" t="inlineStr">
+        <is>
+          <t>76.067.436-2</t>
+        </is>
+      </c>
+      <c r="K119" t="inlineStr"/>
+      <c r="L119" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M119" s="2" t="n">
+        <v>1717.38</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>1350296-953-CM26</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>2239-16-LR24</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>may-2026</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>65.228.694-1</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>HOSPITAL DE ALTO HOSPICIO</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA NENE SPA</t>
+        </is>
+      </c>
+      <c r="J120" t="inlineStr">
+        <is>
+          <t>76.067.436-2</t>
+        </is>
+      </c>
+      <c r="K120" t="inlineStr"/>
+      <c r="L120" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M120" s="2" t="n">
+        <v>2900.32</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>3349-159-CM26</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>2239-16-LR24</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>may-2026</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>65.283.230-K</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>Ejercito de Chile</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA NENE SPA</t>
+        </is>
+      </c>
+      <c r="J121" t="inlineStr">
+        <is>
+          <t>76.067.436-2</t>
+        </is>
+      </c>
+      <c r="K121" t="inlineStr"/>
+      <c r="L121" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M121" s="2" t="n">
+        <v>1338.38</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>1070620-5112-CM26</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>2239-16-LR24</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>jun-2026</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>62.000.530-4</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>HOSPITAL DOCTOR ERNESTO TORRES GALDAMES</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA NENE SPA</t>
+        </is>
+      </c>
+      <c r="J122" t="inlineStr">
+        <is>
+          <t>76.067.436-2</t>
+        </is>
+      </c>
+      <c r="K122" t="inlineStr"/>
+      <c r="L122" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M122" s="2" t="n">
+        <v>4394.29</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>1070620-5145-CM26</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>2239-16-LR24</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>jun-2026</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>62.000.530-4</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>HOSPITAL DOCTOR ERNESTO TORRES GALDAMES</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA NENE SPA</t>
+        </is>
+      </c>
+      <c r="J123" t="inlineStr">
+        <is>
+          <t>76.067.436-2</t>
+        </is>
+      </c>
+      <c r="K123" t="inlineStr"/>
+      <c r="L123" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M123" s="2" t="n">
+        <v>806.4299999999999</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>1350296-923-CM26</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>2239-16-LR24</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>jun-2026</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>65.228.694-1</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>HOSPITAL DE ALTO HOSPICIO</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr">
+        <is>
+          <t>COMERCIALIZADORA IGESCOM SPA</t>
+        </is>
+      </c>
+      <c r="J124" t="inlineStr">
+        <is>
+          <t>77.152.668-3</t>
+        </is>
+      </c>
+      <c r="K124" t="inlineStr"/>
+      <c r="L124" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M124" s="2" t="n">
+        <v>1288.94</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>948-72-CM26</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>2239-16-LR24</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>jun-2026</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>60.901.003-7</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>Secretaría Regional Ministerial de Educación de la Primera Región</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="I125" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA NENE SPA</t>
+        </is>
+      </c>
+      <c r="J125" t="inlineStr">
+        <is>
+          <t>76.067.436-2</t>
+        </is>
+      </c>
+      <c r="K125" t="inlineStr"/>
+      <c r="L125" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M125" s="2" t="n">
+        <v>783.7</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>1407-331-CM26</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>2239-16-LR24</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>jun-2026</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>61.004.002-0</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>Dirección Regional de Gendarmeria - Iquique</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA NENE SPA</t>
+        </is>
+      </c>
+      <c r="J126" t="inlineStr">
+        <is>
+          <t>76.067.436-2</t>
+        </is>
+      </c>
+      <c r="K126" t="inlineStr"/>
+      <c r="L126" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M126" s="2" t="n">
+        <v>1097.01</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>1057448-209-CM26</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>2239-16-LR24</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>jun-2026</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>61.606.100-3</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD IQUIQUE</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA NENE SPA</t>
+        </is>
+      </c>
+      <c r="J127" t="inlineStr">
+        <is>
+          <t>76.067.436-2</t>
+        </is>
+      </c>
+      <c r="K127" t="inlineStr"/>
+      <c r="L127" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M127" s="2" t="n">
+        <v>1133.72</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>1227-161-CM26</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>2239-16-LR24</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>jun-2026</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>60.804.002-1</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>DIRECCIÓN REGIONAL ADUANA DE IQUIQUE</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA NENE SPA</t>
+        </is>
+      </c>
+      <c r="J128" t="inlineStr">
+        <is>
+          <t>76.067.436-2</t>
+        </is>
+      </c>
+      <c r="K128" t="inlineStr"/>
+      <c r="L128" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M128" s="2" t="n">
+        <v>833.25</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>1346281-93-CM26</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>2239-16-LR24</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>jun-2026</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>62.000.970-9</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="I129" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA NENE SPA</t>
+        </is>
+      </c>
+      <c r="J129" t="inlineStr">
+        <is>
+          <t>76.067.436-2</t>
+        </is>
+      </c>
+      <c r="K129" t="inlineStr"/>
+      <c r="L129" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M129" s="2" t="n">
+        <v>818.53</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>548847-33-CM26</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>2239-16-LR24</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>jun-2026</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>61.979.440-0</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>Instituto de Prevision Social</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="I130" t="inlineStr">
+        <is>
+          <t>DIMERC S A</t>
+        </is>
+      </c>
+      <c r="J130" t="inlineStr">
+        <is>
+          <t>96.670.840-9</t>
+        </is>
+      </c>
+      <c r="K130" t="inlineStr"/>
+      <c r="L130" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M130" s="2" t="n">
+        <v>3171.11</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>707412-47-CM26</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>2239-16-LR24</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>jun-2026</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>70.574.900-0</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+        </is>
+      </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA NENE SPA</t>
+        </is>
+      </c>
+      <c r="J131" t="inlineStr">
+        <is>
+          <t>76.067.436-2</t>
+        </is>
+      </c>
+      <c r="K131" t="inlineStr"/>
+      <c r="L131" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M131" s="2" t="n">
+        <v>8179.49</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>1070620-5843-CM26</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>2239-16-LR24</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>jun-2026</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>62.000.530-4</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>HOSPITAL DOCTOR ERNESTO TORRES GALDAMES</t>
+        </is>
+      </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="I132" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA NENE SPA</t>
+        </is>
+      </c>
+      <c r="J132" t="inlineStr">
+        <is>
+          <t>76.067.436-2</t>
+        </is>
+      </c>
+      <c r="K132" t="inlineStr"/>
+      <c r="L132" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M132" s="2" t="n">
+        <v>4432.28</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>1350296-1137-CM26</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>2239-16-LR24</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>jun-2026</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>65.228.694-1</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>HOSPITAL DE ALTO HOSPICIO</t>
+        </is>
+      </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA NENE SPA</t>
+        </is>
+      </c>
+      <c r="J133" t="inlineStr">
+        <is>
+          <t>76.067.436-2</t>
+        </is>
+      </c>
+      <c r="K133" t="inlineStr"/>
+      <c r="L133" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M133" s="2" t="n">
+        <v>1081.22</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>1350296-1138-CM26</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>2239-16-LR24</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>jun-2026</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>65.228.694-1</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>HOSPITAL DE ALTO HOSPICIO</t>
+        </is>
+      </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="I134" t="inlineStr">
+        <is>
+          <t>DIMERC S A</t>
+        </is>
+      </c>
+      <c r="J134" t="inlineStr">
+        <is>
+          <t>96.670.840-9</t>
+        </is>
+      </c>
+      <c r="K134" t="inlineStr"/>
+      <c r="L134" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M134" s="2" t="n">
+        <v>1227.57</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>2013-1102-CM26</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>2239-16-LR24</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>jun-2026</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>70.777.500-9</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD ARTURO PRAT</t>
+        </is>
+      </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="I135" t="inlineStr">
+        <is>
+          <t>COMERCIAL RED OFFICE LIMITADA</t>
+        </is>
+      </c>
+      <c r="J135" t="inlineStr">
+        <is>
+          <t>77.012.870-6</t>
+        </is>
+      </c>
+      <c r="K135" t="inlineStr"/>
+      <c r="L135" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M135" s="2" t="n">
+        <v>9813.75</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>802-17-CM26</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>2239-16-LR24</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>72.396.000-2</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>CORP NACIONAL DE DESARROLLO INDIGENA</t>
+        </is>
+      </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA NENE SPA</t>
+        </is>
+      </c>
+      <c r="J136" t="inlineStr">
+        <is>
+          <t>76.067.436-2</t>
+        </is>
+      </c>
+      <c r="K136" t="inlineStr"/>
+      <c r="L136" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M136" s="2" t="n">
+        <v>3398.37</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>1070620-6258-CM26</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>2239-16-LR24</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>62.000.530-4</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>HOSPITAL DOCTOR ERNESTO TORRES GALDAMES</t>
+        </is>
+      </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="I137" t="inlineStr">
+        <is>
+          <t>COMERCIAL RED OFFICE LIMITADA</t>
+        </is>
+      </c>
+      <c r="J137" t="inlineStr">
+        <is>
+          <t>77.012.870-6</t>
+        </is>
+      </c>
+      <c r="K137" t="inlineStr"/>
+      <c r="L137" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M137" s="2" t="n">
+        <v>805</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>1346281-109-CM26</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>2239-16-LR24</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>62.000.970-9</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
+        </is>
+      </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="I138" t="inlineStr">
+        <is>
+          <t>DIMERC S A</t>
+        </is>
+      </c>
+      <c r="J138" t="inlineStr">
+        <is>
+          <t>96.670.840-9</t>
+        </is>
+      </c>
+      <c r="K138" t="inlineStr"/>
+      <c r="L138" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M138" s="2" t="n">
+        <v>1202.13</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>5690-95-CM26</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>2239-16-LR24</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>61.308.000-7</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>SERVICIO AGRICOLA Y GANADERO</t>
+        </is>
+      </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="I139" t="inlineStr">
+        <is>
+          <t>DIMERC S A</t>
+        </is>
+      </c>
+      <c r="J139" t="inlineStr">
+        <is>
+          <t>96.670.840-9</t>
+        </is>
+      </c>
+      <c r="K139" t="inlineStr"/>
+      <c r="L139" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M139" s="2" t="n">
+        <v>968.89</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>1350296-1197-CM26</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>2239-16-LR24</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>65.228.694-1</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>HOSPITAL DE ALTO HOSPICIO</t>
+        </is>
+      </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="I140" t="inlineStr">
+        <is>
+          <t>DIMERC S A</t>
+        </is>
+      </c>
+      <c r="J140" t="inlineStr">
+        <is>
+          <t>96.670.840-9</t>
+        </is>
+      </c>
+      <c r="K140" t="inlineStr"/>
+      <c r="L140" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M140" s="2" t="n">
+        <v>1401.76</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>1070620-6926-CM26</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>2239-16-LR24</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>62.000.530-4</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>HOSPITAL DOCTOR ERNESTO TORRES GALDAMES</t>
+        </is>
+      </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="I141" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA NENE SPA</t>
+        </is>
+      </c>
+      <c r="J141" t="inlineStr">
+        <is>
+          <t>76.067.436-2</t>
+        </is>
+      </c>
+      <c r="K141" t="inlineStr"/>
+      <c r="L141" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M141" s="2" t="n">
+        <v>6337.61</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>1350296-1342-CM26</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>2239-16-LR24</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>65.228.694-1</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>HOSPITAL DE ALTO HOSPICIO</t>
+        </is>
+      </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="I142" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA NENE SPA</t>
+        </is>
+      </c>
+      <c r="J142" t="inlineStr">
+        <is>
+          <t>76.067.436-2</t>
+        </is>
+      </c>
+      <c r="K142" t="inlineStr"/>
+      <c r="L142" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M142" s="2" t="n">
+        <v>3290.43</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>1350296-1387-CM26</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>2239-16-LR24</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>65.228.694-1</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>HOSPITAL DE ALTO HOSPICIO</t>
+        </is>
+      </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="I143" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA NENE SPA</t>
+        </is>
+      </c>
+      <c r="J143" t="inlineStr">
+        <is>
+          <t>76.067.436-2</t>
+        </is>
+      </c>
+      <c r="K143" t="inlineStr"/>
+      <c r="L143" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M143" s="2" t="n">
         <v>2705.47</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>845-78-CM26</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>2239-16-LR24</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>70.072.600-2</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
+        </is>
+      </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="I144" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA NENE SPA</t>
+        </is>
+      </c>
+      <c r="J144" t="inlineStr">
+        <is>
+          <t>76.067.436-2</t>
+        </is>
+      </c>
+      <c r="K144" t="inlineStr"/>
+      <c r="L144" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M144" s="2" t="n">
+        <v>13837.51</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>845-79-CM26</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>2239-16-LR24</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>70.072.600-2</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
+        </is>
+      </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="I145" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA NENE SPA</t>
+        </is>
+      </c>
+      <c r="J145" t="inlineStr">
+        <is>
+          <t>76.067.436-2</t>
+        </is>
+      </c>
+      <c r="K145" t="inlineStr"/>
+      <c r="L145" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M145" s="2" t="n">
+        <v>4688.17</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>1346281-117-CM26</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>2239-16-LR24</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>62.000.970-9</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
+        </is>
+      </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="I146" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA NENE SPA</t>
+        </is>
+      </c>
+      <c r="J146" t="inlineStr">
+        <is>
+          <t>76.067.436-2</t>
+        </is>
+      </c>
+      <c r="K146" t="inlineStr"/>
+      <c r="L146" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M146" s="2" t="n">
+        <v>1678.16</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>1070620-7279-CM26</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>2239-16-LR24</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>62.000.530-4</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>HOSPITAL DOCTOR ERNESTO TORRES GALDAMES</t>
+        </is>
+      </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="I147" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA NENE SPA</t>
+        </is>
+      </c>
+      <c r="J147" t="inlineStr">
+        <is>
+          <t>76.067.436-2</t>
+        </is>
+      </c>
+      <c r="K147" t="inlineStr"/>
+      <c r="L147" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M147" s="2" t="n">
+        <v>8301.370000000001</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>1070620-7312-CM26</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>2239-16-LR24</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>62.000.530-4</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>HOSPITAL DOCTOR ERNESTO TORRES GALDAMES</t>
+        </is>
+      </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="I148" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA NENE SPA</t>
+        </is>
+      </c>
+      <c r="J148" t="inlineStr">
+        <is>
+          <t>76.067.436-2</t>
+        </is>
+      </c>
+      <c r="K148" t="inlineStr"/>
+      <c r="L148" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M148" s="2" t="n">
+        <v>801.8099999999999</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>1417913-633-CM26</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>2239-16-LR24</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>70.938.800-2</t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>CORP MUNICIPAL DE DESARROLLO SOCIAL DE IQUIQUE</t>
+        </is>
+      </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="I149" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA NENE SPA</t>
+        </is>
+      </c>
+      <c r="J149" t="inlineStr">
+        <is>
+          <t>76.067.436-2</t>
+        </is>
+      </c>
+      <c r="K149" t="inlineStr"/>
+      <c r="L149" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M149" s="2" t="n">
+        <v>3378.41</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>1346281-129-CM26</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>2239-16-LR24</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>62.000.970-9</t>
+        </is>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
+        </is>
+      </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="I150" t="inlineStr">
+        <is>
+          <t>COMERCIALIZADORA CUARENTA Y UNO SPA</t>
+        </is>
+      </c>
+      <c r="J150" t="inlineStr">
+        <is>
+          <t>78.085.401-4</t>
+        </is>
+      </c>
+      <c r="K150" t="inlineStr"/>
+      <c r="L150" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M150" s="2" t="n">
+        <v>852.8</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>3159-131-CM26</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>2239-16-LR24</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>61.102.038-4</t>
+        </is>
+      </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
+        </is>
+      </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="I151" t="inlineStr">
+        <is>
+          <t>COMERCIALIZADORA CUARENTA Y UNO SPA</t>
+        </is>
+      </c>
+      <c r="J151" t="inlineStr">
+        <is>
+          <t>78.085.401-4</t>
+        </is>
+      </c>
+      <c r="K151" t="inlineStr"/>
+      <c r="L151" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M151" s="2" t="n">
+        <v>810.4</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>696217-103-CM26</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>2239-16-LR24</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>61.935.400-1</t>
+        </is>
+      </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>MINISTERIO PUBLICO</t>
+        </is>
+      </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="I152" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA NENE SPA</t>
+        </is>
+      </c>
+      <c r="J152" t="inlineStr">
+        <is>
+          <t>76.067.436-2</t>
+        </is>
+      </c>
+      <c r="K152" t="inlineStr"/>
+      <c r="L152" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M152" s="2" t="n">
+        <v>1399.74</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>3352-154-CM26</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>2239-16-LR24</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>61.101.024-9</t>
+        </is>
+      </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+        </is>
+      </c>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="I153" t="inlineStr">
+        <is>
+          <t>DIMERC S A</t>
+        </is>
+      </c>
+      <c r="J153" t="inlineStr">
+        <is>
+          <t>96.670.840-9</t>
+        </is>
+      </c>
+      <c r="K153" t="inlineStr"/>
+      <c r="L153" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M153" s="2" t="n">
+        <v>787.04</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>696217-109-CM26</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>2239-16-LR24</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>61.935.400-1</t>
+        </is>
+      </c>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>MINISTERIO PUBLICO</t>
+        </is>
+      </c>
+      <c r="H154" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="I154" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA NENE SPA</t>
+        </is>
+      </c>
+      <c r="J154" t="inlineStr">
+        <is>
+          <t>76.067.436-2</t>
+        </is>
+      </c>
+      <c r="K154" t="inlineStr"/>
+      <c r="L154" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M154" s="2" t="n">
+        <v>1695.89</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>1417913-666-CM26</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>2239-16-LR24</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>70.938.800-2</t>
+        </is>
+      </c>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>CORP MUNICIPAL DE DESARROLLO SOCIAL DE IQUIQUE</t>
+        </is>
+      </c>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="I155" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA NENE SPA</t>
+        </is>
+      </c>
+      <c r="J155" t="inlineStr">
+        <is>
+          <t>76.067.436-2</t>
+        </is>
+      </c>
+      <c r="K155" t="inlineStr"/>
+      <c r="L155" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M155" s="2" t="n">
+        <v>4057.08</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>1070620-8047-CM26</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>2239-16-LR24</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>62.000.530-4</t>
+        </is>
+      </c>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>HOSPITAL DOCTOR ERNESTO TORRES GALDAMES</t>
+        </is>
+      </c>
+      <c r="H156" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="I156" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA NENE SPA</t>
+        </is>
+      </c>
+      <c r="J156" t="inlineStr">
+        <is>
+          <t>76.067.436-2</t>
+        </is>
+      </c>
+      <c r="K156" t="inlineStr"/>
+      <c r="L156" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M156" s="2" t="n">
+        <v>11819.76</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>1350296-1585-CM26</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>2239-16-LR24</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>65.228.694-1</t>
+        </is>
+      </c>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>HOSPITAL DE ALTO HOSPICIO</t>
+        </is>
+      </c>
+      <c r="H157" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="I157" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA NENE SPA</t>
+        </is>
+      </c>
+      <c r="J157" t="inlineStr">
+        <is>
+          <t>76.067.436-2</t>
+        </is>
+      </c>
+      <c r="K157" t="inlineStr"/>
+      <c r="L157" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M157" s="2" t="n">
+        <v>777.5700000000001</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>1350296-1586-CM26</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>2239-16-LR24</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>65.228.694-1</t>
+        </is>
+      </c>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>HOSPITAL DE ALTO HOSPICIO</t>
+        </is>
+      </c>
+      <c r="H158" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="I158" t="inlineStr">
+        <is>
+          <t>MUÑOZ Y VILCHES LIMITADA</t>
+        </is>
+      </c>
+      <c r="J158" t="inlineStr">
+        <is>
+          <t>77.008.207-2</t>
+        </is>
+      </c>
+      <c r="K158" t="inlineStr"/>
+      <c r="L158" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M158" s="2" t="n">
+        <v>1900.92</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/articulos-de-escritorio-y-papeleria/tarapaca.xlsx
+++ b/docs/oc-regiones/articulos-de-escritorio-y-papeleria/tarapaca.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M158"/>
+  <dimension ref="A1:M170"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -697,7 +697,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>845-121-CM25</t>
+          <t>845-122-CM25</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>10608.84</v>
+        <v>3064</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>845-122-CM25</t>
+          <t>845-121-CM25</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -813,7 +813,7 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>3064</v>
+        <v>10608.84</v>
       </c>
     </row>
     <row r="7">
@@ -1063,7 +1063,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2013-1142-CM25</t>
+          <t>1417913-212-CM25</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1088,12 +1088,12 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>70.777.500-9</t>
+          <t>70.938.800-2</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD ARTURO PRAT</t>
+          <t>CORP MUNICIPAL DE DESARROLLO SOCIAL DE IQUIQUE</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1103,12 +1103,12 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE LIMITADA</t>
+          <t>COMERCIALIZADORA IGESCOM SPA</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>77.012.870-6</t>
+          <t>77.152.668-3</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
@@ -1118,13 +1118,13 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>7696.6</v>
+        <v>1102.98</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>1417913-212-CM25</t>
+          <t>2013-1142-CM25</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1149,12 +1149,12 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>70.938.800-2</t>
+          <t>70.777.500-9</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>CORP MUNICIPAL DE DESARROLLO SOCIAL DE IQUIQUE</t>
+          <t>UNIVERSIDAD ARTURO PRAT</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1164,12 +1164,12 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA IGESCOM SPA</t>
+          <t>COMERCIAL RED OFFICE LIMITADA</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>77.152.668-3</t>
+          <t>77.012.870-6</t>
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
@@ -1179,7 +1179,7 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>1102.98</v>
+        <v>7696.6</v>
       </c>
     </row>
     <row r="13">
@@ -2588,7 +2588,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>696217-121-CM25</t>
+          <t>1350296-2287-CM25</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2608,17 +2608,17 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>61.935.400-1</t>
+          <t>65.228.694-1</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>MINISTERIO PUBLICO</t>
+          <t>HOSPITAL DE ALTO HOSPICIO</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -2643,13 +2643,13 @@
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>966.9</v>
+        <v>1744.49</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>1350296-2287-CM25</t>
+          <t>696217-121-CM25</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2669,17 +2669,17 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>65.228.694-1</t>
+          <t>61.935.400-1</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>HOSPITAL DE ALTO HOSPICIO</t>
+          <t>MINISTERIO PUBLICO</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -2704,7 +2704,7 @@
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>1744.49</v>
+        <v>966.9</v>
       </c>
     </row>
     <row r="38">
@@ -2862,7 +2862,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS I ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -2984,7 +2984,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>CORPORACION MUNICIPAL DE DESARROLLO SOCIAL POZO AL</t>
+          <t>CORP MUNICIPAL DE DESARROLLO SOCIAL DE POZO ALMONTE</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -3228,7 +3228,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS I ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -3686,7 +3686,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>548847-88-CM25</t>
+          <t>845-220-CM25</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -3706,17 +3706,17 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>61.979.440-0</t>
+          <t>70.072.600-2</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Instituto de Prevision Social</t>
+          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -3726,12 +3726,12 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE LIMITADA</t>
+          <t>DISTRIBUIDORA NENE SPA</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>77.012.870-6</t>
+          <t>76.067.436-2</t>
         </is>
       </c>
       <c r="K54" t="inlineStr"/>
@@ -3741,13 +3741,13 @@
         </is>
       </c>
       <c r="M54" s="2" t="n">
-        <v>1368.37</v>
+        <v>11162.18</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>3145-686-CM25</t>
+          <t>548847-88-CM25</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -3772,12 +3772,12 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>61.103.023-1</t>
+          <t>61.979.440-0</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Iª Brigada Aérea</t>
+          <t>INSTITUTO DE PREVISION SOCIAL</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -3787,12 +3787,12 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA NENE SPA</t>
+          <t>COMERCIAL RED OFFICE LIMITADA</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>76.067.436-2</t>
+          <t>77.012.870-6</t>
         </is>
       </c>
       <c r="K55" t="inlineStr"/>
@@ -3802,13 +3802,13 @@
         </is>
       </c>
       <c r="M55" s="2" t="n">
-        <v>4420.53</v>
+        <v>1368.37</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>845-222-CM25</t>
+          <t>3145-686-CM25</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -3828,17 +3828,17 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>70.072.600-2</t>
+          <t>61.103.023-1</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
+          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -3863,13 +3863,13 @@
         </is>
       </c>
       <c r="M56" s="2" t="n">
-        <v>2009.47</v>
+        <v>4420.53</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>845-220-CM25</t>
+          <t>845-222-CM25</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -3924,7 +3924,7 @@
         </is>
       </c>
       <c r="M57" s="2" t="n">
-        <v>11162.18</v>
+        <v>2009.47</v>
       </c>
     </row>
     <row r="58">
@@ -4021,7 +4021,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Servicio de Registro Civil e Identificación</t>
+          <t>SERVICIO DE REGISTRO CIVIL E IDENTIFICACION</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -4143,7 +4143,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Departamento Provincial de Educación Iquique</t>
+          <t>SUBSECRETARIA DEL MINISTERIO DE EDUCACION PUBLICA</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -4235,7 +4235,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>1350296-22-CM26</t>
+          <t>1350296-21-CM26</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -4290,13 +4290,13 @@
         </is>
       </c>
       <c r="M63" s="2" t="n">
-        <v>6508.96</v>
+        <v>2007.61</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>1350296-21-CM26</t>
+          <t>1350296-22-CM26</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -4351,7 +4351,7 @@
         </is>
       </c>
       <c r="M64" s="2" t="n">
-        <v>2007.61</v>
+        <v>6508.96</v>
       </c>
     </row>
     <row r="65">
@@ -4479,7 +4479,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>1070620-732-CM26</t>
+          <t>1227-10-CM26</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -4504,12 +4504,12 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>62.000.530-4</t>
+          <t>60.804.002-1</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>HOSPITAL DOCTOR ERNESTO TORRES GALDAMES</t>
+          <t>SERVICIO NACIONAL DE ADUANAS</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -4534,13 +4534,13 @@
         </is>
       </c>
       <c r="M67" s="2" t="n">
-        <v>7767.17</v>
+        <v>1782.34</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2174-2-CM26</t>
+          <t>1070620-732-CM26</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -4565,12 +4565,12 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>60.301.001-9</t>
+          <t>62.000.530-4</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
+          <t>HOSPITAL DOCTOR ERNESTO TORRES GALDAMES</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -4580,12 +4580,12 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>DISTRIBUIDORA NENE SPA</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>76.067.436-2</t>
         </is>
       </c>
       <c r="K68" t="inlineStr"/>
@@ -4595,13 +4595,13 @@
         </is>
       </c>
       <c r="M68" s="2" t="n">
-        <v>9561.139999999999</v>
+        <v>7767.17</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>1227-10-CM26</t>
+          <t>2174-2-CM26</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -4626,12 +4626,12 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>60.804.002-1</t>
+          <t>60.301.001-9</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>DIRECCIÓN REGIONAL ADUANA DE IQUIQUE</t>
+          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -4641,12 +4641,12 @@
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA NENE SPA</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>76.067.436-2</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K69" t="inlineStr"/>
@@ -4656,13 +4656,13 @@
         </is>
       </c>
       <c r="M69" s="2" t="n">
-        <v>1782.34</v>
+        <v>9561.139999999999</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>1091793-13-CM26</t>
+          <t>1426397-13-CM26</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -4677,7 +4677,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2026-01-20</t>
+          <t>2026-01-29</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -4687,12 +4687,12 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>62.000.710-2</t>
+          <t>61.980.910-6</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>INSTITUTO NACIONAL DE DESARROLLO SUSTENTABLE DE LA</t>
+          <t>Servicio Local de Educación Pública Iquique</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -4702,12 +4702,12 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>COMERCIAL RED OFFICE LIMITADA</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>77.012.870-6</t>
         </is>
       </c>
       <c r="K70" t="inlineStr"/>
@@ -4717,13 +4717,13 @@
         </is>
       </c>
       <c r="M70" s="2" t="n">
-        <v>1169.1</v>
+        <v>2563.32</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>1426397-13-CM26</t>
+          <t>1426397-14-CM26</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -4763,12 +4763,12 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE LIMITADA</t>
+          <t>BARDANE SPA</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>77.012.870-6</t>
+          <t>77.205.722-9</t>
         </is>
       </c>
       <c r="K71" t="inlineStr"/>
@@ -4778,13 +4778,13 @@
         </is>
       </c>
       <c r="M71" s="2" t="n">
-        <v>2563.32</v>
+        <v>2066.95</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>1426397-14-CM26</t>
+          <t>838102-17-CM26</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -4794,12 +4794,12 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2026-01-29</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -4809,12 +4809,12 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>61.980.910-6</t>
+          <t>73.923.800-5</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Servicio Local de Educación Pública Iquique</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -4824,12 +4824,12 @@
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>BARDANE SPA</t>
+          <t>DISTRIBUIDORA NENE SPA</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>77.205.722-9</t>
+          <t>76.067.436-2</t>
         </is>
       </c>
       <c r="K72" t="inlineStr"/>
@@ -4839,13 +4839,13 @@
         </is>
       </c>
       <c r="M72" s="2" t="n">
-        <v>2066.95</v>
+        <v>909.05</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>838102-17-CM26</t>
+          <t>1057448-20-CM26</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -4870,12 +4870,12 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>73.923.800-5</t>
+          <t>61.606.100-3</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Zona Bienestar "Iquique" Bienestar Social</t>
+          <t>SERVICIO DE SALUD IQUIQUE</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -4900,13 +4900,13 @@
         </is>
       </c>
       <c r="M73" s="2" t="n">
-        <v>909.05</v>
+        <v>5553.82</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>1057448-20-CM26</t>
+          <t>838102-20-CM26</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -4921,7 +4921,7 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -4931,12 +4931,12 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>61.606.100-3</t>
+          <t>73.923.800-5</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD IQUIQUE</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -4946,12 +4946,12 @@
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA NENE SPA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>76.067.436-2</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K74" t="inlineStr"/>
@@ -4961,13 +4961,13 @@
         </is>
       </c>
       <c r="M74" s="2" t="n">
-        <v>5553.82</v>
+        <v>860.51</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>838102-20-CM26</t>
+          <t>1417913-83-CM26</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -4982,22 +4982,22 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>73.923.800-5</t>
+          <t>70.938.800-2</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Zona Bienestar "Iquique" Bienestar Social</t>
+          <t>CORP MUNICIPAL DE DESARROLLO SOCIAL DE IQUIQUE</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -5007,12 +5007,12 @@
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>DISTRIBUIDORA NENE SPA</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>76.067.436-2</t>
         </is>
       </c>
       <c r="K75" t="inlineStr"/>
@@ -5022,7 +5022,7 @@
         </is>
       </c>
       <c r="M75" s="2" t="n">
-        <v>860.51</v>
+        <v>52995.67</v>
       </c>
     </row>
     <row r="76">
@@ -5119,7 +5119,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>CENTRO DE ABASTECIMIENTO (I)</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -5180,7 +5180,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>DIRECCIÓN REGIONAL ADUANA DE IQUIQUE</t>
+          <t>SERVICIO NACIONAL DE ADUANAS</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -5546,7 +5546,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -5607,7 +5607,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PROTECCIÓN ESPECIALIZADA A LA</t>
+          <t>SERVICIO NACIONAL DE PROTECCIÓN ESPECIALIZADA A LA NIÑEZ Y ADOLESCENCI</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -5821,7 +5821,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>1407-118-CM26</t>
+          <t>1070620-2522-CM26</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -5846,12 +5846,12 @@
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>61.004.002-0</t>
+          <t>62.000.530-4</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Iquique</t>
+          <t>HOSPITAL DOCTOR ERNESTO TORRES GALDAMES</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -5861,12 +5861,12 @@
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>DISTRIBUIDORA NENE SPA</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>76.067.436-2</t>
         </is>
       </c>
       <c r="K89" t="inlineStr"/>
@@ -5876,13 +5876,13 @@
         </is>
       </c>
       <c r="M89" s="2" t="n">
-        <v>1139.89</v>
+        <v>1588.97</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>1070620-2522-CM26</t>
+          <t>1407-118-CM26</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -5907,12 +5907,12 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>62.000.530-4</t>
+          <t>61.004.002-0</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>HOSPITAL DOCTOR ERNESTO TORRES GALDAMES</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
@@ -5922,12 +5922,12 @@
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA NENE SPA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>76.067.436-2</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K90" t="inlineStr"/>
@@ -5937,7 +5937,7 @@
         </is>
       </c>
       <c r="M90" s="2" t="n">
-        <v>1588.97</v>
+        <v>1139.89</v>
       </c>
     </row>
     <row r="91">
@@ -5973,7 +5973,7 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>EJERCITO DE CHILE ESCUELA CABALLERIA QUI</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
@@ -6034,7 +6034,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -6126,7 +6126,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>1346281-48-CM26</t>
+          <t>1079967-130-CM26</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -6151,12 +6151,12 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>62.000.970-9</t>
+          <t>60.505.102-2</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
@@ -6166,12 +6166,12 @@
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>MALMO S.A.</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>76.195.558-6</t>
         </is>
       </c>
       <c r="K94" t="inlineStr"/>
@@ -6181,13 +6181,13 @@
         </is>
       </c>
       <c r="M94" s="2" t="n">
-        <v>859.85</v>
+        <v>31748.88</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>3352-49-CM26</t>
+          <t>1346281-50-CM26</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -6212,12 +6212,12 @@
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>61.101.024-9</t>
+          <t>62.000.970-9</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>EJERCITO DE CHILE ESCUELA CABALLERIA QUI</t>
+          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
@@ -6227,12 +6227,12 @@
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>MALMO S.A.</t>
+          <t>DISTRIBUIDORA NENE SPA</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>76.195.558-6</t>
+          <t>76.067.436-2</t>
         </is>
       </c>
       <c r="K95" t="inlineStr"/>
@@ -6242,13 +6242,13 @@
         </is>
       </c>
       <c r="M95" s="2" t="n">
-        <v>1475.02</v>
+        <v>753.52</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>1346281-50-CM26</t>
+          <t>1346281-48-CM26</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -6288,12 +6288,12 @@
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA NENE SPA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>76.067.436-2</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K96" t="inlineStr"/>
@@ -6303,13 +6303,13 @@
         </is>
       </c>
       <c r="M96" s="2" t="n">
-        <v>753.52</v>
+        <v>859.85</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>1079967-130-CM26</t>
+          <t>3352-49-CM26</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -6334,12 +6334,12 @@
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>60.505.102-2</t>
+          <t>61.101.024-9</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS I ZONA</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -6364,7 +6364,7 @@
         </is>
       </c>
       <c r="M97" s="2" t="n">
-        <v>31748.88</v>
+        <v>1475.02</v>
       </c>
     </row>
     <row r="98">
@@ -6400,7 +6400,7 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Estado Mayor Conjunto</t>
+          <t>ESTADO MAYOR CONJUNTO</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
@@ -6431,7 +6431,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>1070620-3155-CM26</t>
+          <t>1070620-3123-CM26</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -6471,12 +6471,12 @@
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA NENE SPA</t>
+          <t>IMPORTADORA HEVIA SPA</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>76.067.436-2</t>
+          <t>76.872.717-1</t>
         </is>
       </c>
       <c r="K99" t="inlineStr"/>
@@ -6486,13 +6486,13 @@
         </is>
       </c>
       <c r="M99" s="2" t="n">
-        <v>775.48</v>
+        <v>983.75</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>1070620-3123-CM26</t>
+          <t>1070620-3155-CM26</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -6532,12 +6532,12 @@
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>IMPORTADORA HEVIA SPA</t>
+          <t>DISTRIBUIDORA NENE SPA</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>76.872.717-1</t>
+          <t>76.067.436-2</t>
         </is>
       </c>
       <c r="K100" t="inlineStr"/>
@@ -6547,7 +6547,7 @@
         </is>
       </c>
       <c r="M100" s="2" t="n">
-        <v>983.75</v>
+        <v>775.48</v>
       </c>
     </row>
     <row r="101">
@@ -6583,7 +6583,7 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Instituto de Prevision Social</t>
+          <t>INSTITUTO DE PREVISION SOCIAL</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
@@ -6766,7 +6766,7 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>EJERCITO DE CHILE ESCUELA CABALLERIA QUI</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
@@ -6919,7 +6919,7 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>5690-47-CM26</t>
+          <t>1417913-205-CM26</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -6934,22 +6934,22 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>61.308.000-7</t>
+          <t>70.938.800-2</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>SERVICIO AGRICOLA Y GANADERO</t>
+          <t>CORP MUNICIPAL DE DESARROLLO SOCIAL DE IQUIQUE</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
@@ -6959,12 +6959,12 @@
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>DISTRIBUIDORA NENE SPA</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>76.067.436-2</t>
         </is>
       </c>
       <c r="K107" t="inlineStr"/>
@@ -6974,13 +6974,13 @@
         </is>
       </c>
       <c r="M107" s="2" t="n">
-        <v>1851.11</v>
+        <v>19400.21</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>935934-87-CM26</t>
+          <t>5690-47-CM26</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -6995,7 +6995,7 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
@@ -7005,12 +7005,12 @@
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>61.980.770-7</t>
+          <t>61.308.000-7</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Zona de Bienestar Iquique</t>
+          <t>SERVICIO AGRICOLA Y GANADERO</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
@@ -7035,13 +7035,13 @@
         </is>
       </c>
       <c r="M108" s="2" t="n">
-        <v>839.79</v>
+        <v>1851.11</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>1070620-3772-CM26</t>
+          <t>935934-87-CM26</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -7056,7 +7056,7 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
@@ -7066,12 +7066,12 @@
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>62.000.530-4</t>
+          <t>61.980.770-7</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>HOSPITAL DOCTOR ERNESTO TORRES GALDAMES</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
@@ -7081,12 +7081,12 @@
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA NENE SPA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
         <is>
-          <t>76.067.436-2</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K109" t="inlineStr"/>
@@ -7096,13 +7096,13 @@
         </is>
       </c>
       <c r="M109" s="2" t="n">
-        <v>3008.51</v>
+        <v>839.79</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>1026727-110-CM26</t>
+          <t>1070620-3772-CM26</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -7117,7 +7117,7 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
@@ -7127,12 +7127,12 @@
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>65.154.398-3</t>
+          <t>62.000.530-4</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>CENTRO DE FORMACION TECNICA DE LA REGION DE TARAPACA</t>
+          <t>HOSPITAL DOCTOR ERNESTO TORRES GALDAMES</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
@@ -7157,13 +7157,13 @@
         </is>
       </c>
       <c r="M110" s="2" t="n">
-        <v>5730.05</v>
+        <v>3008.51</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>1070620-3965-CM26</t>
+          <t>1026727-110-CM26</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -7178,7 +7178,7 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
@@ -7188,12 +7188,12 @@
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>62.000.530-4</t>
+          <t>65.154.398-3</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>HOSPITAL DOCTOR ERNESTO TORRES GALDAMES</t>
+          <t>CENTRO DE FORMACION TECNICA DE LA REGION DE TARAPACA</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
@@ -7218,13 +7218,13 @@
         </is>
       </c>
       <c r="M111" s="2" t="n">
-        <v>2654.48</v>
+        <v>5730.05</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>1070620-3970-CM26</t>
+          <t>1070620-3965-CM26</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -7279,13 +7279,13 @@
         </is>
       </c>
       <c r="M112" s="2" t="n">
-        <v>2971.98</v>
+        <v>2654.48</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>696217-36-CM26</t>
+          <t>1070620-3970-CM26</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -7295,27 +7295,27 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>61.935.400-1</t>
+          <t>62.000.530-4</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>MINISTERIO PUBLICO</t>
+          <t>HOSPITAL DOCTOR ERNESTO TORRES GALDAMES</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
@@ -7340,13 +7340,13 @@
         </is>
       </c>
       <c r="M113" s="2" t="n">
-        <v>797.04</v>
+        <v>2971.98</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>1077499-48-CM26</t>
+          <t>696217-36-CM26</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -7366,17 +7366,17 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>61.606.100-3</t>
+          <t>61.935.400-1</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD IQUIQUE</t>
+          <t>MINISTERIO PUBLICO</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
@@ -7386,12 +7386,12 @@
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE LIMITADA</t>
+          <t>DISTRIBUIDORA NENE SPA</t>
         </is>
       </c>
       <c r="J114" t="inlineStr">
         <is>
-          <t>77.012.870-6</t>
+          <t>76.067.436-2</t>
         </is>
       </c>
       <c r="K114" t="inlineStr"/>
@@ -7401,13 +7401,13 @@
         </is>
       </c>
       <c r="M114" s="2" t="n">
-        <v>1421.78</v>
+        <v>797.04</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>1355-15-CM26</t>
+          <t>1077499-48-CM26</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -7422,7 +7422,7 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
@@ -7432,12 +7432,12 @@
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>61.002.007-0</t>
+          <t>61.606.100-3</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Servicio de Registro Civil e Identificación</t>
+          <t>SERVICIO DE SALUD IQUIQUE</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
@@ -7447,12 +7447,12 @@
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA SAN JERONIMO SPA</t>
+          <t>COMERCIAL RED OFFICE LIMITADA</t>
         </is>
       </c>
       <c r="J115" t="inlineStr">
         <is>
-          <t>77.610.393-4</t>
+          <t>77.012.870-6</t>
         </is>
       </c>
       <c r="K115" t="inlineStr"/>
@@ -7462,7 +7462,7 @@
         </is>
       </c>
       <c r="M115" s="2" t="n">
-        <v>9123.34</v>
+        <v>1421.78</v>
       </c>
     </row>
     <row r="116">
@@ -7529,7 +7529,7 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>2013-788-CM26</t>
+          <t>1355-15-CM26</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -7544,22 +7544,22 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>70.777.500-9</t>
+          <t>61.002.007-0</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD ARTURO PRAT</t>
+          <t>SERVICIO DE REGISTRO CIVIL E IDENTIFICACION</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
@@ -7569,12 +7569,12 @@
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>INVERSIONES CORP PREMIER LTDA</t>
+          <t>COMERCIALIZADORA SAN JERONIMO SPA</t>
         </is>
       </c>
       <c r="J117" t="inlineStr">
         <is>
-          <t>76.473.108-5</t>
+          <t>77.610.393-4</t>
         </is>
       </c>
       <c r="K117" t="inlineStr"/>
@@ -7584,13 +7584,13 @@
         </is>
       </c>
       <c r="M117" s="2" t="n">
-        <v>3448.12</v>
+        <v>9123.34</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>1426397-149-CM26</t>
+          <t>2013-788-CM26</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -7610,17 +7610,17 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>61.980.910-6</t>
+          <t>70.777.500-9</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Servicio Local de Educación Pública Iquique</t>
+          <t>UNIVERSIDAD ARTURO PRAT</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
@@ -7630,12 +7630,12 @@
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA NENE SPA</t>
+          <t>Inversiones Corp Premier Ltda</t>
         </is>
       </c>
       <c r="J118" t="inlineStr">
         <is>
-          <t>76.067.436-2</t>
+          <t>76.473.108-5</t>
         </is>
       </c>
       <c r="K118" t="inlineStr"/>
@@ -7645,13 +7645,13 @@
         </is>
       </c>
       <c r="M118" s="2" t="n">
-        <v>27867.05</v>
+        <v>3448.12</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>1070620-4588-CM26</t>
+          <t>1426397-149-CM26</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -7666,7 +7666,7 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
@@ -7676,12 +7676,12 @@
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>62.000.530-4</t>
+          <t>61.980.910-6</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>HOSPITAL DOCTOR ERNESTO TORRES GALDAMES</t>
+          <t>Servicio Local de Educación Pública Iquique</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
@@ -7706,13 +7706,13 @@
         </is>
       </c>
       <c r="M119" s="2" t="n">
-        <v>1717.38</v>
+        <v>27867.05</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>1350296-953-CM26</t>
+          <t>1070620-4588-CM26</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -7727,7 +7727,7 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
@@ -7737,12 +7737,12 @@
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>65.228.694-1</t>
+          <t>62.000.530-4</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>HOSPITAL DE ALTO HOSPICIO</t>
+          <t>HOSPITAL DOCTOR ERNESTO TORRES GALDAMES</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
@@ -7767,13 +7767,13 @@
         </is>
       </c>
       <c r="M120" s="2" t="n">
-        <v>2900.32</v>
+        <v>1717.38</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>3349-159-CM26</t>
+          <t>1305552-58-CM26</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -7788,7 +7788,7 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
@@ -7798,12 +7798,12 @@
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>65.283.230-K</t>
+          <t>61.981.030-9</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA TAMARUGAL</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
@@ -7813,12 +7813,12 @@
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA NENE SPA</t>
+          <t>EVENTAIL SPA</t>
         </is>
       </c>
       <c r="J121" t="inlineStr">
         <is>
-          <t>76.067.436-2</t>
+          <t>76.710.414-6</t>
         </is>
       </c>
       <c r="K121" t="inlineStr"/>
@@ -7828,13 +7828,13 @@
         </is>
       </c>
       <c r="M121" s="2" t="n">
-        <v>1338.38</v>
+        <v>2940.96</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>1070620-5112-CM26</t>
+          <t>1350296-953-CM26</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -7844,12 +7844,12 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
@@ -7859,12 +7859,12 @@
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>62.000.530-4</t>
+          <t>65.228.694-1</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>HOSPITAL DOCTOR ERNESTO TORRES GALDAMES</t>
+          <t>HOSPITAL DE ALTO HOSPICIO</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
@@ -7889,13 +7889,13 @@
         </is>
       </c>
       <c r="M122" s="2" t="n">
-        <v>4394.29</v>
+        <v>2900.32</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>1070620-5145-CM26</t>
+          <t>1305552-57-CM26</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -7905,12 +7905,12 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
@@ -7920,12 +7920,12 @@
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>62.000.530-4</t>
+          <t>61.981.030-9</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>HOSPITAL DOCTOR ERNESTO TORRES GALDAMES</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA TAMARUGAL</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
@@ -7950,13 +7950,13 @@
         </is>
       </c>
       <c r="M123" s="2" t="n">
-        <v>806.4299999999999</v>
+        <v>5275.36</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>1350296-923-CM26</t>
+          <t>3349-159-CM26</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -7966,12 +7966,12 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
@@ -7981,12 +7981,12 @@
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>65.228.694-1</t>
+          <t>65.283.230-K</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>HOSPITAL DE ALTO HOSPICIO</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
@@ -7996,12 +7996,12 @@
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA IGESCOM SPA</t>
+          <t>DISTRIBUIDORA NENE SPA</t>
         </is>
       </c>
       <c r="J124" t="inlineStr">
         <is>
-          <t>77.152.668-3</t>
+          <t>76.067.436-2</t>
         </is>
       </c>
       <c r="K124" t="inlineStr"/>
@@ -8011,13 +8011,13 @@
         </is>
       </c>
       <c r="M124" s="2" t="n">
-        <v>1288.94</v>
+        <v>1338.38</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>948-72-CM26</t>
+          <t>1070620-5112-CM26</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -8032,7 +8032,7 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
@@ -8042,12 +8042,12 @@
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>60.901.003-7</t>
+          <t>62.000.530-4</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Secretaría Regional Ministerial de Educación de la Primera Región</t>
+          <t>HOSPITAL DOCTOR ERNESTO TORRES GALDAMES</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
@@ -8072,13 +8072,13 @@
         </is>
       </c>
       <c r="M125" s="2" t="n">
-        <v>783.7</v>
+        <v>4394.29</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>1407-331-CM26</t>
+          <t>1070620-5145-CM26</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -8093,7 +8093,7 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
@@ -8103,12 +8103,12 @@
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>61.004.002-0</t>
+          <t>62.000.530-4</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Iquique</t>
+          <t>HOSPITAL DOCTOR ERNESTO TORRES GALDAMES</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
@@ -8133,13 +8133,13 @@
         </is>
       </c>
       <c r="M126" s="2" t="n">
-        <v>1097.01</v>
+        <v>806.4299999999999</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>1057448-209-CM26</t>
+          <t>1350296-923-CM26</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -8154,7 +8154,7 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
@@ -8164,12 +8164,12 @@
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>61.606.100-3</t>
+          <t>65.228.694-1</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD IQUIQUE</t>
+          <t>HOSPITAL DE ALTO HOSPICIO</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
@@ -8179,12 +8179,12 @@
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA NENE SPA</t>
+          <t>COMERCIALIZADORA IGESCOM SPA</t>
         </is>
       </c>
       <c r="J127" t="inlineStr">
         <is>
-          <t>76.067.436-2</t>
+          <t>77.152.668-3</t>
         </is>
       </c>
       <c r="K127" t="inlineStr"/>
@@ -8194,13 +8194,13 @@
         </is>
       </c>
       <c r="M127" s="2" t="n">
-        <v>1133.72</v>
+        <v>1288.94</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>1227-161-CM26</t>
+          <t>1407-331-CM26</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -8215,7 +8215,7 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
@@ -8225,12 +8225,12 @@
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>60.804.002-1</t>
+          <t>61.004.002-0</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>DIRECCIÓN REGIONAL ADUANA DE IQUIQUE</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
@@ -8255,13 +8255,13 @@
         </is>
       </c>
       <c r="M128" s="2" t="n">
-        <v>833.25</v>
+        <v>1097.01</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>1346281-93-CM26</t>
+          <t>948-72-CM26</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -8276,7 +8276,7 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
@@ -8286,12 +8286,12 @@
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>62.000.970-9</t>
+          <t>60.901.003-7</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
+          <t>SUBSECRETARIA DEL MINISTERIO DE EDUCACION PUBLICA</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
@@ -8316,13 +8316,13 @@
         </is>
       </c>
       <c r="M129" s="2" t="n">
-        <v>818.53</v>
+        <v>783.7</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>548847-33-CM26</t>
+          <t>1057448-209-CM26</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -8337,7 +8337,7 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
@@ -8347,12 +8347,12 @@
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>61.979.440-0</t>
+          <t>61.606.100-3</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Instituto de Prevision Social</t>
+          <t>SERVICIO DE SALUD IQUIQUE</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
@@ -8362,12 +8362,12 @@
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>DISTRIBUIDORA NENE SPA</t>
         </is>
       </c>
       <c r="J130" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>76.067.436-2</t>
         </is>
       </c>
       <c r="K130" t="inlineStr"/>
@@ -8377,13 +8377,13 @@
         </is>
       </c>
       <c r="M130" s="2" t="n">
-        <v>3171.11</v>
+        <v>1133.72</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>707412-47-CM26</t>
+          <t>1227-161-CM26</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -8398,22 +8398,22 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>60.804.002-1</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>SERVICIO NACIONAL DE ADUANAS</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
@@ -8438,13 +8438,13 @@
         </is>
       </c>
       <c r="M131" s="2" t="n">
-        <v>8179.49</v>
+        <v>833.25</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>1070620-5843-CM26</t>
+          <t>1346281-93-CM26</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -8459,7 +8459,7 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
@@ -8469,12 +8469,12 @@
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>62.000.530-4</t>
+          <t>62.000.970-9</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>HOSPITAL DOCTOR ERNESTO TORRES GALDAMES</t>
+          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
@@ -8499,13 +8499,13 @@
         </is>
       </c>
       <c r="M132" s="2" t="n">
-        <v>4432.28</v>
+        <v>818.53</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>1350296-1137-CM26</t>
+          <t>548847-33-CM26</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -8520,7 +8520,7 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
@@ -8530,12 +8530,12 @@
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>65.228.694-1</t>
+          <t>61.979.440-0</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>HOSPITAL DE ALTO HOSPICIO</t>
+          <t>INSTITUTO DE PREVISION SOCIAL</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
@@ -8545,12 +8545,12 @@
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA NENE SPA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J133" t="inlineStr">
         <is>
-          <t>76.067.436-2</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K133" t="inlineStr"/>
@@ -8560,13 +8560,13 @@
         </is>
       </c>
       <c r="M133" s="2" t="n">
-        <v>1081.22</v>
+        <v>3171.11</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>1350296-1138-CM26</t>
+          <t>707412-47-CM26</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -8581,22 +8581,22 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>65.228.694-1</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>HOSPITAL DE ALTO HOSPICIO</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>DISTRIBUIDORA NENE SPA</t>
         </is>
       </c>
       <c r="J134" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>76.067.436-2</t>
         </is>
       </c>
       <c r="K134" t="inlineStr"/>
@@ -8621,13 +8621,13 @@
         </is>
       </c>
       <c r="M134" s="2" t="n">
-        <v>1227.57</v>
+        <v>8179.49</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>2013-1102-CM26</t>
+          <t>1070620-5843-CM26</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -8642,22 +8642,22 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>70.777.500-9</t>
+          <t>62.000.530-4</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD ARTURO PRAT</t>
+          <t>HOSPITAL DOCTOR ERNESTO TORRES GALDAMES</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
@@ -8667,12 +8667,12 @@
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE LIMITADA</t>
+          <t>DISTRIBUIDORA NENE SPA</t>
         </is>
       </c>
       <c r="J135" t="inlineStr">
         <is>
-          <t>77.012.870-6</t>
+          <t>76.067.436-2</t>
         </is>
       </c>
       <c r="K135" t="inlineStr"/>
@@ -8682,13 +8682,13 @@
         </is>
       </c>
       <c r="M135" s="2" t="n">
-        <v>9813.75</v>
+        <v>4432.28</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>802-17-CM26</t>
+          <t>1350296-1137-CM26</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -8698,27 +8698,27 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>72.396.000-2</t>
+          <t>65.228.694-1</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>CORP NACIONAL DE DESARROLLO INDIGENA</t>
+          <t>HOSPITAL DE ALTO HOSPICIO</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
@@ -8743,13 +8743,13 @@
         </is>
       </c>
       <c r="M136" s="2" t="n">
-        <v>3398.37</v>
+        <v>1081.22</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>1070620-6258-CM26</t>
+          <t>1350296-1138-CM26</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -8759,12 +8759,12 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
@@ -8774,12 +8774,12 @@
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>62.000.530-4</t>
+          <t>65.228.694-1</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>HOSPITAL DOCTOR ERNESTO TORRES GALDAMES</t>
+          <t>HOSPITAL DE ALTO HOSPICIO</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
@@ -8789,12 +8789,12 @@
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE LIMITADA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J137" t="inlineStr">
         <is>
-          <t>77.012.870-6</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K137" t="inlineStr"/>
@@ -8804,13 +8804,13 @@
         </is>
       </c>
       <c r="M137" s="2" t="n">
-        <v>805</v>
+        <v>1227.57</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>1346281-109-CM26</t>
+          <t>2013-1102-CM26</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -8820,27 +8820,27 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>62.000.970-9</t>
+          <t>70.777.500-9</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
+          <t>UNIVERSIDAD ARTURO PRAT</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
@@ -8850,12 +8850,12 @@
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>COMERCIAL RED OFFICE LIMITADA</t>
         </is>
       </c>
       <c r="J138" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>77.012.870-6</t>
         </is>
       </c>
       <c r="K138" t="inlineStr"/>
@@ -8865,13 +8865,13 @@
         </is>
       </c>
       <c r="M138" s="2" t="n">
-        <v>1202.13</v>
+        <v>9813.75</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>5690-95-CM26</t>
+          <t>802-17-CM26</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -8886,22 +8886,22 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>61.308.000-7</t>
+          <t>72.396.000-2</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>SERVICIO AGRICOLA Y GANADERO</t>
+          <t>CORP NACIONAL DE DESARROLLO INDIGENA</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
@@ -8911,12 +8911,12 @@
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>DISTRIBUIDORA NENE SPA</t>
         </is>
       </c>
       <c r="J139" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>76.067.436-2</t>
         </is>
       </c>
       <c r="K139" t="inlineStr"/>
@@ -8926,13 +8926,13 @@
         </is>
       </c>
       <c r="M139" s="2" t="n">
-        <v>968.89</v>
+        <v>3398.37</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>1350296-1197-CM26</t>
+          <t>1070620-6258-CM26</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -8947,7 +8947,7 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
@@ -8957,12 +8957,12 @@
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>65.228.694-1</t>
+          <t>62.000.530-4</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>HOSPITAL DE ALTO HOSPICIO</t>
+          <t>HOSPITAL DOCTOR ERNESTO TORRES GALDAMES</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
@@ -8972,12 +8972,12 @@
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>COMERCIAL RED OFFICE LIMITADA</t>
         </is>
       </c>
       <c r="J140" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>77.012.870-6</t>
         </is>
       </c>
       <c r="K140" t="inlineStr"/>
@@ -8987,13 +8987,13 @@
         </is>
       </c>
       <c r="M140" s="2" t="n">
-        <v>1401.76</v>
+        <v>805</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>1070620-6926-CM26</t>
+          <t>1417913-529-CM26</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -9008,22 +9008,22 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>62.000.530-4</t>
+          <t>70.938.800-2</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>HOSPITAL DOCTOR ERNESTO TORRES GALDAMES</t>
+          <t>CORP MUNICIPAL DE DESARROLLO SOCIAL DE IQUIQUE</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
@@ -9048,13 +9048,13 @@
         </is>
       </c>
       <c r="M141" s="2" t="n">
-        <v>6337.61</v>
+        <v>4982.34</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>1350296-1342-CM26</t>
+          <t>1417913-532-CM26</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -9069,22 +9069,22 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>65.228.694-1</t>
+          <t>70.938.800-2</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>HOSPITAL DE ALTO HOSPICIO</t>
+          <t>CORP MUNICIPAL DE DESARROLLO SOCIAL DE IQUIQUE</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
@@ -9109,13 +9109,13 @@
         </is>
       </c>
       <c r="M142" s="2" t="n">
-        <v>3290.43</v>
+        <v>6758.59</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>1350296-1387-CM26</t>
+          <t>1346281-109-CM26</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -9130,7 +9130,7 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
@@ -9140,12 +9140,12 @@
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>65.228.694-1</t>
+          <t>62.000.970-9</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>HOSPITAL DE ALTO HOSPICIO</t>
+          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
@@ -9155,12 +9155,12 @@
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA NENE SPA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J143" t="inlineStr">
         <is>
-          <t>76.067.436-2</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K143" t="inlineStr"/>
@@ -9170,13 +9170,13 @@
         </is>
       </c>
       <c r="M143" s="2" t="n">
-        <v>2705.47</v>
+        <v>1202.13</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>845-78-CM26</t>
+          <t>5690-95-CM26</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -9186,27 +9186,27 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>jul-2026</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>70.072.600-2</t>
+          <t>61.308.000-7</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
+          <t>SERVICIO AGRICOLA Y GANADERO</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
@@ -9216,12 +9216,12 @@
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA NENE SPA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J144" t="inlineStr">
         <is>
-          <t>76.067.436-2</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K144" t="inlineStr"/>
@@ -9231,13 +9231,13 @@
         </is>
       </c>
       <c r="M144" s="2" t="n">
-        <v>13837.51</v>
+        <v>968.89</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>845-79-CM26</t>
+          <t>1350296-1197-CM26</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -9247,12 +9247,12 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>jul-2026</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
@@ -9262,12 +9262,12 @@
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>70.072.600-2</t>
+          <t>65.228.694-1</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
+          <t>HOSPITAL DE ALTO HOSPICIO</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
@@ -9277,12 +9277,12 @@
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA NENE SPA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J145" t="inlineStr">
         <is>
-          <t>76.067.436-2</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K145" t="inlineStr"/>
@@ -9292,13 +9292,13 @@
         </is>
       </c>
       <c r="M145" s="2" t="n">
-        <v>4688.17</v>
+        <v>1401.76</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>1346281-117-CM26</t>
+          <t>1070620-6926-CM26</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -9308,12 +9308,12 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>jul-2026</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
@@ -9323,12 +9323,12 @@
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>62.000.970-9</t>
+          <t>62.000.530-4</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
+          <t>HOSPITAL DOCTOR ERNESTO TORRES GALDAMES</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
@@ -9353,13 +9353,13 @@
         </is>
       </c>
       <c r="M146" s="2" t="n">
-        <v>1678.16</v>
+        <v>6337.61</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>1070620-7279-CM26</t>
+          <t>1350296-1342-CM26</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -9369,12 +9369,12 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>jul-2026</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
@@ -9384,12 +9384,12 @@
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>62.000.530-4</t>
+          <t>65.228.694-1</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>HOSPITAL DOCTOR ERNESTO TORRES GALDAMES</t>
+          <t>HOSPITAL DE ALTO HOSPICIO</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
@@ -9414,13 +9414,13 @@
         </is>
       </c>
       <c r="M147" s="2" t="n">
-        <v>8301.370000000001</v>
+        <v>3290.43</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>1070620-7312-CM26</t>
+          <t>1350296-1387-CM26</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -9430,12 +9430,12 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>jul-2026</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
@@ -9445,12 +9445,12 @@
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>62.000.530-4</t>
+          <t>65.228.694-1</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>HOSPITAL DOCTOR ERNESTO TORRES GALDAMES</t>
+          <t>HOSPITAL DE ALTO HOSPICIO</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
@@ -9475,13 +9475,13 @@
         </is>
       </c>
       <c r="M148" s="2" t="n">
-        <v>801.8099999999999</v>
+        <v>2705.47</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>1417913-633-CM26</t>
+          <t>845-79-CM26</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -9496,22 +9496,22 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>70.938.800-2</t>
+          <t>70.072.600-2</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>CORP MUNICIPAL DE DESARROLLO SOCIAL DE IQUIQUE</t>
+          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
@@ -9536,13 +9536,13 @@
         </is>
       </c>
       <c r="M149" s="2" t="n">
-        <v>3378.41</v>
+        <v>4688.17</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>1346281-129-CM26</t>
+          <t>845-78-CM26</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -9557,22 +9557,22 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>62.000.970-9</t>
+          <t>70.072.600-2</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
+          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
@@ -9582,12 +9582,12 @@
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA CUARENTA Y UNO SPA</t>
+          <t>DISTRIBUIDORA NENE SPA</t>
         </is>
       </c>
       <c r="J150" t="inlineStr">
         <is>
-          <t>78.085.401-4</t>
+          <t>76.067.436-2</t>
         </is>
       </c>
       <c r="K150" t="inlineStr"/>
@@ -9597,13 +9597,13 @@
         </is>
       </c>
       <c r="M150" s="2" t="n">
-        <v>852.8</v>
+        <v>13837.51</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>3159-131-CM26</t>
+          <t>1346281-117-CM26</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -9618,22 +9618,22 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>61.102.038-4</t>
+          <t>62.000.970-9</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
+          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
@@ -9643,12 +9643,12 @@
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA CUARENTA Y UNO SPA</t>
+          <t>DISTRIBUIDORA NENE SPA</t>
         </is>
       </c>
       <c r="J151" t="inlineStr">
         <is>
-          <t>78.085.401-4</t>
+          <t>76.067.436-2</t>
         </is>
       </c>
       <c r="K151" t="inlineStr"/>
@@ -9658,13 +9658,13 @@
         </is>
       </c>
       <c r="M151" s="2" t="n">
-        <v>810.4</v>
+        <v>1678.16</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>696217-103-CM26</t>
+          <t>1070620-7279-CM26</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -9679,22 +9679,22 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>61.935.400-1</t>
+          <t>62.000.530-4</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>MINISTERIO PUBLICO</t>
+          <t>HOSPITAL DOCTOR ERNESTO TORRES GALDAMES</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
@@ -9719,13 +9719,13 @@
         </is>
       </c>
       <c r="M152" s="2" t="n">
-        <v>1399.74</v>
+        <v>8301.370000000001</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>3352-154-CM26</t>
+          <t>1070620-7312-CM26</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -9740,7 +9740,7 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
@@ -9750,12 +9750,12 @@
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>61.101.024-9</t>
+          <t>62.000.530-4</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>HOSPITAL DOCTOR ERNESTO TORRES GALDAMES</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
@@ -9765,12 +9765,12 @@
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>DISTRIBUIDORA NENE SPA</t>
         </is>
       </c>
       <c r="J153" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>76.067.436-2</t>
         </is>
       </c>
       <c r="K153" t="inlineStr"/>
@@ -9780,13 +9780,13 @@
         </is>
       </c>
       <c r="M153" s="2" t="n">
-        <v>787.04</v>
+        <v>801.8099999999999</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>696217-109-CM26</t>
+          <t>1417913-633-CM26</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -9801,7 +9801,7 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
@@ -9811,12 +9811,12 @@
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>61.935.400-1</t>
+          <t>70.938.800-2</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>MINISTERIO PUBLICO</t>
+          <t>CORP MUNICIPAL DE DESARROLLO SOCIAL DE IQUIQUE</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
@@ -9841,13 +9841,13 @@
         </is>
       </c>
       <c r="M154" s="2" t="n">
-        <v>1695.89</v>
+        <v>3378.41</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>1417913-666-CM26</t>
+          <t>1346281-129-CM26</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -9862,7 +9862,7 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
@@ -9872,12 +9872,12 @@
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>70.938.800-2</t>
+          <t>62.000.970-9</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>CORP MUNICIPAL DE DESARROLLO SOCIAL DE IQUIQUE</t>
+          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
@@ -9887,12 +9887,12 @@
       </c>
       <c r="I155" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA NENE SPA</t>
+          <t>COMERCIALIZADORA CUARENTA Y UNO SPA</t>
         </is>
       </c>
       <c r="J155" t="inlineStr">
         <is>
-          <t>76.067.436-2</t>
+          <t>78.085.401-4</t>
         </is>
       </c>
       <c r="K155" t="inlineStr"/>
@@ -9902,13 +9902,13 @@
         </is>
       </c>
       <c r="M155" s="2" t="n">
-        <v>4057.08</v>
+        <v>852.8</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>1070620-8047-CM26</t>
+          <t>3159-131-CM26</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -9923,22 +9923,22 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>62.000.530-4</t>
+          <t>61.102.038-4</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>HOSPITAL DOCTOR ERNESTO TORRES GALDAMES</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
@@ -9948,12 +9948,12 @@
       </c>
       <c r="I156" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA NENE SPA</t>
+          <t>COMERCIALIZADORA CUARENTA Y UNO SPA</t>
         </is>
       </c>
       <c r="J156" t="inlineStr">
         <is>
-          <t>76.067.436-2</t>
+          <t>78.085.401-4</t>
         </is>
       </c>
       <c r="K156" t="inlineStr"/>
@@ -9963,13 +9963,13 @@
         </is>
       </c>
       <c r="M156" s="2" t="n">
-        <v>11819.76</v>
+        <v>810.4</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>1350296-1585-CM26</t>
+          <t>696217-103-CM26</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -9984,22 +9984,22 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>65.228.694-1</t>
+          <t>61.935.400-1</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>HOSPITAL DE ALTO HOSPICIO</t>
+          <t>MINISTERIO PUBLICO</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
@@ -10024,13 +10024,13 @@
         </is>
       </c>
       <c r="M157" s="2" t="n">
-        <v>777.5700000000001</v>
+        <v>1399.74</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>1350296-1586-CM26</t>
+          <t>3352-154-CM26</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -10045,22 +10045,22 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>65.228.694-1</t>
+          <t>61.101.024-9</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>HOSPITAL DE ALTO HOSPICIO</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
@@ -10070,12 +10070,12 @@
       </c>
       <c r="I158" t="inlineStr">
         <is>
-          <t>MUÑOZ Y VILCHES LIMITADA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J158" t="inlineStr">
         <is>
-          <t>77.008.207-2</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K158" t="inlineStr"/>
@@ -10085,7 +10085,739 @@
         </is>
       </c>
       <c r="M158" s="2" t="n">
+        <v>787.04</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>696217-109-CM26</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>2239-16-LR24</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>61.935.400-1</t>
+        </is>
+      </c>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>MINISTERIO PUBLICO</t>
+        </is>
+      </c>
+      <c r="H159" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="I159" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA NENE SPA</t>
+        </is>
+      </c>
+      <c r="J159" t="inlineStr">
+        <is>
+          <t>76.067.436-2</t>
+        </is>
+      </c>
+      <c r="K159" t="inlineStr"/>
+      <c r="L159" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M159" s="2" t="n">
+        <v>1695.89</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>1417913-666-CM26</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>2239-16-LR24</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>70.938.800-2</t>
+        </is>
+      </c>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>CORP MUNICIPAL DE DESARROLLO SOCIAL DE IQUIQUE</t>
+        </is>
+      </c>
+      <c r="H160" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="I160" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA NENE SPA</t>
+        </is>
+      </c>
+      <c r="J160" t="inlineStr">
+        <is>
+          <t>76.067.436-2</t>
+        </is>
+      </c>
+      <c r="K160" t="inlineStr"/>
+      <c r="L160" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M160" s="2" t="n">
+        <v>4057.08</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>1070620-8047-CM26</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>2239-16-LR24</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>62.000.530-4</t>
+        </is>
+      </c>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>HOSPITAL DOCTOR ERNESTO TORRES GALDAMES</t>
+        </is>
+      </c>
+      <c r="H161" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="I161" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA NENE SPA</t>
+        </is>
+      </c>
+      <c r="J161" t="inlineStr">
+        <is>
+          <t>76.067.436-2</t>
+        </is>
+      </c>
+      <c r="K161" t="inlineStr"/>
+      <c r="L161" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M161" s="2" t="n">
+        <v>11819.76</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>1350296-1585-CM26</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>2239-16-LR24</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>65.228.694-1</t>
+        </is>
+      </c>
+      <c r="G162" t="inlineStr">
+        <is>
+          <t>HOSPITAL DE ALTO HOSPICIO</t>
+        </is>
+      </c>
+      <c r="H162" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="I162" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA NENE SPA</t>
+        </is>
+      </c>
+      <c r="J162" t="inlineStr">
+        <is>
+          <t>76.067.436-2</t>
+        </is>
+      </c>
+      <c r="K162" t="inlineStr"/>
+      <c r="L162" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M162" s="2" t="n">
+        <v>777.5700000000001</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>1350296-1586-CM26</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>2239-16-LR24</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>65.228.694-1</t>
+        </is>
+      </c>
+      <c r="G163" t="inlineStr">
+        <is>
+          <t>HOSPITAL DE ALTO HOSPICIO</t>
+        </is>
+      </c>
+      <c r="H163" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="I163" t="inlineStr">
+        <is>
+          <t>MUÑOZ Y VILCHES LIMITADA</t>
+        </is>
+      </c>
+      <c r="J163" t="inlineStr">
+        <is>
+          <t>77.008.207-2</t>
+        </is>
+      </c>
+      <c r="K163" t="inlineStr"/>
+      <c r="L163" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M163" s="2" t="n">
         <v>1900.92</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>600644-61-CM26</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>2239-16-LR24</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>61.979.010-3</t>
+        </is>
+      </c>
+      <c r="G164" t="inlineStr">
+        <is>
+          <t>DELEGACIÓN PRESIDENCIAL PROVINCIAL DEL TAMARUGAL</t>
+        </is>
+      </c>
+      <c r="H164" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="I164" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA NENE SPA</t>
+        </is>
+      </c>
+      <c r="J164" t="inlineStr">
+        <is>
+          <t>76.067.436-2</t>
+        </is>
+      </c>
+      <c r="K164" t="inlineStr"/>
+      <c r="L164" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M164" s="2" t="n">
+        <v>783.8200000000001</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>838102-95-CM26</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>2239-16-LR24</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>73.923.800-5</t>
+        </is>
+      </c>
+      <c r="G165" t="inlineStr">
+        <is>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+        </is>
+      </c>
+      <c r="H165" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="I165" t="inlineStr">
+        <is>
+          <t>COMERCIALIZADORA CUARENTA Y UNO SPA</t>
+        </is>
+      </c>
+      <c r="J165" t="inlineStr">
+        <is>
+          <t>78.085.401-4</t>
+        </is>
+      </c>
+      <c r="K165" t="inlineStr"/>
+      <c r="L165" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M165" s="2" t="n">
+        <v>779.88</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>1350296-1676-CM26</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>2239-16-LR24</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>65.228.694-1</t>
+        </is>
+      </c>
+      <c r="G166" t="inlineStr">
+        <is>
+          <t>HOSPITAL DE ALTO HOSPICIO</t>
+        </is>
+      </c>
+      <c r="H166" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="I166" t="inlineStr">
+        <is>
+          <t>COMERCIALIZADORA CUARENTA Y UNO SPA</t>
+        </is>
+      </c>
+      <c r="J166" t="inlineStr">
+        <is>
+          <t>78.085.401-4</t>
+        </is>
+      </c>
+      <c r="K166" t="inlineStr"/>
+      <c r="L166" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M166" s="2" t="n">
+        <v>1355.6</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>3359-86-CM26</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>2239-16-LR24</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>61.952.300-8</t>
+        </is>
+      </c>
+      <c r="G167" t="inlineStr">
+        <is>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+        </is>
+      </c>
+      <c r="H167" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="I167" t="inlineStr">
+        <is>
+          <t>MUÑOZ Y VILCHES LIMITADA</t>
+        </is>
+      </c>
+      <c r="J167" t="inlineStr">
+        <is>
+          <t>77.008.207-2</t>
+        </is>
+      </c>
+      <c r="K167" t="inlineStr"/>
+      <c r="L167" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M167" s="2" t="n">
+        <v>993.76</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>1346281-142-CM26</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>2239-16-LR24</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>62.000.970-9</t>
+        </is>
+      </c>
+      <c r="G168" t="inlineStr">
+        <is>
+          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
+        </is>
+      </c>
+      <c r="H168" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="I168" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA NENE SPA</t>
+        </is>
+      </c>
+      <c r="J168" t="inlineStr">
+        <is>
+          <t>76.067.436-2</t>
+        </is>
+      </c>
+      <c r="K168" t="inlineStr"/>
+      <c r="L168" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M168" s="2" t="n">
+        <v>912.4</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>548847-57-CM26</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>2239-16-LR24</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>61.979.440-0</t>
+        </is>
+      </c>
+      <c r="G169" t="inlineStr">
+        <is>
+          <t>INSTITUTO DE PREVISION SOCIAL</t>
+        </is>
+      </c>
+      <c r="H169" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="I169" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA NENE SPA</t>
+        </is>
+      </c>
+      <c r="J169" t="inlineStr">
+        <is>
+          <t>76.067.436-2</t>
+        </is>
+      </c>
+      <c r="K169" t="inlineStr"/>
+      <c r="L169" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M169" s="2" t="n">
+        <v>777.26</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>1417913-785-CM26</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>2239-16-LR24</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>70.938.800-2</t>
+        </is>
+      </c>
+      <c r="G170" t="inlineStr">
+        <is>
+          <t>CORP MUNICIPAL DE DESARROLLO SOCIAL DE IQUIQUE</t>
+        </is>
+      </c>
+      <c r="H170" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="I170" t="inlineStr">
+        <is>
+          <t>RUSTIC PINK SPA</t>
+        </is>
+      </c>
+      <c r="J170" t="inlineStr">
+        <is>
+          <t>77.649.678-2</t>
+        </is>
+      </c>
+      <c r="K170" t="inlineStr"/>
+      <c r="L170" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M170" s="2" t="n">
+        <v>5808.87</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/articulos-de-escritorio-y-papeleria/tarapaca.xlsx
+++ b/docs/oc-regiones/articulos-de-escritorio-y-papeleria/tarapaca.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M234"/>
+  <dimension ref="A1:M245"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1453,7 +1453,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>696217-11-CM25</t>
+          <t>696217-12-CM25</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1508,13 +1508,13 @@
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>2180.98</v>
+        <v>782.75</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>696217-12-CM25</t>
+          <t>696217-11-CM25</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1569,13 +1569,13 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>782.75</v>
+        <v>2180.98</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>1260688-12-CM25</t>
+          <t>1260688-10-CM25</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1634,13 +1634,13 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>4727.67</v>
+        <v>10724.52</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>1260688-10-CM25</t>
+          <t>1260688-11-CM25</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1699,13 +1699,13 @@
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>10724.52</v>
+        <v>4727.67</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>1260688-14-CM25</t>
+          <t>1260688-12-CM25</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1764,7 +1764,7 @@
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>5986.69</v>
+        <v>4727.67</v>
       </c>
     </row>
     <row r="22">
@@ -1835,7 +1835,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>1260688-11-CM25</t>
+          <t>1260688-14-CM25</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1894,7 +1894,7 @@
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>4727.67</v>
+        <v>5986.69</v>
       </c>
     </row>
     <row r="24">
@@ -2148,7 +2148,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>618472-6-CM25</t>
+          <t>1070620-4238-CM25</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2173,12 +2173,12 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>61.979.990-9</t>
+          <t>62.000.530-4</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>HOSPITAL DOCTOR ERNESTO TORRES GALDAMES</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -2203,13 +2203,13 @@
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>2014.88</v>
+        <v>1608.13</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>1070620-4238-CM25</t>
+          <t>618472-6-CM25</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2234,12 +2234,12 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>62.000.530-4</t>
+          <t>61.979.990-9</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>HOSPITAL DOCTOR ERNESTO TORRES GALDAMES</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -2264,7 +2264,7 @@
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>1608.13</v>
+        <v>2014.88</v>
       </c>
     </row>
     <row r="30">
@@ -2526,7 +2526,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>548847-25-CM25</t>
+          <t>1079967-114-CM25</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2551,12 +2551,12 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>61.979.440-0</t>
+          <t>60.505.102-2</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>INSTITUTO DE PREVISION SOCIAL</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -2581,13 +2581,13 @@
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>2604.07</v>
+        <v>2147.79</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>1079967-114-CM25</t>
+          <t>548847-25-CM25</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2612,12 +2612,12 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>60.505.102-2</t>
+          <t>61.979.440-0</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>INSTITUTO DE PREVISION SOCIAL</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -2642,7 +2642,7 @@
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>2147.79</v>
+        <v>2604.07</v>
       </c>
     </row>
     <row r="36">
@@ -2774,7 +2774,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>1079967-122-CM25</t>
+          <t>5690-29-CM25</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2799,12 +2799,12 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>60.505.102-2</t>
+          <t>61.308.000-7</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>SERVICIO AGRICOLA Y GANADERO</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -2814,17 +2814,17 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>SOCIEDAD SOLUCIONES INTEGRALES SPA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>76.540.457-6</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
@@ -2833,13 +2833,13 @@
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>7856.96</v>
+        <v>850.89</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>5690-29-CM25</t>
+          <t>1079967-122-CM25</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2864,12 +2864,12 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>61.308.000-7</t>
+          <t>60.505.102-2</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>SERVICIO AGRICOLA Y GANADERO</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -2879,17 +2879,17 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>SOCIEDAD SOLUCIONES INTEGRALES SPA</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>76.540.457-6</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
@@ -2898,13 +2898,13 @@
         </is>
       </c>
       <c r="M39" s="2" t="n">
-        <v>850.89</v>
+        <v>7856.96</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>1407-15212-CM25</t>
+          <t>908366-26-CM25</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2929,12 +2929,12 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>61.004.002-0</t>
+          <t>69.010.400-8</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+          <t>I MUNICIPALIDAD DE PICA</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -2944,28 +2944,32 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA NENE SPA</t>
+          <t>COMERCIALIZADORA SAN JERONIMO SPA</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>76.067.436-2</t>
-        </is>
-      </c>
-      <c r="K40" t="inlineStr"/>
+          <t>77.610.393-4</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L40" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M40" s="2" t="n">
-        <v>684.41</v>
+        <v>12141.81</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>908366-26-CM25</t>
+          <t>1407-15212-CM25</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2990,12 +2994,12 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>69.010.400-8</t>
+          <t>61.004.002-0</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PICA</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -3005,26 +3009,22 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA SAN JERONIMO SPA</t>
+          <t>DISTRIBUIDORA NENE SPA</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>77.610.393-4</t>
-        </is>
-      </c>
-      <c r="K41" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.067.436-2</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr"/>
       <c r="L41" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M41" s="2" t="n">
-        <v>12141.81</v>
+        <v>684.41</v>
       </c>
     </row>
     <row r="42">
@@ -4749,7 +4749,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>845-122-CM25</t>
+          <t>845-121-CM25</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -4808,13 +4808,13 @@
         </is>
       </c>
       <c r="M69" s="2" t="n">
-        <v>3064</v>
+        <v>10608.84</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>845-121-CM25</t>
+          <t>845-122-CM25</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -4873,7 +4873,7 @@
         </is>
       </c>
       <c r="M70" s="2" t="n">
-        <v>10608.84</v>
+        <v>3064</v>
       </c>
     </row>
     <row r="71">
@@ -7810,7 +7810,7 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>845-220-CM25</t>
+          <t>3145-686-CM25</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -7830,17 +7830,17 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>70.072.600-2</t>
+          <t>61.103.023-1</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
+          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
@@ -7865,13 +7865,13 @@
         </is>
       </c>
       <c r="M118" s="2" t="n">
-        <v>11162.18</v>
+        <v>4420.53</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>845-222-CM25</t>
+          <t>548847-88-CM25</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -7891,17 +7891,17 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>70.072.600-2</t>
+          <t>61.979.440-0</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
+          <t>INSTITUTO DE PREVISION SOCIAL</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
@@ -7911,28 +7911,32 @@
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA NENE SPA</t>
+          <t>COMERCIAL RED OFFICE LIMITADA</t>
         </is>
       </c>
       <c r="J119" t="inlineStr">
         <is>
-          <t>76.067.436-2</t>
-        </is>
-      </c>
-      <c r="K119" t="inlineStr"/>
+          <t>77.012.870-6</t>
+        </is>
+      </c>
+      <c r="K119" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L119" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M119" s="2" t="n">
-        <v>2009.47</v>
+        <v>1368.37</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>3145-686-CM25</t>
+          <t>845-222-CM25</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -7952,17 +7956,17 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>61.103.023-1</t>
+          <t>70.072.600-2</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
+          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
@@ -7987,13 +7991,13 @@
         </is>
       </c>
       <c r="M120" s="2" t="n">
-        <v>4420.53</v>
+        <v>2009.47</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>548847-88-CM25</t>
+          <t>845-220-CM25</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -8013,17 +8017,17 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>61.979.440-0</t>
+          <t>70.072.600-2</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>INSTITUTO DE PREVISION SOCIAL</t>
+          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
@@ -8033,26 +8037,22 @@
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE LIMITADA</t>
+          <t>DISTRIBUIDORA NENE SPA</t>
         </is>
       </c>
       <c r="J121" t="inlineStr">
         <is>
-          <t>77.012.870-6</t>
-        </is>
-      </c>
-      <c r="K121" t="inlineStr">
-        <is>
-          <t>Coquimbo</t>
-        </is>
-      </c>
+          <t>76.067.436-2</t>
+        </is>
+      </c>
+      <c r="K121" t="inlineStr"/>
       <c r="L121" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M121" s="2" t="n">
-        <v>1368.37</v>
+        <v>11162.18</v>
       </c>
     </row>
     <row r="122">
@@ -8932,7 +8932,7 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>838102-17-CM26</t>
+          <t>1057448-20-CM26</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -8957,12 +8957,12 @@
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>73.923.800-5</t>
+          <t>61.606.100-3</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>SERVICIO DE SALUD IQUIQUE</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
@@ -8987,13 +8987,13 @@
         </is>
       </c>
       <c r="M136" s="2" t="n">
-        <v>909.05</v>
+        <v>5553.82</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>1057448-20-CM26</t>
+          <t>838102-17-CM26</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -9018,12 +9018,12 @@
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>61.606.100-3</t>
+          <t>73.923.800-5</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD IQUIQUE</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
@@ -9048,7 +9048,7 @@
         </is>
       </c>
       <c r="M137" s="2" t="n">
-        <v>5553.82</v>
+        <v>909.05</v>
       </c>
     </row>
     <row r="138">
@@ -9119,7 +9119,7 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>1417913-83-CM26</t>
+          <t>1346281-35-CM26</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -9144,12 +9144,12 @@
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>70.938.800-2</t>
+          <t>62.000.970-9</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>CORP MUNICIPAL DE DESARROLLO SOCIAL DE IQUIQUE</t>
+          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
@@ -9174,13 +9174,13 @@
         </is>
       </c>
       <c r="M139" s="2" t="n">
-        <v>52995.67</v>
+        <v>1298.1</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>1346281-35-CM26</t>
+          <t>1417913-83-CM26</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -9205,12 +9205,12 @@
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>62.000.970-9</t>
+          <t>70.938.800-2</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
+          <t>CORP MUNICIPAL DE DESARROLLO SOCIAL DE IQUIQUE</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
@@ -9235,7 +9235,7 @@
         </is>
       </c>
       <c r="M140" s="2" t="n">
-        <v>1298.1</v>
+        <v>52995.67</v>
       </c>
     </row>
     <row r="141">
@@ -10302,7 +10302,7 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>1346281-48-CM26</t>
+          <t>1346281-50-CM26</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -10342,32 +10342,28 @@
       </c>
       <c r="I158" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>DISTRIBUIDORA NENE SPA</t>
         </is>
       </c>
       <c r="J158" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
-        </is>
-      </c>
-      <c r="K158" t="inlineStr">
-        <is>
-          <t>Antofagasta</t>
-        </is>
-      </c>
+          <t>76.067.436-2</t>
+        </is>
+      </c>
+      <c r="K158" t="inlineStr"/>
       <c r="L158" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M158" s="2" t="n">
-        <v>859.85</v>
+        <v>753.52</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>3352-49-CM26</t>
+          <t>1079967-130-CM26</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -10392,12 +10388,12 @@
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>61.101.024-9</t>
+          <t>60.505.102-2</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
@@ -10422,13 +10418,13 @@
         </is>
       </c>
       <c r="M159" s="2" t="n">
-        <v>1475.02</v>
+        <v>31748.88</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>1346281-50-CM26</t>
+          <t>3352-49-CM26</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -10453,12 +10449,12 @@
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>62.000.970-9</t>
+          <t>61.101.024-9</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
@@ -10468,12 +10464,12 @@
       </c>
       <c r="I160" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA NENE SPA</t>
+          <t>MALMO S.A.</t>
         </is>
       </c>
       <c r="J160" t="inlineStr">
         <is>
-          <t>76.067.436-2</t>
+          <t>76.195.558-6</t>
         </is>
       </c>
       <c r="K160" t="inlineStr"/>
@@ -10483,13 +10479,13 @@
         </is>
       </c>
       <c r="M160" s="2" t="n">
-        <v>753.52</v>
+        <v>1475.02</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>1079967-130-CM26</t>
+          <t>1346281-48-CM26</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -10514,12 +10510,12 @@
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>60.505.102-2</t>
+          <t>62.000.970-9</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
@@ -10529,22 +10525,26 @@
       </c>
       <c r="I161" t="inlineStr">
         <is>
-          <t>MALMO S.A.</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J161" t="inlineStr">
         <is>
-          <t>76.195.558-6</t>
-        </is>
-      </c>
-      <c r="K161" t="inlineStr"/>
+          <t>96.670.840-9</t>
+        </is>
+      </c>
+      <c r="K161" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L161" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M161" s="2" t="n">
-        <v>31748.88</v>
+        <v>859.85</v>
       </c>
     </row>
     <row r="162">
@@ -10802,7 +10802,7 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>1312459-13-CM26</t>
+          <t>1312459-14-CM26</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -10857,13 +10857,13 @@
         </is>
       </c>
       <c r="M166" s="2" t="n">
-        <v>883.89</v>
+        <v>2737.42</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>1312459-14-CM26</t>
+          <t>1312459-13-CM26</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -10918,7 +10918,7 @@
         </is>
       </c>
       <c r="M167" s="2" t="n">
-        <v>2737.42</v>
+        <v>883.89</v>
       </c>
     </row>
     <row r="168">
@@ -11424,7 +11424,7 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>1070620-3965-CM26</t>
+          <t>1070620-3970-CM26</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -11479,13 +11479,13 @@
         </is>
       </c>
       <c r="M176" s="2" t="n">
-        <v>2654.48</v>
+        <v>2971.98</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>1070620-3970-CM26</t>
+          <t>1070620-3965-CM26</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -11540,7 +11540,7 @@
         </is>
       </c>
       <c r="M177" s="2" t="n">
-        <v>2971.98</v>
+        <v>2654.48</v>
       </c>
     </row>
     <row r="178">
@@ -12412,7 +12412,7 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>948-72-CM26</t>
+          <t>1407-331-CM26</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -12437,12 +12437,12 @@
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>60.901.003-7</t>
+          <t>61.004.002-0</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DEL MINISTERIO DE EDUCACION PUBLICA</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
@@ -12467,13 +12467,13 @@
         </is>
       </c>
       <c r="M192" s="2" t="n">
-        <v>783.7</v>
+        <v>1097.01</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>1407-331-CM26</t>
+          <t>948-72-CM26</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -12498,12 +12498,12 @@
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>61.004.002-0</t>
+          <t>60.901.003-7</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+          <t>SUBSECRETARIA DEL MINISTERIO DE EDUCACION PUBLICA</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
@@ -12528,7 +12528,7 @@
         </is>
       </c>
       <c r="M193" s="2" t="n">
-        <v>1097.01</v>
+        <v>783.7</v>
       </c>
     </row>
     <row r="194">
@@ -12843,7 +12843,7 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>1070620-5843-CM26</t>
+          <t>1350296-1138-CM26</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -12868,12 +12868,12 @@
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>62.000.530-4</t>
+          <t>65.228.694-1</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>HOSPITAL DOCTOR ERNESTO TORRES GALDAMES</t>
+          <t>HOSPITAL DE ALTO HOSPICIO</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
@@ -12883,28 +12883,32 @@
       </c>
       <c r="I199" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA NENE SPA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J199" t="inlineStr">
         <is>
-          <t>76.067.436-2</t>
-        </is>
-      </c>
-      <c r="K199" t="inlineStr"/>
+          <t>96.670.840-9</t>
+        </is>
+      </c>
+      <c r="K199" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L199" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M199" s="2" t="n">
-        <v>4432.28</v>
+        <v>1227.57</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>1350296-1137-CM26</t>
+          <t>1070620-5843-CM26</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -12929,12 +12933,12 @@
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>65.228.694-1</t>
+          <t>62.000.530-4</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>HOSPITAL DE ALTO HOSPICIO</t>
+          <t>HOSPITAL DOCTOR ERNESTO TORRES GALDAMES</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
@@ -12959,13 +12963,13 @@
         </is>
       </c>
       <c r="M200" s="2" t="n">
-        <v>1081.22</v>
+        <v>4432.28</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>1350296-1138-CM26</t>
+          <t>1350296-1137-CM26</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -13005,26 +13009,22 @@
       </c>
       <c r="I201" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>DISTRIBUIDORA NENE SPA</t>
         </is>
       </c>
       <c r="J201" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
-        </is>
-      </c>
-      <c r="K201" t="inlineStr">
-        <is>
-          <t>Antofagasta</t>
-        </is>
-      </c>
+          <t>76.067.436-2</t>
+        </is>
+      </c>
+      <c r="K201" t="inlineStr"/>
       <c r="L201" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M201" s="2" t="n">
-        <v>1227.57</v>
+        <v>1081.22</v>
       </c>
     </row>
     <row r="202">
@@ -13221,7 +13221,7 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>1417913-529-CM26</t>
+          <t>1417913-532-CM26</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -13276,13 +13276,13 @@
         </is>
       </c>
       <c r="M205" s="2" t="n">
-        <v>4982.34</v>
+        <v>6758.59</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>1417913-532-CM26</t>
+          <t>1417913-529-CM26</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -13337,7 +13337,7 @@
         </is>
       </c>
       <c r="M206" s="2" t="n">
-        <v>6758.59</v>
+        <v>4982.34</v>
       </c>
     </row>
     <row r="207">
@@ -13904,7 +13904,7 @@
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>1070620-7279-CM26</t>
+          <t>1070620-7312-CM26</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -13959,13 +13959,13 @@
         </is>
       </c>
       <c r="M216" s="2" t="n">
-        <v>8301.370000000001</v>
+        <v>801.8099999999999</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>1070620-7312-CM26</t>
+          <t>1070620-7279-CM26</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -14020,7 +14020,7 @@
         </is>
       </c>
       <c r="M217" s="2" t="n">
-        <v>801.8099999999999</v>
+        <v>8301.370000000001</v>
       </c>
     </row>
     <row r="218">
@@ -14087,7 +14087,7 @@
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>1346281-129-CM26</t>
+          <t>3159-131-CM26</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -14112,12 +14112,12 @@
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>62.000.970-9</t>
+          <t>61.102.038-4</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H219" t="inlineStr">
@@ -14146,13 +14146,13 @@
         </is>
       </c>
       <c r="M219" s="2" t="n">
-        <v>852.8</v>
+        <v>810.4</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>3159-131-CM26</t>
+          <t>1346281-129-CM26</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -14177,12 +14177,12 @@
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>61.102.038-4</t>
+          <t>62.000.970-9</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
+          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
         </is>
       </c>
       <c r="H220" t="inlineStr">
@@ -14211,7 +14211,7 @@
         </is>
       </c>
       <c r="M220" s="2" t="n">
-        <v>810.4</v>
+        <v>852.8</v>
       </c>
     </row>
     <row r="221">
@@ -14465,7 +14465,7 @@
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>1070620-8047-CM26</t>
+          <t>1350296-1586-CM26</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -14490,12 +14490,12 @@
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>62.000.530-4</t>
+          <t>65.228.694-1</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>HOSPITAL DOCTOR ERNESTO TORRES GALDAMES</t>
+          <t>HOSPITAL DE ALTO HOSPICIO</t>
         </is>
       </c>
       <c r="H225" t="inlineStr">
@@ -14505,12 +14505,12 @@
       </c>
       <c r="I225" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA NENE SPA</t>
+          <t>MUÑOZ Y VILCHES LIMITADA</t>
         </is>
       </c>
       <c r="J225" t="inlineStr">
         <is>
-          <t>76.067.436-2</t>
+          <t>77.008.207-2</t>
         </is>
       </c>
       <c r="K225" t="inlineStr"/>
@@ -14520,7 +14520,7 @@
         </is>
       </c>
       <c r="M225" s="2" t="n">
-        <v>11819.76</v>
+        <v>1900.92</v>
       </c>
     </row>
     <row r="226">
@@ -14587,7 +14587,7 @@
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>1350296-1586-CM26</t>
+          <t>1070620-8047-CM26</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
@@ -14612,12 +14612,12 @@
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>65.228.694-1</t>
+          <t>62.000.530-4</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>HOSPITAL DE ALTO HOSPICIO</t>
+          <t>HOSPITAL DOCTOR ERNESTO TORRES GALDAMES</t>
         </is>
       </c>
       <c r="H227" t="inlineStr">
@@ -14627,12 +14627,12 @@
       </c>
       <c r="I227" t="inlineStr">
         <is>
-          <t>MUÑOZ Y VILCHES LIMITADA</t>
+          <t>DISTRIBUIDORA NENE SPA</t>
         </is>
       </c>
       <c r="J227" t="inlineStr">
         <is>
-          <t>77.008.207-2</t>
+          <t>76.067.436-2</t>
         </is>
       </c>
       <c r="K227" t="inlineStr"/>
@@ -14642,7 +14642,7 @@
         </is>
       </c>
       <c r="M227" s="2" t="n">
-        <v>1900.92</v>
+        <v>11819.76</v>
       </c>
     </row>
     <row r="228">
@@ -14794,7 +14794,7 @@
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F230" t="inlineStr">
@@ -14920,7 +14920,7 @@
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F232" t="inlineStr">
@@ -14981,7 +14981,7 @@
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F233" t="inlineStr">
@@ -15082,6 +15082,701 @@
       </c>
       <c r="M234" s="2" t="n">
         <v>5808.87</v>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>5690-139-CM26</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>2239-16-LR24</t>
+        </is>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="E235" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F235" t="inlineStr">
+        <is>
+          <t>61.308.000-7</t>
+        </is>
+      </c>
+      <c r="G235" t="inlineStr">
+        <is>
+          <t>SERVICIO AGRICOLA Y GANADERO</t>
+        </is>
+      </c>
+      <c r="H235" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="I235" t="inlineStr">
+        <is>
+          <t>DIMERC S A</t>
+        </is>
+      </c>
+      <c r="J235" t="inlineStr">
+        <is>
+          <t>96.670.840-9</t>
+        </is>
+      </c>
+      <c r="K235" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="L235" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M235" s="2" t="n">
+        <v>1898.78</v>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>1350296-1873-CM26</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>2239-16-LR24</t>
+        </is>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D236" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="E236" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F236" t="inlineStr">
+        <is>
+          <t>65.228.694-1</t>
+        </is>
+      </c>
+      <c r="G236" t="inlineStr">
+        <is>
+          <t>HOSPITAL DE ALTO HOSPICIO</t>
+        </is>
+      </c>
+      <c r="H236" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="I236" t="inlineStr">
+        <is>
+          <t>DIMERC S A</t>
+        </is>
+      </c>
+      <c r="J236" t="inlineStr">
+        <is>
+          <t>96.670.840-9</t>
+        </is>
+      </c>
+      <c r="K236" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="L236" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M236" s="2" t="n">
+        <v>8380.049999999999</v>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>792895-21-CM26</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>2239-16-LR24</t>
+        </is>
+      </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D237" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="E237" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F237" t="inlineStr">
+        <is>
+          <t>61.980.220-9</t>
+        </is>
+      </c>
+      <c r="G237" t="inlineStr">
+        <is>
+          <t>SUPERINTENDENCIA DE EDUCACION ESCOLAR</t>
+        </is>
+      </c>
+      <c r="H237" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="I237" t="inlineStr">
+        <is>
+          <t>DIMERC S A</t>
+        </is>
+      </c>
+      <c r="J237" t="inlineStr">
+        <is>
+          <t>96.670.840-9</t>
+        </is>
+      </c>
+      <c r="K237" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="L237" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M237" s="2" t="n">
+        <v>1089.68</v>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>1346281-153-CM26</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>2239-16-LR24</t>
+        </is>
+      </c>
+      <c r="C238" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D238" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="E238" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F238" t="inlineStr">
+        <is>
+          <t>62.000.970-9</t>
+        </is>
+      </c>
+      <c r="G238" t="inlineStr">
+        <is>
+          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
+        </is>
+      </c>
+      <c r="H238" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="I238" t="inlineStr">
+        <is>
+          <t>DIMERC S A</t>
+        </is>
+      </c>
+      <c r="J238" t="inlineStr">
+        <is>
+          <t>96.670.840-9</t>
+        </is>
+      </c>
+      <c r="K238" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="L238" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M238" s="2" t="n">
+        <v>853.7</v>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>1346281-155-CM26</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>2239-16-LR24</t>
+        </is>
+      </c>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D239" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="E239" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F239" t="inlineStr">
+        <is>
+          <t>62.000.970-9</t>
+        </is>
+      </c>
+      <c r="G239" t="inlineStr">
+        <is>
+          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
+        </is>
+      </c>
+      <c r="H239" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="I239" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA NENE SPA</t>
+        </is>
+      </c>
+      <c r="J239" t="inlineStr">
+        <is>
+          <t>76.067.436-2</t>
+        </is>
+      </c>
+      <c r="K239" t="inlineStr"/>
+      <c r="L239" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M239" s="2" t="n">
+        <v>808.96</v>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>1347772-96-CM26</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>2239-16-LR24</t>
+        </is>
+      </c>
+      <c r="C240" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D240" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="E240" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F240" t="inlineStr">
+        <is>
+          <t>62.000.890-7</t>
+        </is>
+      </c>
+      <c r="G240" t="inlineStr">
+        <is>
+          <t>SERVICIO NACIONAL DE PROTECCIÓN ESPECIALIZADA A LA NIÑEZ Y ADOLESCENCI</t>
+        </is>
+      </c>
+      <c r="H240" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="I240" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA NENE SPA</t>
+        </is>
+      </c>
+      <c r="J240" t="inlineStr">
+        <is>
+          <t>76.067.436-2</t>
+        </is>
+      </c>
+      <c r="K240" t="inlineStr"/>
+      <c r="L240" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M240" s="2" t="n">
+        <v>1693.17</v>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>951-60-CM26</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>2239-16-LR24</t>
+        </is>
+      </c>
+      <c r="C241" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D241" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="E241" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F241" t="inlineStr">
+        <is>
+          <t>60.511.010-K</t>
+        </is>
+      </c>
+      <c r="G241" t="inlineStr">
+        <is>
+          <t>DELEGACIÓN PRESIDENCIAL REGIONAL DE TARAPACÁ</t>
+        </is>
+      </c>
+      <c r="H241" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="I241" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA NENE SPA</t>
+        </is>
+      </c>
+      <c r="J241" t="inlineStr">
+        <is>
+          <t>76.067.436-2</t>
+        </is>
+      </c>
+      <c r="K241" t="inlineStr"/>
+      <c r="L241" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M241" s="2" t="n">
+        <v>814.1900000000001</v>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>1070620-9199-CM26</t>
+        </is>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>2239-16-LR24</t>
+        </is>
+      </c>
+      <c r="C242" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D242" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="E242" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F242" t="inlineStr">
+        <is>
+          <t>62.000.530-4</t>
+        </is>
+      </c>
+      <c r="G242" t="inlineStr">
+        <is>
+          <t>HOSPITAL DOCTOR ERNESTO TORRES GALDAMES</t>
+        </is>
+      </c>
+      <c r="H242" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="I242" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA NENE SPA</t>
+        </is>
+      </c>
+      <c r="J242" t="inlineStr">
+        <is>
+          <t>76.067.436-2</t>
+        </is>
+      </c>
+      <c r="K242" t="inlineStr"/>
+      <c r="L242" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M242" s="2" t="n">
+        <v>8109.99</v>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>707412-75-CM26</t>
+        </is>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>2239-16-LR24</t>
+        </is>
+      </c>
+      <c r="C243" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D243" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="E243" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F243" t="inlineStr">
+        <is>
+          <t>70.574.900-0</t>
+        </is>
+      </c>
+      <c r="G243" t="inlineStr">
+        <is>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+        </is>
+      </c>
+      <c r="H243" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="I243" t="inlineStr">
+        <is>
+          <t>DIMERC S A</t>
+        </is>
+      </c>
+      <c r="J243" t="inlineStr">
+        <is>
+          <t>96.670.840-9</t>
+        </is>
+      </c>
+      <c r="K243" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="L243" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M243" s="2" t="n">
+        <v>1782.22</v>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>2013-1683-CM26</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>2239-16-LR24</t>
+        </is>
+      </c>
+      <c r="C244" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D244" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="E244" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F244" t="inlineStr">
+        <is>
+          <t>70.777.500-9</t>
+        </is>
+      </c>
+      <c r="G244" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD ARTURO PRAT</t>
+        </is>
+      </c>
+      <c r="H244" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="I244" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA NENE SPA</t>
+        </is>
+      </c>
+      <c r="J244" t="inlineStr">
+        <is>
+          <t>76.067.436-2</t>
+        </is>
+      </c>
+      <c r="K244" t="inlineStr"/>
+      <c r="L244" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M244" s="2" t="n">
+        <v>1369.95</v>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>935934-248-CM26</t>
+        </is>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>2239-16-LR24</t>
+        </is>
+      </c>
+      <c r="C245" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D245" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="E245" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F245" t="inlineStr">
+        <is>
+          <t>61.980.770-7</t>
+        </is>
+      </c>
+      <c r="G245" t="inlineStr">
+        <is>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+        </is>
+      </c>
+      <c r="H245" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="I245" t="inlineStr">
+        <is>
+          <t>DIMERC S A</t>
+        </is>
+      </c>
+      <c r="J245" t="inlineStr">
+        <is>
+          <t>96.670.840-9</t>
+        </is>
+      </c>
+      <c r="K245" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="L245" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M245" s="2" t="n">
+        <v>1647.9</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/articulos-de-escritorio-y-papeleria/tarapaca.xlsx
+++ b/docs/oc-regiones/articulos-de-escritorio-y-papeleria/tarapaca.xlsx
@@ -15611,7 +15611,7 @@
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F243" t="inlineStr">
